--- a/fine_tuning_excel_pack_brand_voice_UTF8_FIXED/01_train_examples_brand_voice_UTF8_FIXED.xlsx
+++ b/fine_tuning_excel_pack_brand_voice_UTF8_FIXED/01_train_examples_brand_voice_UTF8_FIXED.xlsx
@@ -39,27 +39,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="208">
-  <si>
-    <t>input</t>
-  </si>
-  <si>
-    <t>output</t>
-  </si>
-  <si>
-    <t>industry</t>
-  </si>
-  <si>
-    <t>tone</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>product</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="582">
+  <si>
+    <t xml:space="preserve">input</t>
+  </si>
+  <si>
+    <t xml:space="preserve">output</t>
+  </si>
+  <si>
+    <t xml:space="preserve">industry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">product</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Khẩn cấp.
 Sản phẩm/dịch vụ: bình giữ nhiệt thép 316.
 Từ khóa chính: giữ nóng 8 giờ; nắp chống tràn; dễ vệ sinh.
@@ -82,33 +82,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Đừng chần chừ với bình giữ nhiệt thép 316 cho dân văn phòng mang cà phê đi làm với giữ nóng 8 giờ.
-Subheadline: Tập trung vào nắp chống tràn và dễ vệ sinh, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: bình giữ nhiệt thép 316 là lựa chọn đáng cân nhắc cho dân văn phòng mang cà phê đi làm.
-Subheadline: Điểm mạnh nằm ở nắp chống tràn, giữ nóng 8 giờ và freeship cho đơn từ 2 sản phẩm để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Giữ nhịp nhanh hơn cho bình giữ nhiệt thép 316 nếu bạn cần giữ nóng 8 giờ và nắp chống tràn.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>ecommerce</t>
-  </si>
-  <si>
-    <t>urgent</t>
-  </si>
-  <si>
-    <t>headline</t>
-  </si>
-  <si>
-    <t>bình giữ nhiệt thép 316</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: bình giữ nhiệt thép 316: gọn hơn cho những lúc giữ nóng 8 giờ thật sự quan trọng.
+Subheadline: Dành cho dân văn phòng mang cà phê đi làm, nhất là khi buổi sáng bỏ bình vào túi, đi qua vài cuộc họp vẫn còn cảm giác yên tâm vì đồ uống được chuẩn bị từ nhà. Điểm đáng xem là giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên kiểm tra dung tích và cách đóng nắp trước khi chọn.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với bình giữ nhiệt thép 316.
+Subheadline: Nếu bạn từng ngại chuyện ngại nước rò ra giấy tờ, laptop hoặc phải mất thời gian cọ rửa cuối ngày, hãy bắt đầu từ ba điểm: giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh. Ưu đãi hiện có: freeship cho đơn từ 2 sản phẩm.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn bình giữ nhiệt thép 316 vừa đủ thực tế cho dân văn phòng mang cà phê đi làm.
+Subheadline: Hợp với người muốn ly cà phê mang đi gọn gàng, không thành một việc phải canh chừng. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Freeship cho đơn từ 2 sản phẩm là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bình giữ nhiệt thép 316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
 Sản phẩm/dịch vụ: bình giữ nhiệt thép 316.
 Từ khóa chính: giữ nóng 8 giờ; nắp chống tràn; dễ vệ sinh.
@@ -131,24 +134,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Gợi ý dễ dùng cho bình giữ nhiệt thép 316 cho dân văn phòng mang cà phê đi làm với giữ nóng 8 giờ.
-Subheadline: Tập trung vào nắp chống tràn và dễ vệ sinh, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: bình giữ nhiệt thép 316 là lựa chọn đáng cân nhắc cho dân văn phòng mang cà phê đi làm.
-Subheadline: Điểm mạnh nằm ở nắp chống tràn, giữ nóng 8 giờ và freeship cho đơn từ 2 sản phẩm để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Thêm tiện lợi cho bình giữ nhiệt thép 316 nếu bạn cần giữ nóng 8 giờ và nắp chống tràn.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>friendly</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: bình giữ nhiệt thép 316: gọn hơn cho những lúc giữ nóng 8 giờ thật sự quan trọng.
+Subheadline: Dành cho dân văn phòng mang cà phê đi làm, nhất là khi buổi sáng bỏ bình vào túi, đi qua vài cuộc họp vẫn còn cảm giác yên tâm vì đồ uống được chuẩn bị từ nhà. Điểm đáng xem là giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên kiểm tra dung tích và cách đóng nắp trước khi chọn.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với bình giữ nhiệt thép 316.
+Subheadline: Nếu bạn từng ngại chuyện ngại nước rò ra giấy tờ, laptop hoặc phải mất thời gian cọ rửa cuối ngày, hãy bắt đầu từ ba điểm: giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh. Ưu đãi hiện có: freeship cho đơn từ 2 sản phẩm.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn bình giữ nhiệt thép 316 vừa đủ thực tế cho dân văn phòng mang cà phê đi làm.
+Subheadline: Hợp với người muốn ly cà phê mang đi gọn gàng, không thành một việc phải canh chừng. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Freeship cho đơn từ 2 sản phẩm là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bình giữ nhiệt thép 316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Cảm xúc.
 Sản phẩm/dịch vụ: bình giữ nhiệt thép 316.
 Từ khóa chính: giữ nóng 8 giờ; nắp chống tràn; dễ vệ sinh.
@@ -172,42 +187,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Mô tả ngắn: bình giữ nhiệt thép 316 dành cho dân văn phòng mang cà phê đi làm, nhấn vào trải nghiệm dùng rõ ràng và dễ hiểu.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. bình giữ nhiệt thép 316 dành cho dân văn phòng mang cà phê đi làm trong những lúc buổi sáng bỏ bình vào túi, đi qua vài cuộc họp vẫn còn cảm giác yên tâm vì đồ uống được chuẩn bị từ nhà.
 Lợi ích chính:
-- Hỗ trợ nhu cầu thực tế nhờ giữ nóng 8 giờ và nắp chống tràn.
-- Giúp bạn cân nhắc nhanh hơn với thông tin đúng brief và freeship cho đơn từ 2 sản phẩm.
+- Giúp bạn yên tâm hơn với nhu cầu giữ nóng 8 giờ mà không phải đọc quá nhiều thông tin rối.
+- Nắp chống tràn là điểm cộng rõ ràng khi dùng hằng ngày.
+- Dễ vệ sinh giúp sản phẩm dễ được đưa vào thói quen hiện có.
 Đặc điểm nổi bật:
-- giữ nóng 8 giờ.
-- dễ vệ sinh.
-Lời kêu gọi hành động: Xem chi tiết để chọn mẫu phù hợp.
-Phiên bản 2:
-Mô tả ngắn: Nếu bạn là dân văn phòng mang cà phê đi làm, bình giữ nhiệt thép 316 là một lựa chọn gọn gàng, dễ dùng và sát nhu cầu.
+- giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh.
+- Thông tin đi kèm: freeship cho đơn từ 2 sản phẩm.
+Góc cần biết: Bạn nên kiểm tra dung tích và cách đóng nắp trước khi chọn.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì ngại nước rò ra giấy tờ, laptop hoặc phải mất thời gian cọ rửa cuối ngày, bình giữ nhiệt thép 316 là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh.
 Lợi ích chính:
-- Mang lại cảm giác yên tâm khi xem thông tin rõ ràng.
-- Tập trung vào nắp chống tràn và dễ vệ sinh để phục vụ dùng hằng ngày.
-Đặc điểm nổi bật:
-- nắp chống tràn.
-- freeship cho đơn từ 2 sản phẩm.
-Lời kêu gọi hành động: Nhắn tin để được tư vấn trước khi mua.
-Phiên bản 3:
-Mô tả ngắn: bình giữ nhiệt thép 316 giúp dân văn phòng mang cà phê đi làm có thêm một lựa chọn hợp lý cho nhu cầu thường ngày.
-Lợi ích chính:
-- dễ vệ sinh làm cho việc dùng tiện hơn.
-- giữ nóng 8 giờ hỗ trợ đúng mối quan tâm chính.
+- Phù hợp với dân văn phòng mang cà phê đi làm muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi freeship cho đơn từ 2 sản phẩm giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
 Đặc điểm nổi bật:
 - giữ nóng 8 giờ.
 - nắp chống tràn.
-Lời kêu gọi hành động: Lưu lại để so sánh khi cần.</t>
-  </si>
-  <si>
-    <t>emotional</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+- dễ vệ sinh.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: bình giữ nhiệt thép 316 hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người muốn ly cà phê mang đi gọn gàng, không thành một việc phải canh chừng.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh.
+- Ghi chú thêm để cân nhắc: freeship cho đơn từ 2 sản phẩm.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emotional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bình giữ nhiệt thép 316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: bình giữ nhiệt thép 316.
 Từ khóa chính: giữ nóng 8 giờ; nắp chống tràn; dễ vệ sinh.
@@ -231,10 +259,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>professional</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. bình giữ nhiệt thép 316 dành cho dân văn phòng mang cà phê đi làm trong những lúc buổi sáng bỏ bình vào túi, đi qua vài cuộc họp vẫn còn cảm giác yên tâm vì đồ uống được chuẩn bị từ nhà.
+Lợi ích chính:
+- Giúp bạn yên tâm hơn với nhu cầu giữ nóng 8 giờ mà không phải đọc quá nhiều thông tin rối.
+- Nắp chống tràn là điểm cộng rõ ràng khi dùng hằng ngày.
+- Dễ vệ sinh giúp sản phẩm dễ được đưa vào thói quen hiện có.
+Đặc điểm nổi bật:
+- giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh.
+- Thông tin đi kèm: freeship cho đơn từ 2 sản phẩm.
+Góc cần biết: Bạn nên kiểm tra dung tích và cách đóng nắp trước khi chọn.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì ngại nước rò ra giấy tờ, laptop hoặc phải mất thời gian cọ rửa cuối ngày, bình giữ nhiệt thép 316 là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh.
+Lợi ích chính:
+- Phù hợp với dân văn phòng mang cà phê đi làm muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi freeship cho đơn từ 2 sản phẩm giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
+Đặc điểm nổi bật:
+- giữ nóng 8 giờ.
+- nắp chống tràn.
+- dễ vệ sinh.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: bình giữ nhiệt thép 316 hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người muốn ly cà phê mang đi gọn gàng, không thành một việc phải canh chừng.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh.
+- Ghi chú thêm để cân nhắc: freeship cho đơn từ 2 sản phẩm.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bình giữ nhiệt thép 316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Thân thiện.
 Sản phẩm/dịch vụ: bình giữ nhiệt thép 316.
 Từ khóa chính: giữ nóng 8 giờ; nắp chống tràn; dễ vệ sinh.
@@ -258,27 +331,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Một lựa chọn thân thiện cho dân văn phòng mang cà phê đi làm.
-Caption: bình giữ nhiệt thép 316 giúp việc hằng ngày nhẹ hơn nhờ giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh. Hiện có freeship cho đơn từ 2 sản phẩm, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #BinhGiuNhiet #DanVanPhong #GiuNong8
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của dân văn phòng mang cà phê đi làm.
-Caption: Với nắp chống tràn và dễ vệ sinh, bình giữ nhiệt thép 316 cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. freeship cho đơn từ 2 sản phẩm là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #BinhGiuNhiet #NapChongTran #MuaSamThongMinh
-Phiên bản 3:
-Hook: Gợi ý dễ dùng cho dân văn phòng mang cà phê đi làm một lựa chọn gọn gàng hơn.
-Caption: Khi xem bình giữ nhiệt thép 316, hãy chú ý vào giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #BinhGiuNhiet #DeVeSinh #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>social</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Một món nhỏ, nhưng dùng đúng lúc thì thấy ngày nhẹ hơn một chút.
+Caption: bình giữ nhiệt thép 316 dành cho dân văn phòng mang cà phê đi làm trong những lúc buổi sáng bỏ bình vào túi, đi qua vài cuộc họp vẫn còn cảm giác yên tâm vì đồ uống được chuẩn bị từ nhà. Mình sẽ nhìn vào giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh trước, rồi mới xét đến ưu đãi freeship cho đơn từ 2 sản phẩm. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên kiểm tra dung tích và cách đóng nắp trước khi chọn.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #BinhGiuNhiet #CaPheDiLam #MuaSamThongMinh
+Phiên bản 2:
+Hook: Mua sắm dễ chịu hơn khi thông tin đủ rõ và không bị thúc ép.
+Caption: Nếu bạn từng gặp chuyện ngại nước rò ra giấy tờ, laptop hoặc phải mất thời gian cọ rửa cuối ngày, bình giữ nhiệt thép 316 là một lựa chọn đáng để lưu lại. Sản phẩm có giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Freeship cho đơn từ 2 sản phẩm là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #BinhGiuNhiet #CaPheDiLam #MuaSamThongMinh
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với bình giữ nhiệt thép 316, hãy bắt đầu từ nhu cầu của dân văn phòng mang cà phê đi làm: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người muốn ly cà phê mang đi gọn gàng, không thành một việc phải canh chừng.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #BinhGiuNhiet #CaPheDiLam #MuaSamThongMinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bình giữ nhiệt thép 316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Khẩn cấp.
 Sản phẩm/dịch vụ: bình giữ nhiệt thép 316.
 Từ khóa chính: giữ nóng 8 giờ; nắp chống tràn; dễ vệ sinh.
@@ -302,24 +387,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Cần xem ngay cho dân văn phòng mang cà phê đi làm.
-Caption: bình giữ nhiệt thép 316 giúp việc hằng ngày nhẹ hơn nhờ giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh. Hiện có freeship cho đơn từ 2 sản phẩm, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #BinhGiuNhiet #DanVanPhong #GiuNong8
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của dân văn phòng mang cà phê đi làm.
-Caption: Với nắp chống tràn và dễ vệ sinh, bình giữ nhiệt thép 316 cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. freeship cho đơn từ 2 sản phẩm là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #BinhGiuNhiet #NapChongTran #MuaSamThongMinh
-Phiên bản 3:
-Hook: Đừng chần chừ với dân văn phòng mang cà phê đi làm một lựa chọn gọn gàng hơn.
-Caption: Khi xem bình giữ nhiệt thép 316, hãy chú ý vào giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #BinhGiuNhiet #DeVeSinh #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Đang cân nhắc thì nên xem kỹ hôm nay, nhưng không cần mua vội.
+Caption: bình giữ nhiệt thép 316 dành cho dân văn phòng mang cà phê đi làm trong những lúc buổi sáng bỏ bình vào túi, đi qua vài cuộc họp vẫn còn cảm giác yên tâm vì đồ uống được chuẩn bị từ nhà. Mình sẽ nhìn vào giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh trước, rồi mới xét đến ưu đãi freeship cho đơn từ 2 sản phẩm. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên kiểm tra dung tích và cách đóng nắp trước khi chọn.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #BinhGiuNhiet #CaPheDiLam #MuaSamThongMinh
+Phiên bản 2:
+Hook: Ưu đãi chỉ đáng giữ lại khi sản phẩm thật sự hợp với cách bạn dùng.
+Caption: Nếu bạn từng gặp chuyện ngại nước rò ra giấy tờ, laptop hoặc phải mất thời gian cọ rửa cuối ngày, bình giữ nhiệt thép 316 là một lựa chọn đáng để lưu lại. Sản phẩm có giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Freeship cho đơn từ 2 sản phẩm là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #BinhGiuNhiet #CaPheDiLam #MuaSamThongMinh
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với bình giữ nhiệt thép 316, hãy bắt đầu từ nhu cầu của dân văn phòng mang cà phê đi làm: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người muốn ly cà phê mang đi gọn gàng, không thành một việc phải canh chừng.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #BinhGiuNhiet #CaPheDiLam #MuaSamThongMinh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bình giữ nhiệt thép 316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Email Marketing với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: bình giữ nhiệt thép 316.
 Từ khóa chính: giữ nóng 8 giờ; nắp chống tràn; dễ vệ sinh.
@@ -344,30 +444,45 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Subject: Gợi ý bình giữ nhiệt thép 316 cho dân văn phòng mang cà phê đi làm
-Preview text: Tóm tắt nhanh các điểm đáng cân nhắc trước khi chọn mua.
+    <t xml:space="preserve">Phiên bản 1:
+Subject: Gợi ý bình giữ nhiệt thép 316 cho nhu cầu dùng hằng ngày
+Preview text: Một vài điểm đáng xem trước khi bạn quyết định.
 Lời chào: Chào bạn,
-Nội dung chính: Nếu bạn đang tìm một lựa chọn phù hợp cho nhu cầu hằng ngày, bình giữ nhiệt thép 316 có các điểm nổi bật như giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh. Hiện có freeship cho đơn từ 2 sản phẩm, nên bạn có thể xem thêm thông tin trước khi quyết định.
-Lời kêu gọi hành động: Xem chi tiết sản phẩm hôm nay.
-Phiên bản 2:
-Subject: bình giữ nhiệt thép 316 có thể hợp với nhu cầu của bạn
-Preview text: Một vài lý do để dân văn phòng mang cà phê đi làm cân nhắc sản phẩm này.
+Nội dung chính: Nếu bạn là dân văn phòng mang cà phê đi làm, có lẽ điều bạn cần không phải một lời giới thiệu quá mạnh. Bạn cần biết bình giữ nhiệt thép 316 có hợp với bối cảnh buổi sáng bỏ bình vào túi, đi qua vài cuộc họp vẫn còn cảm giác yên tâm vì đồ uống được chuẩn bị từ nhà hay không.
+Sản phẩm này đáng xem nhờ giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh. Trong đó, giữ nóng 8 giờ giúp xử lý nhu cầu chính; nắp chống tràn và dễ vệ sinh làm trải nghiệm dùng trọn vẹn hơn.
+Góc cần biết: Bạn nên kiểm tra dung tích và cách đóng nắp trước khi chọn. Hiện có freeship cho đơn từ 2 sản phẩm, bạn có thể xem như một điểm cộng nếu sản phẩm đã đúng nhu cầu.
+Lời kêu gọi hành động: Mở chi tiết sản phẩm hoặc nhắn shop để được tư vấn kỹ hơn.
+Phiên bản 2:
+Subject: Trước khi mua bình giữ nhiệt thép 316, bạn có thể xem nhanh điểm này
+Preview text: Chọn chắc hơn khi biết sản phẩm giải quyết đúng việc gì.
 Lời chào: Chào bạn,
-Nội dung chính: bình giữ nhiệt thép 316 tập trung vào nắp chống tràn, giữ nóng 8 giờ và dễ vệ sinh. Thông tin được viết theo đúng brief, không thêm chứng nhận hay số liệu ngoài phạm vi. freeship cho đơn từ 2 sản phẩm giúp bạn có thêm lý do so sánh.
-Lời kêu gọi hành động: Nhắn lại để được tư vấn lựa chọn phù hợp.
-Phiên bản 3:
-Subject: Xem nhanh bình giữ nhiệt thép 316 trước khi bạn chọn
-Preview text: Thông tin ngắn gọn, dễ so sánh và có ưu đãi đi kèm.
+Nội dung chính: Nhiều người phân vân vì ngại nước rò ra giấy tờ, laptop hoặc phải mất thời gian cọ rửa cuối ngày. Vì vậy, với bình giữ nhiệt thép 316, hãy nhìn vào nhu cầu thật trước: bạn cần giữ nóng 8 giờ, muốn nắp chống tràn, hay quan tâm nhiều hơn đến dễ vệ sinh?
+Nếu câu trả lời khớp với cách bạn dùng hằng ngày, đây là lựa chọn đáng cân nhắc. Nếu chưa chắc, bạn có thể hỏi shop trước khi đặt.
+Góc cần biết: Freeship cho đơn từ 2 sản phẩm đang đi kèm, nhưng quyết định cuối cùng vẫn nên dựa trên mức độ phù hợp.
+Lời kêu gọi hành động: Trả lời tin nhắn này với nhu cầu của bạn, shop sẽ gợi ý cụ thể hơn.
+Phiên bản 3:
+Subject: bình giữ nhiệt thép 316 có thể là món bạn đang tìm
+Preview text: Rõ lợi ích, rõ tình huống dùng, không cần quyết định vội.
 Lời chào: Chào bạn,
-Nội dung chính: Với dân văn phòng mang cà phê đi làm, một sản phẩm dễ hiểu thường giúp quyết định nhanh hơn. bình giữ nhiệt thép 316 có giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh; ngoài ra còn có freeship cho đơn từ 2 sản phẩm để bạn cân nhắc thêm.
-Lời kêu gọi hành động: Mở trang sản phẩm để xem thêm chi tiết.</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Nội dung chính: Hợp với người muốn ly cà phê mang đi gọn gàng, không thành một việc phải canh chừng. bình giữ nhiệt thép 316 tập trung vào giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh, phù hợp với dân văn phòng mang cà phê đi làm khi muốn một lựa chọn thực tế hơn cho sinh hoạt hằng ngày.
+Bạn có thể cân nhắc sản phẩm này nếu đang cần giải quyết chuyện ngại nước rò ra giấy tờ, laptop hoặc phải mất thời gian cọ rửa cuối ngày. Còn nếu muốn chắc hơn, hãy hỏi shop về tình huống dùng của bạn.
+Góc cần biết: Bạn nên kiểm tra dung tích và cách đóng nắp trước khi chọn.
+Lời kêu gọi hành động: Xem chi tiết hoặc nhắn shop trước khi chốt đơn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bình giữ nhiệt thép 316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Lời Kêu Gọi Hành Động với tone Thân thiện.
 Sản phẩm/dịch vụ: bình giữ nhiệt thép 316.
 Từ khóa chính: giữ nóng 8 giờ; nắp chống tràn; dễ vệ sinh.
@@ -389,21 +504,30 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Lời kêu gọi hành động chính: Mua bình giữ nhiệt thép 316 ngay hôm nay
-Microcopy: Phù hợp cho dân văn phòng mang cà phê đi làm, có freeship cho đơn từ 2 sản phẩm và thông tin rõ ràng để bạn chọn nhanh.
-Phiên bản 2:
-Lời kêu gọi hành động chính: Chọn bình giữ nhiệt thép 316 cho nhu cầu hiện tại
-Microcopy: Tập trung vào giữ nóng 8 giờ và nắp chống tràn, giúp bạn quyết định dễ hơn.
-Phiên bản 3:
-Lời kêu gọi hành động chính: Nhắn shop để được tư vấn bình giữ nhiệt thép 316
-Microcopy: Bạn có thể hỏi thêm về dễ vệ sinh và freeship cho đơn từ 2 sản phẩm trước khi quyết định.</t>
-  </si>
-  <si>
-    <t>cta</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Lời kêu gọi hành động chính: Xem bình giữ nhiệt thép 316 có hợp với bạn không
+Microcopy: Dành cho dân văn phòng mang cà phê đi làm, nổi bật với giữ nóng 8 giờ, nắp chống tràn và dễ vệ sinh. Có freeship cho đơn từ 2 sản phẩm nếu bạn muốn cân nhắc thêm.
+Phiên bản 2:
+Lời kêu gọi hành động chính: Nhắn shop để chọn bình giữ nhiệt thép 316 đúng nhu cầu
+Microcopy: Kể nhanh bạn dùng trong bối cảnh nào, shop sẽ gợi ý theo tình huống thật như buổi sáng bỏ bình vào túi, đi qua vài cuộc họp vẫn còn cảm giác yên tâm vì đồ uống được chuẩn bị từ nhà.
+Phiên bản 3:
+Lời kêu gọi hành động chính: Lưu bình giữ nhiệt thép 316 để so sánh trước khi mua
+Microcopy: Phù hợp hơn khi bạn muốn giải quyết chuyện ngại nước rò ra giấy tờ, laptop hoặc phải mất thời gian cọ rửa cuối ngày mà vẫn cần một lựa chọn rõ ràng, dễ hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bình giữ nhiệt thép 316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Khẩn cấp.
 Sản phẩm/dịch vụ: đèn bàn LED chống chói.
 Từ khóa chính: 3 mức sáng; cổ đèn linh hoạt; tiết kiệm điện.
@@ -426,24 +550,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Đừng chần chừ với đèn bàn LED chống chói cho sinh viên học khuya và làm việc tại nhà với 3 mức sáng.
-Subheadline: Tập trung vào cổ đèn linh hoạt và tiết kiệm điện, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: đèn bàn LED chống chói là lựa chọn đáng cân nhắc cho sinh viên học khuya và làm việc tại nhà.
-Subheadline: Điểm mạnh nằm ở cổ đèn linh hoạt, 3 mức sáng và giảm 10 phần trăm cho khách mới để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Giữ nhịp nhanh hơn cho đèn bàn LED chống chói nếu bạn cần 3 mức sáng và cổ đèn linh hoạt.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>đèn bàn LED chống chói</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: đèn bàn LED chống chói: gọn hơn cho những lúc 3 mức sáng thật sự quan trọng.
+Subheadline: Dành cho sinh viên học khuya và làm việc tại nhà, nhất là khi góc bàn học khuya hoặc bàn làm việc tại nhà cần ánh sáng ổn định, không quá gắt. Điểm đáng xem là 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên cân nhắc diện tích bàn và thói quen đọc, viết, dùng laptop.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với đèn bàn LED chống chói.
+Subheadline: Nếu bạn từng ngại chuyện ngồi lâu dễ mỏi mắt nếu đèn quá chói hoặc không chỉnh được hướng sáng, hãy bắt đầu từ ba điểm: 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện. Ưu đãi hiện có: giảm 10 phần trăm cho khách mới.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn đèn bàn LED chống chói vừa đủ thực tế cho sinh viên học khuya và làm việc tại nhà.
+Subheadline: Hợp với người cần một chiếc đèn dễ dùng mỗi tối, không phải setup phức tạp. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Giảm 10 phần trăm cho khách mới là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">đèn bàn LED chống chói</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
 Sản phẩm/dịch vụ: đèn bàn LED chống chói.
 Từ khóa chính: 3 mức sáng; cổ đèn linh hoạt; tiết kiệm điện.
@@ -466,21 +602,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Gợi ý dễ dùng cho đèn bàn LED chống chói cho sinh viên học khuya và làm việc tại nhà với 3 mức sáng.
-Subheadline: Tập trung vào cổ đèn linh hoạt và tiết kiệm điện, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: đèn bàn LED chống chói là lựa chọn đáng cân nhắc cho sinh viên học khuya và làm việc tại nhà.
-Subheadline: Điểm mạnh nằm ở cổ đèn linh hoạt, 3 mức sáng và giảm 10 phần trăm cho khách mới để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Thêm tiện lợi cho đèn bàn LED chống chói nếu bạn cần 3 mức sáng và cổ đèn linh hoạt.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: đèn bàn LED chống chói: gọn hơn cho những lúc 3 mức sáng thật sự quan trọng.
+Subheadline: Dành cho sinh viên học khuya và làm việc tại nhà, nhất là khi góc bàn học khuya hoặc bàn làm việc tại nhà cần ánh sáng ổn định, không quá gắt. Điểm đáng xem là 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên cân nhắc diện tích bàn và thói quen đọc, viết, dùng laptop.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với đèn bàn LED chống chói.
+Subheadline: Nếu bạn từng ngại chuyện ngồi lâu dễ mỏi mắt nếu đèn quá chói hoặc không chỉnh được hướng sáng, hãy bắt đầu từ ba điểm: 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện. Ưu đãi hiện có: giảm 10 phần trăm cho khách mới.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn đèn bàn LED chống chói vừa đủ thực tế cho sinh viên học khuya và làm việc tại nhà.
+Subheadline: Hợp với người cần một chiếc đèn dễ dùng mỗi tối, không phải setup phức tạp. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Giảm 10 phần trăm cho khách mới là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">đèn bàn LED chống chói</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Cảm xúc.
 Sản phẩm/dịch vụ: đèn bàn LED chống chói.
 Từ khóa chính: 3 mức sáng; cổ đèn linh hoạt; tiết kiệm điện.
@@ -504,36 +655,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Mô tả ngắn: đèn bàn LED chống chói dành cho sinh viên học khuya và làm việc tại nhà, nhấn vào trải nghiệm dùng rõ ràng và dễ hiểu.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. đèn bàn LED chống chói dành cho sinh viên học khuya và làm việc tại nhà trong những lúc góc bàn học khuya hoặc bàn làm việc tại nhà cần ánh sáng ổn định, không quá gắt.
 Lợi ích chính:
-- Hỗ trợ nhu cầu thực tế nhờ 3 mức sáng và cổ đèn linh hoạt.
-- Giúp bạn cân nhắc nhanh hơn với thông tin đúng brief và giảm 10 phần trăm cho khách mới.
+- Giúp bạn yên tâm hơn với nhu cầu 3 mức sáng mà không phải đọc quá nhiều thông tin rối.
+- Cổ đèn linh hoạt là điểm cộng rõ ràng khi dùng hằng ngày.
+- Tiết kiệm điện giúp sản phẩm dễ được đưa vào thói quen hiện có.
 Đặc điểm nổi bật:
-- 3 mức sáng.
-- tiết kiệm điện.
-Lời kêu gọi hành động: Xem chi tiết để chọn mẫu phù hợp.
-Phiên bản 2:
-Mô tả ngắn: Nếu bạn là sinh viên học khuya và làm việc tại nhà, đèn bàn LED chống chói là một lựa chọn gọn gàng, dễ dùng và sát nhu cầu.
+- 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện.
+- Thông tin đi kèm: giảm 10 phần trăm cho khách mới.
+Góc cần biết: Bạn nên cân nhắc diện tích bàn và thói quen đọc, viết, dùng laptop.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì ngồi lâu dễ mỏi mắt nếu đèn quá chói hoặc không chỉnh được hướng sáng, đèn bàn LED chống chói là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện.
 Lợi ích chính:
-- Mang lại cảm giác yên tâm khi xem thông tin rõ ràng.
-- Tập trung vào cổ đèn linh hoạt và tiết kiệm điện để phục vụ dùng hằng ngày.
-Đặc điểm nổi bật:
-- cổ đèn linh hoạt.
-- giảm 10 phần trăm cho khách mới.
-Lời kêu gọi hành động: Nhắn tin để được tư vấn trước khi mua.
-Phiên bản 3:
-Mô tả ngắn: đèn bàn LED chống chói giúp sinh viên học khuya và làm việc tại nhà có thêm một lựa chọn hợp lý cho nhu cầu thường ngày.
-Lợi ích chính:
-- tiết kiệm điện làm cho việc dùng tiện hơn.
-- 3 mức sáng hỗ trợ đúng mối quan tâm chính.
+- Phù hợp với sinh viên học khuya và làm việc tại nhà muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi giảm 10 phần trăm cho khách mới giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
 Đặc điểm nổi bật:
 - 3 mức sáng.
 - cổ đèn linh hoạt.
-Lời kêu gọi hành động: Lưu lại để so sánh khi cần.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+- tiết kiệm điện.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: đèn bàn LED chống chói hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người cần một chiếc đèn dễ dùng mỗi tối, không phải setup phức tạp.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện.
+- Ghi chú thêm để cân nhắc: giảm 10 phần trăm cho khách mới.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emotional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">đèn bàn LED chống chói</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: đèn bàn LED chống chói.
 Từ khóa chính: 3 mức sáng; cổ đèn linh hoạt; tiết kiệm điện.
@@ -557,7 +727,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. đèn bàn LED chống chói dành cho sinh viên học khuya và làm việc tại nhà trong những lúc góc bàn học khuya hoặc bàn làm việc tại nhà cần ánh sáng ổn định, không quá gắt.
+Lợi ích chính:
+- Giúp bạn yên tâm hơn với nhu cầu 3 mức sáng mà không phải đọc quá nhiều thông tin rối.
+- Cổ đèn linh hoạt là điểm cộng rõ ràng khi dùng hằng ngày.
+- Tiết kiệm điện giúp sản phẩm dễ được đưa vào thói quen hiện có.
+Đặc điểm nổi bật:
+- 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện.
+- Thông tin đi kèm: giảm 10 phần trăm cho khách mới.
+Góc cần biết: Bạn nên cân nhắc diện tích bàn và thói quen đọc, viết, dùng laptop.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì ngồi lâu dễ mỏi mắt nếu đèn quá chói hoặc không chỉnh được hướng sáng, đèn bàn LED chống chói là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện.
+Lợi ích chính:
+- Phù hợp với sinh viên học khuya và làm việc tại nhà muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi giảm 10 phần trăm cho khách mới giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
+Đặc điểm nổi bật:
+- 3 mức sáng.
+- cổ đèn linh hoạt.
+- tiết kiệm điện.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: đèn bàn LED chống chói hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người cần một chiếc đèn dễ dùng mỗi tối, không phải setup phức tạp.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện.
+- Ghi chú thêm để cân nhắc: giảm 10 phần trăm cho khách mới.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">đèn bàn LED chống chói</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Thân thiện.
 Sản phẩm/dịch vụ: đèn bàn LED chống chói.
 Từ khóa chính: 3 mức sáng; cổ đèn linh hoạt; tiết kiệm điện.
@@ -581,24 +799,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Một lựa chọn thân thiện cho sinh viên học khuya và làm việc tại nhà.
-Caption: đèn bàn LED chống chói giúp việc hằng ngày nhẹ hơn nhờ 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện. Hiện có giảm 10 phần trăm cho khách mới, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #DenBanLED #SinhVienHoc #3MucSang
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của sinh viên học khuya và làm việc tại nhà.
-Caption: Với cổ đèn linh hoạt và tiết kiệm điện, đèn bàn LED chống chói cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. giảm 10 phần trăm cho khách mới là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #DenBanLED #CoDenLinh #MuaSamThongMinh
-Phiên bản 3:
-Hook: Gợi ý dễ dùng cho sinh viên học khuya và làm việc tại nhà một lựa chọn gọn gàng hơn.
-Caption: Khi xem đèn bàn LED chống chói, hãy chú ý vào 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #DenBanLED #TietKiemDien #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Một món nhỏ, nhưng dùng đúng lúc thì thấy ngày nhẹ hơn một chút.
+Caption: đèn bàn LED chống chói dành cho sinh viên học khuya và làm việc tại nhà trong những lúc góc bàn học khuya hoặc bàn làm việc tại nhà cần ánh sáng ổn định, không quá gắt. Mình sẽ nhìn vào 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện trước, rồi mới xét đến ưu đãi giảm 10 phần trăm cho khách mới. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên cân nhắc diện tích bàn và thói quen đọc, viết, dùng laptop.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #DenBanLED #GocHocTap #LamViecTaiNha
+Phiên bản 2:
+Hook: Mua sắm dễ chịu hơn khi thông tin đủ rõ và không bị thúc ép.
+Caption: Nếu bạn từng gặp chuyện ngồi lâu dễ mỏi mắt nếu đèn quá chói hoặc không chỉnh được hướng sáng, đèn bàn LED chống chói là một lựa chọn đáng để lưu lại. Sản phẩm có 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Giảm 10 phần trăm cho khách mới là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #DenBanLED #GocHocTap #LamViecTaiNha
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với đèn bàn LED chống chói, hãy bắt đầu từ nhu cầu của sinh viên học khuya và làm việc tại nhà: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người cần một chiếc đèn dễ dùng mỗi tối, không phải setup phức tạp.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #DenBanLED #GocHocTap #LamViecTaiNha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">đèn bàn LED chống chói</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Khẩn cấp.
 Sản phẩm/dịch vụ: đèn bàn LED chống chói.
 Từ khóa chính: 3 mức sáng; cổ đèn linh hoạt; tiết kiệm điện.
@@ -622,24 +855,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Cần xem ngay cho sinh viên học khuya và làm việc tại nhà.
-Caption: đèn bàn LED chống chói giúp việc hằng ngày nhẹ hơn nhờ 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện. Hiện có giảm 10 phần trăm cho khách mới, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #DenBanLED #SinhVienHoc #3MucSang
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của sinh viên học khuya và làm việc tại nhà.
-Caption: Với cổ đèn linh hoạt và tiết kiệm điện, đèn bàn LED chống chói cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. giảm 10 phần trăm cho khách mới là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #DenBanLED #CoDenLinh #MuaSamThongMinh
-Phiên bản 3:
-Hook: Đừng chần chừ với sinh viên học khuya và làm việc tại nhà một lựa chọn gọn gàng hơn.
-Caption: Khi xem đèn bàn LED chống chói, hãy chú ý vào 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #DenBanLED #TietKiemDien #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Đang cân nhắc thì nên xem kỹ hôm nay, nhưng không cần mua vội.
+Caption: đèn bàn LED chống chói dành cho sinh viên học khuya và làm việc tại nhà trong những lúc góc bàn học khuya hoặc bàn làm việc tại nhà cần ánh sáng ổn định, không quá gắt. Mình sẽ nhìn vào 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện trước, rồi mới xét đến ưu đãi giảm 10 phần trăm cho khách mới. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên cân nhắc diện tích bàn và thói quen đọc, viết, dùng laptop.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #DenBanLED #GocHocTap #LamViecTaiNha
+Phiên bản 2:
+Hook: Ưu đãi chỉ đáng giữ lại khi sản phẩm thật sự hợp với cách bạn dùng.
+Caption: Nếu bạn từng gặp chuyện ngồi lâu dễ mỏi mắt nếu đèn quá chói hoặc không chỉnh được hướng sáng, đèn bàn LED chống chói là một lựa chọn đáng để lưu lại. Sản phẩm có 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Giảm 10 phần trăm cho khách mới là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #DenBanLED #GocHocTap #LamViecTaiNha
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với đèn bàn LED chống chói, hãy bắt đầu từ nhu cầu của sinh viên học khuya và làm việc tại nhà: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người cần một chiếc đèn dễ dùng mỗi tối, không phải setup phức tạp.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #DenBanLED #GocHocTap #LamViecTaiNha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">đèn bàn LED chống chói</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Email Marketing với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: đèn bàn LED chống chói.
 Từ khóa chính: 3 mức sáng; cổ đèn linh hoạt; tiết kiệm điện.
@@ -664,27 +912,45 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Subject: Gợi ý đèn bàn LED chống chói cho sinh viên học khuya và làm việc tại nhà
-Preview text: Tóm tắt nhanh các điểm đáng cân nhắc trước khi chọn mua.
+    <t xml:space="preserve">Phiên bản 1:
+Subject: Gợi ý đèn bàn LED chống chói cho nhu cầu dùng hằng ngày
+Preview text: Một vài điểm đáng xem trước khi bạn quyết định.
 Lời chào: Chào bạn,
-Nội dung chính: Nếu bạn đang tìm một lựa chọn phù hợp cho nhu cầu hằng ngày, đèn bàn LED chống chói có các điểm nổi bật như 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện. Hiện có giảm 10 phần trăm cho khách mới, nên bạn có thể xem thêm thông tin trước khi quyết định.
-Lời kêu gọi hành động: Xem chi tiết sản phẩm hôm nay.
-Phiên bản 2:
-Subject: đèn bàn LED chống chói có thể hợp với nhu cầu của bạn
-Preview text: Một vài lý do để sinh viên học khuya và làm việc tại nhà cân nhắc sản phẩm này.
+Nội dung chính: Nếu bạn là sinh viên học khuya và làm việc tại nhà, có lẽ điều bạn cần không phải một lời giới thiệu quá mạnh. Bạn cần biết đèn bàn LED chống chói có hợp với bối cảnh góc bàn học khuya hoặc bàn làm việc tại nhà cần ánh sáng ổn định, không quá gắt hay không.
+Sản phẩm này đáng xem nhờ 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện. Trong đó, 3 mức sáng giúp xử lý nhu cầu chính; cổ đèn linh hoạt và tiết kiệm điện làm trải nghiệm dùng trọn vẹn hơn.
+Góc cần biết: Bạn nên cân nhắc diện tích bàn và thói quen đọc, viết, dùng laptop. Hiện có giảm 10 phần trăm cho khách mới, bạn có thể xem như một điểm cộng nếu sản phẩm đã đúng nhu cầu.
+Lời kêu gọi hành động: Mở chi tiết sản phẩm hoặc nhắn shop để được tư vấn kỹ hơn.
+Phiên bản 2:
+Subject: Trước khi mua đèn bàn LED chống chói, bạn có thể xem nhanh điểm này
+Preview text: Chọn chắc hơn khi biết sản phẩm giải quyết đúng việc gì.
 Lời chào: Chào bạn,
-Nội dung chính: đèn bàn LED chống chói tập trung vào cổ đèn linh hoạt, 3 mức sáng và tiết kiệm điện. Thông tin được viết theo đúng brief, không thêm chứng nhận hay số liệu ngoài phạm vi. giảm 10 phần trăm cho khách mới giúp bạn có thêm lý do so sánh.
-Lời kêu gọi hành động: Nhắn lại để được tư vấn lựa chọn phù hợp.
-Phiên bản 3:
-Subject: Xem nhanh đèn bàn LED chống chói trước khi bạn chọn
-Preview text: Thông tin ngắn gọn, dễ so sánh và có ưu đãi đi kèm.
+Nội dung chính: Nhiều người phân vân vì ngồi lâu dễ mỏi mắt nếu đèn quá chói hoặc không chỉnh được hướng sáng. Vì vậy, với đèn bàn LED chống chói, hãy nhìn vào nhu cầu thật trước: bạn cần 3 mức sáng, muốn cổ đèn linh hoạt, hay quan tâm nhiều hơn đến tiết kiệm điện?
+Nếu câu trả lời khớp với cách bạn dùng hằng ngày, đây là lựa chọn đáng cân nhắc. Nếu chưa chắc, bạn có thể hỏi shop trước khi đặt.
+Góc cần biết: Giảm 10 phần trăm cho khách mới đang đi kèm, nhưng quyết định cuối cùng vẫn nên dựa trên mức độ phù hợp.
+Lời kêu gọi hành động: Trả lời tin nhắn này với nhu cầu của bạn, shop sẽ gợi ý cụ thể hơn.
+Phiên bản 3:
+Subject: đèn bàn LED chống chói có thể là món bạn đang tìm
+Preview text: Rõ lợi ích, rõ tình huống dùng, không cần quyết định vội.
 Lời chào: Chào bạn,
-Nội dung chính: Với sinh viên học khuya và làm việc tại nhà, một sản phẩm dễ hiểu thường giúp quyết định nhanh hơn. đèn bàn LED chống chói có 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện; ngoài ra còn có giảm 10 phần trăm cho khách mới để bạn cân nhắc thêm.
-Lời kêu gọi hành động: Mở trang sản phẩm để xem thêm chi tiết.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Nội dung chính: Hợp với người cần một chiếc đèn dễ dùng mỗi tối, không phải setup phức tạp. đèn bàn LED chống chói tập trung vào 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện, phù hợp với sinh viên học khuya và làm việc tại nhà khi muốn một lựa chọn thực tế hơn cho sinh hoạt hằng ngày.
+Bạn có thể cân nhắc sản phẩm này nếu đang cần giải quyết chuyện ngồi lâu dễ mỏi mắt nếu đèn quá chói hoặc không chỉnh được hướng sáng. Còn nếu muốn chắc hơn, hãy hỏi shop về tình huống dùng của bạn.
+Góc cần biết: Bạn nên cân nhắc diện tích bàn và thói quen đọc, viết, dùng laptop.
+Lời kêu gọi hành động: Xem chi tiết hoặc nhắn shop trước khi chốt đơn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">đèn bàn LED chống chói</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Lời Kêu Gọi Hành Động với tone Thân thiện.
 Sản phẩm/dịch vụ: đèn bàn LED chống chói.
 Từ khóa chính: 3 mức sáng; cổ đèn linh hoạt; tiết kiệm điện.
@@ -706,18 +972,30 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Lời kêu gọi hành động chính: Mua đèn bàn LED chống chói ngay hôm nay
-Microcopy: Phù hợp cho sinh viên học khuya và làm việc tại nhà, có giảm 10 phần trăm cho khách mới và thông tin rõ ràng để bạn chọn nhanh.
-Phiên bản 2:
-Lời kêu gọi hành động chính: Chọn đèn bàn LED chống chói cho nhu cầu hiện tại
-Microcopy: Tập trung vào 3 mức sáng và cổ đèn linh hoạt, giúp bạn quyết định dễ hơn.
-Phiên bản 3:
-Lời kêu gọi hành động chính: Nhắn shop để được tư vấn đèn bàn LED chống chói
-Microcopy: Bạn có thể hỏi thêm về tiết kiệm điện và giảm 10 phần trăm cho khách mới trước khi quyết định.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Lời kêu gọi hành động chính: Xem đèn bàn LED chống chói có hợp với bạn không
+Microcopy: Dành cho sinh viên học khuya và làm việc tại nhà, nổi bật với 3 mức sáng, cổ đèn linh hoạt và tiết kiệm điện. Có giảm 10 phần trăm cho khách mới nếu bạn muốn cân nhắc thêm.
+Phiên bản 2:
+Lời kêu gọi hành động chính: Nhắn shop để chọn đèn bàn LED chống chói đúng nhu cầu
+Microcopy: Kể nhanh bạn dùng trong bối cảnh nào, shop sẽ gợi ý theo tình huống thật như góc bàn học khuya hoặc bàn làm việc tại nhà cần ánh sáng ổn định, không quá gắt.
+Phiên bản 3:
+Lời kêu gọi hành động chính: Lưu đèn bàn LED chống chói để so sánh trước khi mua
+Microcopy: Phù hợp hơn khi bạn muốn giải quyết chuyện ngồi lâu dễ mỏi mắt nếu đèn quá chói hoặc không chỉnh được hướng sáng mà vẫn cần một lựa chọn rõ ràng, dễ hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">đèn bàn LED chống chói</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Khẩn cấp.
 Sản phẩm/dịch vụ: bộ chăm sóc da tối giản.
 Từ khóa chính: 3 bước dễ theo; kết cấu nhẹ; phù hợp dùng hằng ngày.
@@ -740,24 +1018,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Đừng chần chừ với bộ chăm sóc da tối giản cho người mới bắt đầu skincare với 3 bước dễ theo.
-Subheadline: Tập trung vào kết cấu nhẹ và phù hợp dùng hằng ngày, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: bộ chăm sóc da tối giản là lựa chọn đáng cân nhắc cho người mới bắt đầu skincare.
-Subheadline: Điểm mạnh nằm ở kết cấu nhẹ, 3 bước dễ theo và tặng túi du lịch mini để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Giữ nhịp nhanh hơn cho bộ chăm sóc da tối giản nếu bạn cần 3 bước dễ theo và kết cấu nhẹ.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>bộ chăm sóc da tối giản</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: bộ chăm sóc da tối giản: gọn hơn cho những lúc 3 bước dễ theo thật sự quan trọng.
+Subheadline: Dành cho người mới bắt đầu skincare, nhất là khi buổi tối sau ngày dài, người mới skincare thường chỉ muốn vài bước rõ ràng và dễ duy trì. Điểm đáng xem là 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên thử từ tần suất phù hợp và đọc kỹ phản ứng của da.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với bộ chăm sóc da tối giản.
+Subheadline: Nếu bạn từng ngại chuyện sợ mua quá nhiều món rồi không biết dùng theo thứ tự nào, hãy bắt đầu từ ba điểm: 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày. Ưu đãi hiện có: tặng túi du lịch mini.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn bộ chăm sóc da tối giản vừa đủ thực tế cho người mới bắt đầu skincare.
+Subheadline: Hợp với người muốn bắt đầu nhẹ nhàng, hiểu làn da trước khi thêm nhiều sản phẩm khác. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Tặng túi du lịch mini là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bộ chăm sóc da tối giản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
 Sản phẩm/dịch vụ: bộ chăm sóc da tối giản.
 Từ khóa chính: 3 bước dễ theo; kết cấu nhẹ; phù hợp dùng hằng ngày.
@@ -780,21 +1070,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Gợi ý dễ dùng cho bộ chăm sóc da tối giản cho người mới bắt đầu skincare với 3 bước dễ theo.
-Subheadline: Tập trung vào kết cấu nhẹ và phù hợp dùng hằng ngày, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: bộ chăm sóc da tối giản là lựa chọn đáng cân nhắc cho người mới bắt đầu skincare.
-Subheadline: Điểm mạnh nằm ở kết cấu nhẹ, 3 bước dễ theo và tặng túi du lịch mini để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Thêm tiện lợi cho bộ chăm sóc da tối giản nếu bạn cần 3 bước dễ theo và kết cấu nhẹ.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: bộ chăm sóc da tối giản: gọn hơn cho những lúc 3 bước dễ theo thật sự quan trọng.
+Subheadline: Dành cho người mới bắt đầu skincare, nhất là khi buổi tối sau ngày dài, người mới skincare thường chỉ muốn vài bước rõ ràng và dễ duy trì. Điểm đáng xem là 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên thử từ tần suất phù hợp và đọc kỹ phản ứng của da.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với bộ chăm sóc da tối giản.
+Subheadline: Nếu bạn từng ngại chuyện sợ mua quá nhiều món rồi không biết dùng theo thứ tự nào, hãy bắt đầu từ ba điểm: 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày. Ưu đãi hiện có: tặng túi du lịch mini.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn bộ chăm sóc da tối giản vừa đủ thực tế cho người mới bắt đầu skincare.
+Subheadline: Hợp với người muốn bắt đầu nhẹ nhàng, hiểu làn da trước khi thêm nhiều sản phẩm khác. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Tặng túi du lịch mini là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bộ chăm sóc da tối giản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Cảm xúc.
 Sản phẩm/dịch vụ: bộ chăm sóc da tối giản.
 Từ khóa chính: 3 bước dễ theo; kết cấu nhẹ; phù hợp dùng hằng ngày.
@@ -818,36 +1123,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Mô tả ngắn: bộ chăm sóc da tối giản dành cho người mới bắt đầu skincare, nhấn vào trải nghiệm dùng rõ ràng và dễ hiểu.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. bộ chăm sóc da tối giản dành cho người mới bắt đầu skincare trong những lúc buổi tối sau ngày dài, người mới skincare thường chỉ muốn vài bước rõ ràng và dễ duy trì.
 Lợi ích chính:
-- Hỗ trợ nhu cầu thực tế nhờ 3 bước dễ theo và kết cấu nhẹ.
-- Giúp bạn cân nhắc nhanh hơn với thông tin đúng brief và tặng túi du lịch mini.
+- Giúp bạn yên tâm hơn với nhu cầu 3 bước dễ theo mà không phải đọc quá nhiều thông tin rối.
+- Kết cấu nhẹ là điểm cộng rõ ràng khi dùng hằng ngày.
+- Phù hợp dùng hằng ngày giúp sản phẩm dễ được đưa vào thói quen hiện có.
 Đặc điểm nổi bật:
-- 3 bước dễ theo.
-- phù hợp dùng hằng ngày.
-Lời kêu gọi hành động: Xem chi tiết để chọn mẫu phù hợp.
-Phiên bản 2:
-Mô tả ngắn: Nếu bạn là người mới bắt đầu skincare, bộ chăm sóc da tối giản là một lựa chọn gọn gàng, dễ dùng và sát nhu cầu.
+- 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày.
+- Thông tin đi kèm: tặng túi du lịch mini.
+Góc cần biết: Bạn nên thử từ tần suất phù hợp và đọc kỹ phản ứng của da.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì sợ mua quá nhiều món rồi không biết dùng theo thứ tự nào, bộ chăm sóc da tối giản là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày.
 Lợi ích chính:
-- Mang lại cảm giác yên tâm khi xem thông tin rõ ràng.
-- Tập trung vào kết cấu nhẹ và phù hợp dùng hằng ngày để phục vụ dùng hằng ngày.
-Đặc điểm nổi bật:
-- kết cấu nhẹ.
-- tặng túi du lịch mini.
-Lời kêu gọi hành động: Nhắn tin để được tư vấn trước khi mua.
-Phiên bản 3:
-Mô tả ngắn: bộ chăm sóc da tối giản giúp người mới bắt đầu skincare có thêm một lựa chọn hợp lý cho nhu cầu thường ngày.
-Lợi ích chính:
-- phù hợp dùng hằng ngày làm cho việc dùng tiện hơn.
-- 3 bước dễ theo hỗ trợ đúng mối quan tâm chính.
+- Phù hợp với người mới bắt đầu skincare muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi tặng túi du lịch mini giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
 Đặc điểm nổi bật:
 - 3 bước dễ theo.
 - kết cấu nhẹ.
-Lời kêu gọi hành động: Lưu lại để so sánh khi cần.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+- phù hợp dùng hằng ngày.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: bộ chăm sóc da tối giản hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người muốn bắt đầu nhẹ nhàng, hiểu làn da trước khi thêm nhiều sản phẩm khác.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày.
+- Ghi chú thêm để cân nhắc: tặng túi du lịch mini.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emotional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bộ chăm sóc da tối giản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: bộ chăm sóc da tối giản.
 Từ khóa chính: 3 bước dễ theo; kết cấu nhẹ; phù hợp dùng hằng ngày.
@@ -871,7 +1195,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. bộ chăm sóc da tối giản dành cho người mới bắt đầu skincare trong những lúc buổi tối sau ngày dài, người mới skincare thường chỉ muốn vài bước rõ ràng và dễ duy trì.
+Lợi ích chính:
+- Giúp bạn yên tâm hơn với nhu cầu 3 bước dễ theo mà không phải đọc quá nhiều thông tin rối.
+- Kết cấu nhẹ là điểm cộng rõ ràng khi dùng hằng ngày.
+- Phù hợp dùng hằng ngày giúp sản phẩm dễ được đưa vào thói quen hiện có.
+Đặc điểm nổi bật:
+- 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày.
+- Thông tin đi kèm: tặng túi du lịch mini.
+Góc cần biết: Bạn nên thử từ tần suất phù hợp và đọc kỹ phản ứng của da.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì sợ mua quá nhiều món rồi không biết dùng theo thứ tự nào, bộ chăm sóc da tối giản là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày.
+Lợi ích chính:
+- Phù hợp với người mới bắt đầu skincare muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi tặng túi du lịch mini giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
+Đặc điểm nổi bật:
+- 3 bước dễ theo.
+- kết cấu nhẹ.
+- phù hợp dùng hằng ngày.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: bộ chăm sóc da tối giản hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người muốn bắt đầu nhẹ nhàng, hiểu làn da trước khi thêm nhiều sản phẩm khác.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày.
+- Ghi chú thêm để cân nhắc: tặng túi du lịch mini.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bộ chăm sóc da tối giản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Thân thiện.
 Sản phẩm/dịch vụ: bộ chăm sóc da tối giản.
 Từ khóa chính: 3 bước dễ theo; kết cấu nhẹ; phù hợp dùng hằng ngày.
@@ -895,24 +1267,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Một lựa chọn thân thiện cho người mới bắt đầu skincare.
-Caption: bộ chăm sóc da tối giản giúp việc hằng ngày nhẹ hơn nhờ 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày. Hiện có tặng túi du lịch mini, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #BoChamSoc #NguoiMoiBat #3BuocDe
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của người mới bắt đầu skincare.
-Caption: Với kết cấu nhẹ và phù hợp dùng hằng ngày, bộ chăm sóc da tối giản cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. tặng túi du lịch mini là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #BoChamSoc #KetCauNhe #MuaSamThongMinh
-Phiên bản 3:
-Hook: Gợi ý dễ dùng cho người mới bắt đầu skincare một lựa chọn gọn gàng hơn.
-Caption: Khi xem bộ chăm sóc da tối giản, hãy chú ý vào 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #BoChamSoc #PhuHopDung #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Một món nhỏ, nhưng dùng đúng lúc thì thấy ngày nhẹ hơn một chút.
+Caption: bộ chăm sóc da tối giản dành cho người mới bắt đầu skincare trong những lúc buổi tối sau ngày dài, người mới skincare thường chỉ muốn vài bước rõ ràng và dễ duy trì. Mình sẽ nhìn vào 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày trước, rồi mới xét đến ưu đãi tặng túi du lịch mini. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên thử từ tần suất phù hợp và đọc kỹ phản ứng của da.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #SkincareToiGian #ChamSocDa #NguoiMoiBatDau
+Phiên bản 2:
+Hook: Mua sắm dễ chịu hơn khi thông tin đủ rõ và không bị thúc ép.
+Caption: Nếu bạn từng gặp chuyện sợ mua quá nhiều món rồi không biết dùng theo thứ tự nào, bộ chăm sóc da tối giản là một lựa chọn đáng để lưu lại. Sản phẩm có 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Tặng túi du lịch mini là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #SkincareToiGian #ChamSocDa #NguoiMoiBatDau
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với bộ chăm sóc da tối giản, hãy bắt đầu từ nhu cầu của người mới bắt đầu skincare: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người muốn bắt đầu nhẹ nhàng, hiểu làn da trước khi thêm nhiều sản phẩm khác.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #SkincareToiGian #ChamSocDa #NguoiMoiBatDau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bộ chăm sóc da tối giản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Khẩn cấp.
 Sản phẩm/dịch vụ: bộ chăm sóc da tối giản.
 Từ khóa chính: 3 bước dễ theo; kết cấu nhẹ; phù hợp dùng hằng ngày.
@@ -936,24 +1323,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Cần xem ngay cho người mới bắt đầu skincare.
-Caption: bộ chăm sóc da tối giản giúp việc hằng ngày nhẹ hơn nhờ 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày. Hiện có tặng túi du lịch mini, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #BoChamSoc #NguoiMoiBat #3BuocDe
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của người mới bắt đầu skincare.
-Caption: Với kết cấu nhẹ và phù hợp dùng hằng ngày, bộ chăm sóc da tối giản cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. tặng túi du lịch mini là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #BoChamSoc #KetCauNhe #MuaSamThongMinh
-Phiên bản 3:
-Hook: Đừng chần chừ với người mới bắt đầu skincare một lựa chọn gọn gàng hơn.
-Caption: Khi xem bộ chăm sóc da tối giản, hãy chú ý vào 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #BoChamSoc #PhuHopDung #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Đang cân nhắc thì nên xem kỹ hôm nay, nhưng không cần mua vội.
+Caption: bộ chăm sóc da tối giản dành cho người mới bắt đầu skincare trong những lúc buổi tối sau ngày dài, người mới skincare thường chỉ muốn vài bước rõ ràng và dễ duy trì. Mình sẽ nhìn vào 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày trước, rồi mới xét đến ưu đãi tặng túi du lịch mini. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên thử từ tần suất phù hợp và đọc kỹ phản ứng của da.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #SkincareToiGian #ChamSocDa #NguoiMoiBatDau
+Phiên bản 2:
+Hook: Ưu đãi chỉ đáng giữ lại khi sản phẩm thật sự hợp với cách bạn dùng.
+Caption: Nếu bạn từng gặp chuyện sợ mua quá nhiều món rồi không biết dùng theo thứ tự nào, bộ chăm sóc da tối giản là một lựa chọn đáng để lưu lại. Sản phẩm có 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Tặng túi du lịch mini là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #SkincareToiGian #ChamSocDa #NguoiMoiBatDau
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với bộ chăm sóc da tối giản, hãy bắt đầu từ nhu cầu của người mới bắt đầu skincare: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người muốn bắt đầu nhẹ nhàng, hiểu làn da trước khi thêm nhiều sản phẩm khác.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #SkincareToiGian #ChamSocDa #NguoiMoiBatDau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bộ chăm sóc da tối giản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Email Marketing với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: bộ chăm sóc da tối giản.
 Từ khóa chính: 3 bước dễ theo; kết cấu nhẹ; phù hợp dùng hằng ngày.
@@ -978,27 +1380,45 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Subject: Gợi ý bộ chăm sóc da tối giản cho người mới bắt đầu skincare
-Preview text: Tóm tắt nhanh các điểm đáng cân nhắc trước khi chọn mua.
+    <t xml:space="preserve">Phiên bản 1:
+Subject: Gợi ý bộ chăm sóc da tối giản cho nhu cầu dùng hằng ngày
+Preview text: Một vài điểm đáng xem trước khi bạn quyết định.
 Lời chào: Chào bạn,
-Nội dung chính: Nếu bạn đang tìm một lựa chọn phù hợp cho nhu cầu hằng ngày, bộ chăm sóc da tối giản có các điểm nổi bật như 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày. Hiện có tặng túi du lịch mini, nên bạn có thể xem thêm thông tin trước khi quyết định.
-Lời kêu gọi hành động: Xem chi tiết sản phẩm hôm nay.
-Phiên bản 2:
-Subject: bộ chăm sóc da tối giản có thể hợp với nhu cầu của bạn
-Preview text: Một vài lý do để người mới bắt đầu skincare cân nhắc sản phẩm này.
+Nội dung chính: Nếu bạn là người mới bắt đầu skincare, có lẽ điều bạn cần không phải một lời giới thiệu quá mạnh. Bạn cần biết bộ chăm sóc da tối giản có hợp với bối cảnh buổi tối sau ngày dài, người mới skincare thường chỉ muốn vài bước rõ ràng và dễ duy trì hay không.
+Sản phẩm này đáng xem nhờ 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày. Trong đó, 3 bước dễ theo giúp xử lý nhu cầu chính; kết cấu nhẹ và phù hợp dùng hằng ngày làm trải nghiệm dùng trọn vẹn hơn.
+Góc cần biết: Bạn nên thử từ tần suất phù hợp và đọc kỹ phản ứng của da. Hiện có tặng túi du lịch mini, bạn có thể xem như một điểm cộng nếu sản phẩm đã đúng nhu cầu.
+Lời kêu gọi hành động: Mở chi tiết sản phẩm hoặc nhắn shop để được tư vấn kỹ hơn.
+Phiên bản 2:
+Subject: Trước khi mua bộ chăm sóc da tối giản, bạn có thể xem nhanh điểm này
+Preview text: Chọn chắc hơn khi biết sản phẩm giải quyết đúng việc gì.
 Lời chào: Chào bạn,
-Nội dung chính: bộ chăm sóc da tối giản tập trung vào kết cấu nhẹ, 3 bước dễ theo và phù hợp dùng hằng ngày. Thông tin được viết theo đúng brief, không thêm chứng nhận hay số liệu ngoài phạm vi. tặng túi du lịch mini giúp bạn có thêm lý do so sánh.
-Lời kêu gọi hành động: Nhắn lại để được tư vấn lựa chọn phù hợp.
-Phiên bản 3:
-Subject: Xem nhanh bộ chăm sóc da tối giản trước khi bạn chọn
-Preview text: Thông tin ngắn gọn, dễ so sánh và có ưu đãi đi kèm.
+Nội dung chính: Nhiều người phân vân vì sợ mua quá nhiều món rồi không biết dùng theo thứ tự nào. Vì vậy, với bộ chăm sóc da tối giản, hãy nhìn vào nhu cầu thật trước: bạn cần 3 bước dễ theo, muốn kết cấu nhẹ, hay quan tâm nhiều hơn đến phù hợp dùng hằng ngày?
+Nếu câu trả lời khớp với cách bạn dùng hằng ngày, đây là lựa chọn đáng cân nhắc. Nếu chưa chắc, bạn có thể hỏi shop trước khi đặt.
+Góc cần biết: Tặng túi du lịch mini đang đi kèm, nhưng quyết định cuối cùng vẫn nên dựa trên mức độ phù hợp.
+Lời kêu gọi hành động: Trả lời tin nhắn này với nhu cầu của bạn, shop sẽ gợi ý cụ thể hơn.
+Phiên bản 3:
+Subject: bộ chăm sóc da tối giản có thể là món bạn đang tìm
+Preview text: Rõ lợi ích, rõ tình huống dùng, không cần quyết định vội.
 Lời chào: Chào bạn,
-Nội dung chính: Với người mới bắt đầu skincare, một sản phẩm dễ hiểu thường giúp quyết định nhanh hơn. bộ chăm sóc da tối giản có 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày; ngoài ra còn có tặng túi du lịch mini để bạn cân nhắc thêm.
-Lời kêu gọi hành động: Mở trang sản phẩm để xem thêm chi tiết.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Nội dung chính: Hợp với người muốn bắt đầu nhẹ nhàng, hiểu làn da trước khi thêm nhiều sản phẩm khác. bộ chăm sóc da tối giản tập trung vào 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày, phù hợp với người mới bắt đầu skincare khi muốn một lựa chọn thực tế hơn cho sinh hoạt hằng ngày.
+Bạn có thể cân nhắc sản phẩm này nếu đang cần giải quyết chuyện sợ mua quá nhiều món rồi không biết dùng theo thứ tự nào. Còn nếu muốn chắc hơn, hãy hỏi shop về tình huống dùng của bạn.
+Góc cần biết: Bạn nên thử từ tần suất phù hợp và đọc kỹ phản ứng của da.
+Lời kêu gọi hành động: Xem chi tiết hoặc nhắn shop trước khi chốt đơn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bộ chăm sóc da tối giản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Lời Kêu Gọi Hành Động với tone Thân thiện.
 Sản phẩm/dịch vụ: bộ chăm sóc da tối giản.
 Từ khóa chính: 3 bước dễ theo; kết cấu nhẹ; phù hợp dùng hằng ngày.
@@ -1020,18 +1440,30 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Lời kêu gọi hành động chính: Mua bộ chăm sóc da tối giản ngay hôm nay
-Microcopy: Phù hợp cho người mới bắt đầu skincare, có tặng túi du lịch mini và thông tin rõ ràng để bạn chọn nhanh.
-Phiên bản 2:
-Lời kêu gọi hành động chính: Chọn bộ chăm sóc da tối giản cho nhu cầu hiện tại
-Microcopy: Tập trung vào 3 bước dễ theo và kết cấu nhẹ, giúp bạn quyết định dễ hơn.
-Phiên bản 3:
-Lời kêu gọi hành động chính: Nhắn shop để được tư vấn bộ chăm sóc da tối giản
-Microcopy: Bạn có thể hỏi thêm về phù hợp dùng hằng ngày và tặng túi du lịch mini trước khi quyết định.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Lời kêu gọi hành động chính: Xem bộ chăm sóc da tối giản có hợp với bạn không
+Microcopy: Dành cho người mới bắt đầu skincare, nổi bật với 3 bước dễ theo, kết cấu nhẹ và phù hợp dùng hằng ngày. Có tặng túi du lịch mini nếu bạn muốn cân nhắc thêm.
+Phiên bản 2:
+Lời kêu gọi hành động chính: Nhắn shop để chọn bộ chăm sóc da tối giản đúng nhu cầu
+Microcopy: Kể nhanh bạn dùng trong bối cảnh nào, shop sẽ gợi ý theo tình huống thật như buổi tối sau ngày dài, người mới skincare thường chỉ muốn vài bước rõ ràng và dễ duy trì.
+Phiên bản 3:
+Lời kêu gọi hành động chính: Lưu bộ chăm sóc da tối giản để so sánh trước khi mua
+Microcopy: Phù hợp hơn khi bạn muốn giải quyết chuyện sợ mua quá nhiều món rồi không biết dùng theo thứ tự nào mà vẫn cần một lựa chọn rõ ràng, dễ hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bộ chăm sóc da tối giản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Khẩn cấp.
 Sản phẩm/dịch vụ: máy xay sinh tố mini.
 Từ khóa chính: cốc mang đi; sạc USB; lưỡi dao inox.
@@ -1054,24 +1486,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Đừng chần chừ với máy xay sinh tố mini cho người bận rộn muốn chuẩn bị đồ uống nhanh với cốc mang đi.
-Subheadline: Tập trung vào sạc USB và lưỡi dao inox, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: máy xay sinh tố mini là lựa chọn đáng cân nhắc cho người bận rộn muốn chuẩn bị đồ uống nhanh.
-Subheadline: Điểm mạnh nằm ở sạc USB, cốc mang đi và đổi mới trong 7 ngày nếu lỗi kỹ thuật để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Giữ nhịp nhanh hơn cho máy xay sinh tố mini nếu bạn cần cốc mang đi và sạc USB.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>máy xay sinh tố mini</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: máy xay sinh tố mini: gọn hơn cho những lúc cốc mang đi thật sự quan trọng.
+Subheadline: Dành cho người bận rộn muốn chuẩn bị đồ uống nhanh, nhất là khi sáng bận rộn vẫn muốn chuẩn bị một ly đồ uống nhanh trước khi ra khỏi nhà. Điểm đáng xem là cốc mang đi, sạc USB và lưỡi dao inox; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên cắt nhỏ nguyên liệu và xem kỹ hướng dẫn dùng an toàn.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với máy xay sinh tố mini.
+Subheadline: Nếu bạn từng ngại chuyện ngại máy cồng kềnh, rửa lâu hoặc phải lắp quá nhiều bộ phận, hãy bắt đầu từ ba điểm: cốc mang đi, sạc USB và lưỡi dao inox. Ưu đãi hiện có: đổi mới trong 7 ngày nếu lỗi kỹ thuật.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn máy xay sinh tố mini vừa đủ thực tế cho người bận rộn muốn chuẩn bị đồ uống nhanh.
+Subheadline: Hợp với người thích đồ uống tự chuẩn bị nhưng không có nhiều thời gian. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Đổi mới trong 7 ngày nếu lỗi kỹ thuật là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">máy xay sinh tố mini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
 Sản phẩm/dịch vụ: máy xay sinh tố mini.
 Từ khóa chính: cốc mang đi; sạc USB; lưỡi dao inox.
@@ -1094,21 +1538,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Gợi ý dễ dùng cho máy xay sinh tố mini cho người bận rộn muốn chuẩn bị đồ uống nhanh với cốc mang đi.
-Subheadline: Tập trung vào sạc USB và lưỡi dao inox, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: máy xay sinh tố mini là lựa chọn đáng cân nhắc cho người bận rộn muốn chuẩn bị đồ uống nhanh.
-Subheadline: Điểm mạnh nằm ở sạc USB, cốc mang đi và đổi mới trong 7 ngày nếu lỗi kỹ thuật để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Thêm tiện lợi cho máy xay sinh tố mini nếu bạn cần cốc mang đi và sạc USB.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: máy xay sinh tố mini: gọn hơn cho những lúc cốc mang đi thật sự quan trọng.
+Subheadline: Dành cho người bận rộn muốn chuẩn bị đồ uống nhanh, nhất là khi sáng bận rộn vẫn muốn chuẩn bị một ly đồ uống nhanh trước khi ra khỏi nhà. Điểm đáng xem là cốc mang đi, sạc USB và lưỡi dao inox; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên cắt nhỏ nguyên liệu và xem kỹ hướng dẫn dùng an toàn.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với máy xay sinh tố mini.
+Subheadline: Nếu bạn từng ngại chuyện ngại máy cồng kềnh, rửa lâu hoặc phải lắp quá nhiều bộ phận, hãy bắt đầu từ ba điểm: cốc mang đi, sạc USB và lưỡi dao inox. Ưu đãi hiện có: đổi mới trong 7 ngày nếu lỗi kỹ thuật.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn máy xay sinh tố mini vừa đủ thực tế cho người bận rộn muốn chuẩn bị đồ uống nhanh.
+Subheadline: Hợp với người thích đồ uống tự chuẩn bị nhưng không có nhiều thời gian. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Đổi mới trong 7 ngày nếu lỗi kỹ thuật là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">máy xay sinh tố mini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Cảm xúc.
 Sản phẩm/dịch vụ: máy xay sinh tố mini.
 Từ khóa chính: cốc mang đi; sạc USB; lưỡi dao inox.
@@ -1132,36 +1591,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Mô tả ngắn: máy xay sinh tố mini dành cho người bận rộn muốn chuẩn bị đồ uống nhanh, nhấn vào trải nghiệm dùng rõ ràng và dễ hiểu.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. máy xay sinh tố mini dành cho người bận rộn muốn chuẩn bị đồ uống nhanh trong những lúc sáng bận rộn vẫn muốn chuẩn bị một ly đồ uống nhanh trước khi ra khỏi nhà.
 Lợi ích chính:
-- Hỗ trợ nhu cầu thực tế nhờ cốc mang đi và sạc USB.
-- Giúp bạn cân nhắc nhanh hơn với thông tin đúng brief và đổi mới trong 7 ngày nếu lỗi kỹ thuật.
+- Giúp bạn yên tâm hơn với nhu cầu cốc mang đi mà không phải đọc quá nhiều thông tin rối.
+- Sạc usb là điểm cộng rõ ràng khi dùng hằng ngày.
+- Lưỡi dao inox giúp sản phẩm dễ được đưa vào thói quen hiện có.
 Đặc điểm nổi bật:
-- cốc mang đi.
-- lưỡi dao inox.
-Lời kêu gọi hành động: Xem chi tiết để chọn mẫu phù hợp.
-Phiên bản 2:
-Mô tả ngắn: Nếu bạn là người bận rộn muốn chuẩn bị đồ uống nhanh, máy xay sinh tố mini là một lựa chọn gọn gàng, dễ dùng và sát nhu cầu.
+- cốc mang đi, sạc USB và lưỡi dao inox.
+- Thông tin đi kèm: đổi mới trong 7 ngày nếu lỗi kỹ thuật.
+Góc cần biết: Bạn nên cắt nhỏ nguyên liệu và xem kỹ hướng dẫn dùng an toàn.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì ngại máy cồng kềnh, rửa lâu hoặc phải lắp quá nhiều bộ phận, máy xay sinh tố mini là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: cốc mang đi, sạc USB và lưỡi dao inox.
 Lợi ích chính:
-- Mang lại cảm giác yên tâm khi xem thông tin rõ ràng.
-- Tập trung vào sạc USB và lưỡi dao inox để phục vụ dùng hằng ngày.
-Đặc điểm nổi bật:
-- sạc USB.
-- đổi mới trong 7 ngày nếu lỗi kỹ thuật.
-Lời kêu gọi hành động: Nhắn tin để được tư vấn trước khi mua.
-Phiên bản 3:
-Mô tả ngắn: máy xay sinh tố mini giúp người bận rộn muốn chuẩn bị đồ uống nhanh có thêm một lựa chọn hợp lý cho nhu cầu thường ngày.
-Lợi ích chính:
-- lưỡi dao inox làm cho việc dùng tiện hơn.
-- cốc mang đi hỗ trợ đúng mối quan tâm chính.
+- Phù hợp với người bận rộn muốn chuẩn bị đồ uống nhanh muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi đổi mới trong 7 ngày nếu lỗi kỹ thuật giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
 Đặc điểm nổi bật:
 - cốc mang đi.
 - sạc USB.
-Lời kêu gọi hành động: Lưu lại để so sánh khi cần.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+- lưỡi dao inox.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: máy xay sinh tố mini hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người thích đồ uống tự chuẩn bị nhưng không có nhiều thời gian.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin cốc mang đi, sạc USB và lưỡi dao inox.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: cốc mang đi, sạc USB và lưỡi dao inox.
+- Ghi chú thêm để cân nhắc: đổi mới trong 7 ngày nếu lỗi kỹ thuật.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emotional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">máy xay sinh tố mini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: máy xay sinh tố mini.
 Từ khóa chính: cốc mang đi; sạc USB; lưỡi dao inox.
@@ -1185,7 +1663,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. máy xay sinh tố mini dành cho người bận rộn muốn chuẩn bị đồ uống nhanh trong những lúc sáng bận rộn vẫn muốn chuẩn bị một ly đồ uống nhanh trước khi ra khỏi nhà.
+Lợi ích chính:
+- Giúp bạn yên tâm hơn với nhu cầu cốc mang đi mà không phải đọc quá nhiều thông tin rối.
+- Sạc usb là điểm cộng rõ ràng khi dùng hằng ngày.
+- Lưỡi dao inox giúp sản phẩm dễ được đưa vào thói quen hiện có.
+Đặc điểm nổi bật:
+- cốc mang đi, sạc USB và lưỡi dao inox.
+- Thông tin đi kèm: đổi mới trong 7 ngày nếu lỗi kỹ thuật.
+Góc cần biết: Bạn nên cắt nhỏ nguyên liệu và xem kỹ hướng dẫn dùng an toàn.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì ngại máy cồng kềnh, rửa lâu hoặc phải lắp quá nhiều bộ phận, máy xay sinh tố mini là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: cốc mang đi, sạc USB và lưỡi dao inox.
+Lợi ích chính:
+- Phù hợp với người bận rộn muốn chuẩn bị đồ uống nhanh muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi đổi mới trong 7 ngày nếu lỗi kỹ thuật giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
+Đặc điểm nổi bật:
+- cốc mang đi.
+- sạc USB.
+- lưỡi dao inox.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: máy xay sinh tố mini hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người thích đồ uống tự chuẩn bị nhưng không có nhiều thời gian.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin cốc mang đi, sạc USB và lưỡi dao inox.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: cốc mang đi, sạc USB và lưỡi dao inox.
+- Ghi chú thêm để cân nhắc: đổi mới trong 7 ngày nếu lỗi kỹ thuật.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">máy xay sinh tố mini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Thân thiện.
 Sản phẩm/dịch vụ: máy xay sinh tố mini.
 Từ khóa chính: cốc mang đi; sạc USB; lưỡi dao inox.
@@ -1209,24 +1735,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Một lựa chọn thân thiện cho người bận rộn muốn chuẩn bị đồ uống nhanh.
-Caption: máy xay sinh tố mini giúp việc hằng ngày nhẹ hơn nhờ cốc mang đi, sạc USB và lưỡi dao inox. Hiện có đổi mới trong 7 ngày nếu lỗi kỹ thuật, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #MayXaySinh #NguoiBanRon #CocMangDi
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của người bận rộn muốn chuẩn bị đồ uống nhanh.
-Caption: Với sạc USB và lưỡi dao inox, máy xay sinh tố mini cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. đổi mới trong 7 ngày nếu lỗi kỹ thuật là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #MayXaySinh #SacUSB #MuaSamThongMinh
-Phiên bản 3:
-Hook: Gợi ý dễ dùng cho người bận rộn muốn chuẩn bị đồ uống nhanh một lựa chọn gọn gàng hơn.
-Caption: Khi xem máy xay sinh tố mini, hãy chú ý vào cốc mang đi, sạc USB và lưỡi dao inox. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #MayXaySinh #LuoiDaoInox #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Một món nhỏ, nhưng dùng đúng lúc thì thấy ngày nhẹ hơn một chút.
+Caption: máy xay sinh tố mini dành cho người bận rộn muốn chuẩn bị đồ uống nhanh trong những lúc sáng bận rộn vẫn muốn chuẩn bị một ly đồ uống nhanh trước khi ra khỏi nhà. Mình sẽ nhìn vào cốc mang đi, sạc USB và lưỡi dao inox trước, rồi mới xét đến ưu đãi đổi mới trong 7 ngày nếu lỗi kỹ thuật. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên cắt nhỏ nguyên liệu và xem kỹ hướng dẫn dùng an toàn.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #MayXayMini #SinhToNhanh #BepGon
+Phiên bản 2:
+Hook: Mua sắm dễ chịu hơn khi thông tin đủ rõ và không bị thúc ép.
+Caption: Nếu bạn từng gặp chuyện ngại máy cồng kềnh, rửa lâu hoặc phải lắp quá nhiều bộ phận, máy xay sinh tố mini là một lựa chọn đáng để lưu lại. Sản phẩm có cốc mang đi, sạc USB và lưỡi dao inox, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Đổi mới trong 7 ngày nếu lỗi kỹ thuật là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #MayXayMini #SinhToNhanh #BepGon
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với máy xay sinh tố mini, hãy bắt đầu từ nhu cầu của người bận rộn muốn chuẩn bị đồ uống nhanh: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm cốc mang đi, sạc USB và lưỡi dao inox khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người thích đồ uống tự chuẩn bị nhưng không có nhiều thời gian.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #MayXayMini #SinhToNhanh #BepGon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">máy xay sinh tố mini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Khẩn cấp.
 Sản phẩm/dịch vụ: máy xay sinh tố mini.
 Từ khóa chính: cốc mang đi; sạc USB; lưỡi dao inox.
@@ -1250,24 +1791,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Cần xem ngay cho người bận rộn muốn chuẩn bị đồ uống nhanh.
-Caption: máy xay sinh tố mini giúp việc hằng ngày nhẹ hơn nhờ cốc mang đi, sạc USB và lưỡi dao inox. Hiện có đổi mới trong 7 ngày nếu lỗi kỹ thuật, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #MayXaySinh #NguoiBanRon #CocMangDi
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của người bận rộn muốn chuẩn bị đồ uống nhanh.
-Caption: Với sạc USB và lưỡi dao inox, máy xay sinh tố mini cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. đổi mới trong 7 ngày nếu lỗi kỹ thuật là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #MayXaySinh #SacUSB #MuaSamThongMinh
-Phiên bản 3:
-Hook: Đừng chần chừ với người bận rộn muốn chuẩn bị đồ uống nhanh một lựa chọn gọn gàng hơn.
-Caption: Khi xem máy xay sinh tố mini, hãy chú ý vào cốc mang đi, sạc USB và lưỡi dao inox. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #MayXaySinh #LuoiDaoInox #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Đang cân nhắc thì nên xem kỹ hôm nay, nhưng không cần mua vội.
+Caption: máy xay sinh tố mini dành cho người bận rộn muốn chuẩn bị đồ uống nhanh trong những lúc sáng bận rộn vẫn muốn chuẩn bị một ly đồ uống nhanh trước khi ra khỏi nhà. Mình sẽ nhìn vào cốc mang đi, sạc USB và lưỡi dao inox trước, rồi mới xét đến ưu đãi đổi mới trong 7 ngày nếu lỗi kỹ thuật. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên cắt nhỏ nguyên liệu và xem kỹ hướng dẫn dùng an toàn.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #MayXayMini #SinhToNhanh #BepGon
+Phiên bản 2:
+Hook: Ưu đãi chỉ đáng giữ lại khi sản phẩm thật sự hợp với cách bạn dùng.
+Caption: Nếu bạn từng gặp chuyện ngại máy cồng kềnh, rửa lâu hoặc phải lắp quá nhiều bộ phận, máy xay sinh tố mini là một lựa chọn đáng để lưu lại. Sản phẩm có cốc mang đi, sạc USB và lưỡi dao inox, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Đổi mới trong 7 ngày nếu lỗi kỹ thuật là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #MayXayMini #SinhToNhanh #BepGon
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với máy xay sinh tố mini, hãy bắt đầu từ nhu cầu của người bận rộn muốn chuẩn bị đồ uống nhanh: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm cốc mang đi, sạc USB và lưỡi dao inox khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người thích đồ uống tự chuẩn bị nhưng không có nhiều thời gian.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #MayXayMini #SinhToNhanh #BepGon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">máy xay sinh tố mini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Email Marketing với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: máy xay sinh tố mini.
 Từ khóa chính: cốc mang đi; sạc USB; lưỡi dao inox.
@@ -1292,27 +1848,45 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Subject: Gợi ý máy xay sinh tố mini cho người bận rộn muốn chuẩn bị đồ uống nhanh
-Preview text: Tóm tắt nhanh các điểm đáng cân nhắc trước khi chọn mua.
+    <t xml:space="preserve">Phiên bản 1:
+Subject: Gợi ý máy xay sinh tố mini cho nhu cầu dùng hằng ngày
+Preview text: Một vài điểm đáng xem trước khi bạn quyết định.
 Lời chào: Chào bạn,
-Nội dung chính: Nếu bạn đang tìm một lựa chọn phù hợp cho nhu cầu hằng ngày, máy xay sinh tố mini có các điểm nổi bật như cốc mang đi, sạc USB và lưỡi dao inox. Hiện có đổi mới trong 7 ngày nếu lỗi kỹ thuật, nên bạn có thể xem thêm thông tin trước khi quyết định.
-Lời kêu gọi hành động: Xem chi tiết sản phẩm hôm nay.
-Phiên bản 2:
-Subject: máy xay sinh tố mini có thể hợp với nhu cầu của bạn
-Preview text: Một vài lý do để người bận rộn muốn chuẩn bị đồ uống nhanh cân nhắc sản phẩm này.
+Nội dung chính: Nếu bạn là người bận rộn muốn chuẩn bị đồ uống nhanh, có lẽ điều bạn cần không phải một lời giới thiệu quá mạnh. Bạn cần biết máy xay sinh tố mini có hợp với bối cảnh sáng bận rộn vẫn muốn chuẩn bị một ly đồ uống nhanh trước khi ra khỏi nhà hay không.
+Sản phẩm này đáng xem nhờ cốc mang đi, sạc USB và lưỡi dao inox. Trong đó, cốc mang đi giúp xử lý nhu cầu chính; sạc USB và lưỡi dao inox làm trải nghiệm dùng trọn vẹn hơn.
+Góc cần biết: Bạn nên cắt nhỏ nguyên liệu và xem kỹ hướng dẫn dùng an toàn. Hiện có đổi mới trong 7 ngày nếu lỗi kỹ thuật, bạn có thể xem như một điểm cộng nếu sản phẩm đã đúng nhu cầu.
+Lời kêu gọi hành động: Mở chi tiết sản phẩm hoặc nhắn shop để được tư vấn kỹ hơn.
+Phiên bản 2:
+Subject: Trước khi mua máy xay sinh tố mini, bạn có thể xem nhanh điểm này
+Preview text: Chọn chắc hơn khi biết sản phẩm giải quyết đúng việc gì.
 Lời chào: Chào bạn,
-Nội dung chính: máy xay sinh tố mini tập trung vào sạc USB, cốc mang đi và lưỡi dao inox. Thông tin được viết theo đúng brief, không thêm chứng nhận hay số liệu ngoài phạm vi. đổi mới trong 7 ngày nếu lỗi kỹ thuật giúp bạn có thêm lý do so sánh.
-Lời kêu gọi hành động: Nhắn lại để được tư vấn lựa chọn phù hợp.
-Phiên bản 3:
-Subject: Xem nhanh máy xay sinh tố mini trước khi bạn chọn
-Preview text: Thông tin ngắn gọn, dễ so sánh và có ưu đãi đi kèm.
+Nội dung chính: Nhiều người phân vân vì ngại máy cồng kềnh, rửa lâu hoặc phải lắp quá nhiều bộ phận. Vì vậy, với máy xay sinh tố mini, hãy nhìn vào nhu cầu thật trước: bạn cần cốc mang đi, muốn sạc USB, hay quan tâm nhiều hơn đến lưỡi dao inox?
+Nếu câu trả lời khớp với cách bạn dùng hằng ngày, đây là lựa chọn đáng cân nhắc. Nếu chưa chắc, bạn có thể hỏi shop trước khi đặt.
+Góc cần biết: Đổi mới trong 7 ngày nếu lỗi kỹ thuật đang đi kèm, nhưng quyết định cuối cùng vẫn nên dựa trên mức độ phù hợp.
+Lời kêu gọi hành động: Trả lời tin nhắn này với nhu cầu của bạn, shop sẽ gợi ý cụ thể hơn.
+Phiên bản 3:
+Subject: máy xay sinh tố mini có thể là món bạn đang tìm
+Preview text: Rõ lợi ích, rõ tình huống dùng, không cần quyết định vội.
 Lời chào: Chào bạn,
-Nội dung chính: Với người bận rộn muốn chuẩn bị đồ uống nhanh, một sản phẩm dễ hiểu thường giúp quyết định nhanh hơn. máy xay sinh tố mini có cốc mang đi, sạc USB và lưỡi dao inox; ngoài ra còn có đổi mới trong 7 ngày nếu lỗi kỹ thuật để bạn cân nhắc thêm.
-Lời kêu gọi hành động: Mở trang sản phẩm để xem thêm chi tiết.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Nội dung chính: Hợp với người thích đồ uống tự chuẩn bị nhưng không có nhiều thời gian. máy xay sinh tố mini tập trung vào cốc mang đi, sạc USB và lưỡi dao inox, phù hợp với người bận rộn muốn chuẩn bị đồ uống nhanh khi muốn một lựa chọn thực tế hơn cho sinh hoạt hằng ngày.
+Bạn có thể cân nhắc sản phẩm này nếu đang cần giải quyết chuyện ngại máy cồng kềnh, rửa lâu hoặc phải lắp quá nhiều bộ phận. Còn nếu muốn chắc hơn, hãy hỏi shop về tình huống dùng của bạn.
+Góc cần biết: Bạn nên cắt nhỏ nguyên liệu và xem kỹ hướng dẫn dùng an toàn.
+Lời kêu gọi hành động: Xem chi tiết hoặc nhắn shop trước khi chốt đơn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">máy xay sinh tố mini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Lời Kêu Gọi Hành Động với tone Thân thiện.
 Sản phẩm/dịch vụ: máy xay sinh tố mini.
 Từ khóa chính: cốc mang đi; sạc USB; lưỡi dao inox.
@@ -1334,18 +1908,30 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Lời kêu gọi hành động chính: Mua máy xay sinh tố mini ngay hôm nay
-Microcopy: Phù hợp cho người bận rộn muốn chuẩn bị đồ uống nhanh, có đổi mới trong 7 ngày nếu lỗi kỹ thuật và thông tin rõ ràng để bạn chọn nhanh.
-Phiên bản 2:
-Lời kêu gọi hành động chính: Chọn máy xay sinh tố mini cho nhu cầu hiện tại
-Microcopy: Tập trung vào cốc mang đi và sạc USB, giúp bạn quyết định dễ hơn.
-Phiên bản 3:
-Lời kêu gọi hành động chính: Nhắn shop để được tư vấn máy xay sinh tố mini
-Microcopy: Bạn có thể hỏi thêm về lưỡi dao inox và đổi mới trong 7 ngày nếu lỗi kỹ thuật trước khi quyết định.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Lời kêu gọi hành động chính: Xem máy xay sinh tố mini có hợp với bạn không
+Microcopy: Dành cho người bận rộn muốn chuẩn bị đồ uống nhanh, nổi bật với cốc mang đi, sạc USB và lưỡi dao inox. Có đổi mới trong 7 ngày nếu lỗi kỹ thuật nếu bạn muốn cân nhắc thêm.
+Phiên bản 2:
+Lời kêu gọi hành động chính: Nhắn shop để chọn máy xay sinh tố mini đúng nhu cầu
+Microcopy: Kể nhanh bạn dùng trong bối cảnh nào, shop sẽ gợi ý theo tình huống thật như sáng bận rộn vẫn muốn chuẩn bị một ly đồ uống nhanh trước khi ra khỏi nhà.
+Phiên bản 3:
+Lời kêu gọi hành động chính: Lưu máy xay sinh tố mini để so sánh trước khi mua
+Microcopy: Phù hợp hơn khi bạn muốn giải quyết chuyện ngại máy cồng kềnh, rửa lâu hoặc phải lắp quá nhiều bộ phận mà vẫn cần một lựa chọn rõ ràng, dễ hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">máy xay sinh tố mini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Khẩn cấp.
 Sản phẩm/dịch vụ: ghế công thái học lưng lưới.
 Từ khóa chính: đỡ lưng; tay ghế điều chỉnh; lưới thoáng.
@@ -1368,24 +1954,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Đừng chần chừ với ghế công thái học lưng lưới cho nhân viên ngồi máy tính lâu với đỡ lưng.
-Subheadline: Tập trung vào tay ghế điều chỉnh và lưới thoáng, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: ghế công thái học lưng lưới là lựa chọn đáng cân nhắc cho nhân viên ngồi máy tính lâu.
-Subheadline: Điểm mạnh nằm ở tay ghế điều chỉnh, đỡ lưng và hỗ trợ tư vấn chọn size để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Giữ nhịp nhanh hơn cho ghế công thái học lưng lưới nếu bạn cần đỡ lưng và tay ghế điều chỉnh.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>ghế công thái học lưng lưới</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: ghế công thái học lưng lưới: gọn hơn cho những lúc đỡ lưng thật sự quan trọng.
+Subheadline: Dành cho nhân viên ngồi máy tính lâu, nhất là khi một ngày làm việc dài trước màn hình cần điểm tựa ổn định hơn cho lưng và vai. Điểm đáng xem là đỡ lưng, tay ghế điều chỉnh và lưới thoáng; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên hỏi thêm về chiều cao bàn, vóc dáng và cách chỉnh tay ghế.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với ghế công thái học lưng lưới.
+Subheadline: Nếu bạn từng ngại chuyện ngồi tạm trên ghế không phù hợp dễ khiến cơ thể mỏi sớm, hãy bắt đầu từ ba điểm: đỡ lưng, tay ghế điều chỉnh và lưới thoáng. Ưu đãi hiện có: hỗ trợ tư vấn chọn size.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn ghế công thái học lưng lưới vừa đủ thực tế cho nhân viên ngồi máy tính lâu.
+Subheadline: Hợp với người làm việc tại bàn nhiều giờ và muốn nâng cấp góc làm việc một cách thực tế. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Hỗ trợ tư vấn chọn size là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ghế công thái học lưng lưới</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
 Sản phẩm/dịch vụ: ghế công thái học lưng lưới.
 Từ khóa chính: đỡ lưng; tay ghế điều chỉnh; lưới thoáng.
@@ -1408,21 +2006,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Gợi ý dễ dùng cho ghế công thái học lưng lưới cho nhân viên ngồi máy tính lâu với đỡ lưng.
-Subheadline: Tập trung vào tay ghế điều chỉnh và lưới thoáng, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: ghế công thái học lưng lưới là lựa chọn đáng cân nhắc cho nhân viên ngồi máy tính lâu.
-Subheadline: Điểm mạnh nằm ở tay ghế điều chỉnh, đỡ lưng và hỗ trợ tư vấn chọn size để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Thêm tiện lợi cho ghế công thái học lưng lưới nếu bạn cần đỡ lưng và tay ghế điều chỉnh.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: ghế công thái học lưng lưới: gọn hơn cho những lúc đỡ lưng thật sự quan trọng.
+Subheadline: Dành cho nhân viên ngồi máy tính lâu, nhất là khi một ngày làm việc dài trước màn hình cần điểm tựa ổn định hơn cho lưng và vai. Điểm đáng xem là đỡ lưng, tay ghế điều chỉnh và lưới thoáng; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên hỏi thêm về chiều cao bàn, vóc dáng và cách chỉnh tay ghế.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với ghế công thái học lưng lưới.
+Subheadline: Nếu bạn từng ngại chuyện ngồi tạm trên ghế không phù hợp dễ khiến cơ thể mỏi sớm, hãy bắt đầu từ ba điểm: đỡ lưng, tay ghế điều chỉnh và lưới thoáng. Ưu đãi hiện có: hỗ trợ tư vấn chọn size.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn ghế công thái học lưng lưới vừa đủ thực tế cho nhân viên ngồi máy tính lâu.
+Subheadline: Hợp với người làm việc tại bàn nhiều giờ và muốn nâng cấp góc làm việc một cách thực tế. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Hỗ trợ tư vấn chọn size là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ghế công thái học lưng lưới</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Cảm xúc.
 Sản phẩm/dịch vụ: ghế công thái học lưng lưới.
 Từ khóa chính: đỡ lưng; tay ghế điều chỉnh; lưới thoáng.
@@ -1446,36 +2059,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Mô tả ngắn: ghế công thái học lưng lưới dành cho nhân viên ngồi máy tính lâu, nhấn vào trải nghiệm dùng rõ ràng và dễ hiểu.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. ghế công thái học lưng lưới dành cho nhân viên ngồi máy tính lâu trong những lúc một ngày làm việc dài trước màn hình cần điểm tựa ổn định hơn cho lưng và vai.
 Lợi ích chính:
-- Hỗ trợ nhu cầu thực tế nhờ đỡ lưng và tay ghế điều chỉnh.
-- Giúp bạn cân nhắc nhanh hơn với thông tin đúng brief và hỗ trợ tư vấn chọn size.
+- Giúp bạn yên tâm hơn với nhu cầu đỡ lưng mà không phải đọc quá nhiều thông tin rối.
+- Tay ghế điều chỉnh là điểm cộng rõ ràng khi dùng hằng ngày.
+- Lưới thoáng giúp sản phẩm dễ được đưa vào thói quen hiện có.
 Đặc điểm nổi bật:
-- đỡ lưng.
-- lưới thoáng.
-Lời kêu gọi hành động: Xem chi tiết để chọn mẫu phù hợp.
-Phiên bản 2:
-Mô tả ngắn: Nếu bạn là nhân viên ngồi máy tính lâu, ghế công thái học lưng lưới là một lựa chọn gọn gàng, dễ dùng và sát nhu cầu.
+- đỡ lưng, tay ghế điều chỉnh và lưới thoáng.
+- Thông tin đi kèm: hỗ trợ tư vấn chọn size.
+Góc cần biết: Bạn nên hỏi thêm về chiều cao bàn, vóc dáng và cách chỉnh tay ghế.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì ngồi tạm trên ghế không phù hợp dễ khiến cơ thể mỏi sớm, ghế công thái học lưng lưới là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: đỡ lưng, tay ghế điều chỉnh và lưới thoáng.
 Lợi ích chính:
-- Mang lại cảm giác yên tâm khi xem thông tin rõ ràng.
-- Tập trung vào tay ghế điều chỉnh và lưới thoáng để phục vụ dùng hằng ngày.
-Đặc điểm nổi bật:
-- tay ghế điều chỉnh.
-- hỗ trợ tư vấn chọn size.
-Lời kêu gọi hành động: Nhắn tin để được tư vấn trước khi mua.
-Phiên bản 3:
-Mô tả ngắn: ghế công thái học lưng lưới giúp nhân viên ngồi máy tính lâu có thêm một lựa chọn hợp lý cho nhu cầu thường ngày.
-Lợi ích chính:
-- lưới thoáng làm cho việc dùng tiện hơn.
-- đỡ lưng hỗ trợ đúng mối quan tâm chính.
+- Phù hợp với nhân viên ngồi máy tính lâu muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi hỗ trợ tư vấn chọn size giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
 Đặc điểm nổi bật:
 - đỡ lưng.
 - tay ghế điều chỉnh.
-Lời kêu gọi hành động: Lưu lại để so sánh khi cần.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+- lưới thoáng.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: ghế công thái học lưng lưới hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người làm việc tại bàn nhiều giờ và muốn nâng cấp góc làm việc một cách thực tế.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin đỡ lưng, tay ghế điều chỉnh và lưới thoáng.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: đỡ lưng, tay ghế điều chỉnh và lưới thoáng.
+- Ghi chú thêm để cân nhắc: hỗ trợ tư vấn chọn size.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emotional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ghế công thái học lưng lưới</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: ghế công thái học lưng lưới.
 Từ khóa chính: đỡ lưng; tay ghế điều chỉnh; lưới thoáng.
@@ -1499,7 +2131,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. ghế công thái học lưng lưới dành cho nhân viên ngồi máy tính lâu trong những lúc một ngày làm việc dài trước màn hình cần điểm tựa ổn định hơn cho lưng và vai.
+Lợi ích chính:
+- Giúp bạn yên tâm hơn với nhu cầu đỡ lưng mà không phải đọc quá nhiều thông tin rối.
+- Tay ghế điều chỉnh là điểm cộng rõ ràng khi dùng hằng ngày.
+- Lưới thoáng giúp sản phẩm dễ được đưa vào thói quen hiện có.
+Đặc điểm nổi bật:
+- đỡ lưng, tay ghế điều chỉnh và lưới thoáng.
+- Thông tin đi kèm: hỗ trợ tư vấn chọn size.
+Góc cần biết: Bạn nên hỏi thêm về chiều cao bàn, vóc dáng và cách chỉnh tay ghế.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì ngồi tạm trên ghế không phù hợp dễ khiến cơ thể mỏi sớm, ghế công thái học lưng lưới là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: đỡ lưng, tay ghế điều chỉnh và lưới thoáng.
+Lợi ích chính:
+- Phù hợp với nhân viên ngồi máy tính lâu muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi hỗ trợ tư vấn chọn size giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
+Đặc điểm nổi bật:
+- đỡ lưng.
+- tay ghế điều chỉnh.
+- lưới thoáng.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: ghế công thái học lưng lưới hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người làm việc tại bàn nhiều giờ và muốn nâng cấp góc làm việc một cách thực tế.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin đỡ lưng, tay ghế điều chỉnh và lưới thoáng.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: đỡ lưng, tay ghế điều chỉnh và lưới thoáng.
+- Ghi chú thêm để cân nhắc: hỗ trợ tư vấn chọn size.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ghế công thái học lưng lưới</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Thân thiện.
 Sản phẩm/dịch vụ: ghế công thái học lưng lưới.
 Từ khóa chính: đỡ lưng; tay ghế điều chỉnh; lưới thoáng.
@@ -1523,24 +2203,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Một lựa chọn thân thiện cho nhân viên ngồi máy tính lâu.
-Caption: ghế công thái học lưng lưới giúp việc hằng ngày nhẹ hơn nhờ đỡ lưng, tay ghế điều chỉnh và lưới thoáng. Hiện có hỗ trợ tư vấn chọn size, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #GheCongThai #NhanVienNgoi #DoLung
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của nhân viên ngồi máy tính lâu.
-Caption: Với tay ghế điều chỉnh và lưới thoáng, ghế công thái học lưng lưới cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. hỗ trợ tư vấn chọn size là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #GheCongThai #TayGheDieu #MuaSamThongMinh
-Phiên bản 3:
-Hook: Gợi ý dễ dùng cho nhân viên ngồi máy tính lâu một lựa chọn gọn gàng hơn.
-Caption: Khi xem ghế công thái học lưng lưới, hãy chú ý vào đỡ lưng, tay ghế điều chỉnh và lưới thoáng. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #GheCongThai #LuoiThoang #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Một món nhỏ, nhưng dùng đúng lúc thì thấy ngày nhẹ hơn một chút.
+Caption: ghế công thái học lưng lưới dành cho nhân viên ngồi máy tính lâu trong những lúc một ngày làm việc dài trước màn hình cần điểm tựa ổn định hơn cho lưng và vai. Mình sẽ nhìn vào đỡ lưng, tay ghế điều chỉnh và lưới thoáng trước, rồi mới xét đến ưu đãi hỗ trợ tư vấn chọn size. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên hỏi thêm về chiều cao bàn, vóc dáng và cách chỉnh tay ghế.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #GheCongThaiHoc #GocLamViec #LamViecLau
+Phiên bản 2:
+Hook: Mua sắm dễ chịu hơn khi thông tin đủ rõ và không bị thúc ép.
+Caption: Nếu bạn từng gặp chuyện ngồi tạm trên ghế không phù hợp dễ khiến cơ thể mỏi sớm, ghế công thái học lưng lưới là một lựa chọn đáng để lưu lại. Sản phẩm có đỡ lưng, tay ghế điều chỉnh và lưới thoáng, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Hỗ trợ tư vấn chọn size là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #GheCongThaiHoc #GocLamViec #LamViecLau
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với ghế công thái học lưng lưới, hãy bắt đầu từ nhu cầu của nhân viên ngồi máy tính lâu: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm đỡ lưng, tay ghế điều chỉnh và lưới thoáng khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người làm việc tại bàn nhiều giờ và muốn nâng cấp góc làm việc một cách thực tế.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #GheCongThaiHoc #GocLamViec #LamViecLau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ghế công thái học lưng lưới</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Khẩn cấp.
 Sản phẩm/dịch vụ: ghế công thái học lưng lưới.
 Từ khóa chính: đỡ lưng; tay ghế điều chỉnh; lưới thoáng.
@@ -1564,24 +2259,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Cần xem ngay cho nhân viên ngồi máy tính lâu.
-Caption: ghế công thái học lưng lưới giúp việc hằng ngày nhẹ hơn nhờ đỡ lưng, tay ghế điều chỉnh và lưới thoáng. Hiện có hỗ trợ tư vấn chọn size, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #GheCongThai #NhanVienNgoi #DoLung
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của nhân viên ngồi máy tính lâu.
-Caption: Với tay ghế điều chỉnh và lưới thoáng, ghế công thái học lưng lưới cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. hỗ trợ tư vấn chọn size là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #GheCongThai #TayGheDieu #MuaSamThongMinh
-Phiên bản 3:
-Hook: Đừng chần chừ với nhân viên ngồi máy tính lâu một lựa chọn gọn gàng hơn.
-Caption: Khi xem ghế công thái học lưng lưới, hãy chú ý vào đỡ lưng, tay ghế điều chỉnh và lưới thoáng. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #GheCongThai #LuoiThoang #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Đang cân nhắc thì nên xem kỹ hôm nay, nhưng không cần mua vội.
+Caption: ghế công thái học lưng lưới dành cho nhân viên ngồi máy tính lâu trong những lúc một ngày làm việc dài trước màn hình cần điểm tựa ổn định hơn cho lưng và vai. Mình sẽ nhìn vào đỡ lưng, tay ghế điều chỉnh và lưới thoáng trước, rồi mới xét đến ưu đãi hỗ trợ tư vấn chọn size. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên hỏi thêm về chiều cao bàn, vóc dáng và cách chỉnh tay ghế.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #GheCongThaiHoc #GocLamViec #LamViecLau
+Phiên bản 2:
+Hook: Ưu đãi chỉ đáng giữ lại khi sản phẩm thật sự hợp với cách bạn dùng.
+Caption: Nếu bạn từng gặp chuyện ngồi tạm trên ghế không phù hợp dễ khiến cơ thể mỏi sớm, ghế công thái học lưng lưới là một lựa chọn đáng để lưu lại. Sản phẩm có đỡ lưng, tay ghế điều chỉnh và lưới thoáng, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Hỗ trợ tư vấn chọn size là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #GheCongThaiHoc #GocLamViec #LamViecLau
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với ghế công thái học lưng lưới, hãy bắt đầu từ nhu cầu của nhân viên ngồi máy tính lâu: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm đỡ lưng, tay ghế điều chỉnh và lưới thoáng khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người làm việc tại bàn nhiều giờ và muốn nâng cấp góc làm việc một cách thực tế.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #GheCongThaiHoc #GocLamViec #LamViecLau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ghế công thái học lưng lưới</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Email Marketing với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: ghế công thái học lưng lưới.
 Từ khóa chính: đỡ lưng; tay ghế điều chỉnh; lưới thoáng.
@@ -1606,27 +2316,45 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Subject: Gợi ý ghế công thái học lưng lưới cho nhân viên ngồi máy tính lâu
-Preview text: Tóm tắt nhanh các điểm đáng cân nhắc trước khi chọn mua.
+    <t xml:space="preserve">Phiên bản 1:
+Subject: Gợi ý ghế công thái học lưng lưới cho nhu cầu dùng hằng ngày
+Preview text: Một vài điểm đáng xem trước khi bạn quyết định.
 Lời chào: Chào bạn,
-Nội dung chính: Nếu bạn đang tìm một lựa chọn phù hợp cho nhu cầu hằng ngày, ghế công thái học lưng lưới có các điểm nổi bật như đỡ lưng, tay ghế điều chỉnh và lưới thoáng. Hiện có hỗ trợ tư vấn chọn size, nên bạn có thể xem thêm thông tin trước khi quyết định.
-Lời kêu gọi hành động: Xem chi tiết sản phẩm hôm nay.
-Phiên bản 2:
-Subject: ghế công thái học lưng lưới có thể hợp với nhu cầu của bạn
-Preview text: Một vài lý do để nhân viên ngồi máy tính lâu cân nhắc sản phẩm này.
+Nội dung chính: Nếu bạn là nhân viên ngồi máy tính lâu, có lẽ điều bạn cần không phải một lời giới thiệu quá mạnh. Bạn cần biết ghế công thái học lưng lưới có hợp với bối cảnh một ngày làm việc dài trước màn hình cần điểm tựa ổn định hơn cho lưng và vai hay không.
+Sản phẩm này đáng xem nhờ đỡ lưng, tay ghế điều chỉnh và lưới thoáng. Trong đó, đỡ lưng giúp xử lý nhu cầu chính; tay ghế điều chỉnh và lưới thoáng làm trải nghiệm dùng trọn vẹn hơn.
+Góc cần biết: Bạn nên hỏi thêm về chiều cao bàn, vóc dáng và cách chỉnh tay ghế. Hiện có hỗ trợ tư vấn chọn size, bạn có thể xem như một điểm cộng nếu sản phẩm đã đúng nhu cầu.
+Lời kêu gọi hành động: Mở chi tiết sản phẩm hoặc nhắn shop để được tư vấn kỹ hơn.
+Phiên bản 2:
+Subject: Trước khi mua ghế công thái học lưng lưới, bạn có thể xem nhanh điểm này
+Preview text: Chọn chắc hơn khi biết sản phẩm giải quyết đúng việc gì.
 Lời chào: Chào bạn,
-Nội dung chính: ghế công thái học lưng lưới tập trung vào tay ghế điều chỉnh, đỡ lưng và lưới thoáng. Thông tin được viết theo đúng brief, không thêm chứng nhận hay số liệu ngoài phạm vi. hỗ trợ tư vấn chọn size giúp bạn có thêm lý do so sánh.
-Lời kêu gọi hành động: Nhắn lại để được tư vấn lựa chọn phù hợp.
-Phiên bản 3:
-Subject: Xem nhanh ghế công thái học lưng lưới trước khi bạn chọn
-Preview text: Thông tin ngắn gọn, dễ so sánh và có ưu đãi đi kèm.
+Nội dung chính: Nhiều người phân vân vì ngồi tạm trên ghế không phù hợp dễ khiến cơ thể mỏi sớm. Vì vậy, với ghế công thái học lưng lưới, hãy nhìn vào nhu cầu thật trước: bạn cần đỡ lưng, muốn tay ghế điều chỉnh, hay quan tâm nhiều hơn đến lưới thoáng?
+Nếu câu trả lời khớp với cách bạn dùng hằng ngày, đây là lựa chọn đáng cân nhắc. Nếu chưa chắc, bạn có thể hỏi shop trước khi đặt.
+Góc cần biết: Hỗ trợ tư vấn chọn size đang đi kèm, nhưng quyết định cuối cùng vẫn nên dựa trên mức độ phù hợp.
+Lời kêu gọi hành động: Trả lời tin nhắn này với nhu cầu của bạn, shop sẽ gợi ý cụ thể hơn.
+Phiên bản 3:
+Subject: ghế công thái học lưng lưới có thể là món bạn đang tìm
+Preview text: Rõ lợi ích, rõ tình huống dùng, không cần quyết định vội.
 Lời chào: Chào bạn,
-Nội dung chính: Với nhân viên ngồi máy tính lâu, một sản phẩm dễ hiểu thường giúp quyết định nhanh hơn. ghế công thái học lưng lưới có đỡ lưng, tay ghế điều chỉnh và lưới thoáng; ngoài ra còn có hỗ trợ tư vấn chọn size để bạn cân nhắc thêm.
-Lời kêu gọi hành động: Mở trang sản phẩm để xem thêm chi tiết.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Nội dung chính: Hợp với người làm việc tại bàn nhiều giờ và muốn nâng cấp góc làm việc một cách thực tế. ghế công thái học lưng lưới tập trung vào đỡ lưng, tay ghế điều chỉnh và lưới thoáng, phù hợp với nhân viên ngồi máy tính lâu khi muốn một lựa chọn thực tế hơn cho sinh hoạt hằng ngày.
+Bạn có thể cân nhắc sản phẩm này nếu đang cần giải quyết chuyện ngồi tạm trên ghế không phù hợp dễ khiến cơ thể mỏi sớm. Còn nếu muốn chắc hơn, hãy hỏi shop về tình huống dùng của bạn.
+Góc cần biết: Bạn nên hỏi thêm về chiều cao bàn, vóc dáng và cách chỉnh tay ghế.
+Lời kêu gọi hành động: Xem chi tiết hoặc nhắn shop trước khi chốt đơn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ghế công thái học lưng lưới</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Lời Kêu Gọi Hành Động với tone Thân thiện.
 Sản phẩm/dịch vụ: ghế công thái học lưng lưới.
 Từ khóa chính: đỡ lưng; tay ghế điều chỉnh; lưới thoáng.
@@ -1648,18 +2376,30 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Lời kêu gọi hành động chính: Mua ghế công thái học lưng lưới ngay hôm nay
-Microcopy: Phù hợp cho nhân viên ngồi máy tính lâu, có hỗ trợ tư vấn chọn size và thông tin rõ ràng để bạn chọn nhanh.
-Phiên bản 2:
-Lời kêu gọi hành động chính: Chọn ghế công thái học lưng lưới cho nhu cầu hiện tại
-Microcopy: Tập trung vào đỡ lưng và tay ghế điều chỉnh, giúp bạn quyết định dễ hơn.
-Phiên bản 3:
-Lời kêu gọi hành động chính: Nhắn shop để được tư vấn ghế công thái học lưng lưới
-Microcopy: Bạn có thể hỏi thêm về lưới thoáng và hỗ trợ tư vấn chọn size trước khi quyết định.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Lời kêu gọi hành động chính: Xem ghế công thái học lưng lưới có hợp với bạn không
+Microcopy: Dành cho nhân viên ngồi máy tính lâu, nổi bật với đỡ lưng, tay ghế điều chỉnh và lưới thoáng. Có hỗ trợ tư vấn chọn size nếu bạn muốn cân nhắc thêm.
+Phiên bản 2:
+Lời kêu gọi hành động chính: Nhắn shop để chọn ghế công thái học lưng lưới đúng nhu cầu
+Microcopy: Kể nhanh bạn dùng trong bối cảnh nào, shop sẽ gợi ý theo tình huống thật như một ngày làm việc dài trước màn hình cần điểm tựa ổn định hơn cho lưng và vai.
+Phiên bản 3:
+Lời kêu gọi hành động chính: Lưu ghế công thái học lưng lưới để so sánh trước khi mua
+Microcopy: Phù hợp hơn khi bạn muốn giải quyết chuyện ngồi tạm trên ghế không phù hợp dễ khiến cơ thể mỏi sớm mà vẫn cần một lựa chọn rõ ràng, dễ hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ghế công thái học lưng lưới</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Khẩn cấp.
 Sản phẩm/dịch vụ: nồi chiên không dầu dung tích 6 lít.
 Từ khóa chính: khay chống dính; hẹn giờ; dễ lau chùi.
@@ -1682,24 +2422,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Đừng chần chừ với nồi chiên không dầu dung tích 6 lít cho gia đình muốn nấu nhanh gọn với khay chống dính.
-Subheadline: Tập trung vào hẹn giờ và dễ lau chùi, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: nồi chiên không dầu dung tích 6 lít là lựa chọn đáng cân nhắc cho gia đình muốn nấu nhanh gọn.
-Subheadline: Điểm mạnh nằm ở hẹn giờ, khay chống dính và kèm sổ công thức điện tử để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Giữ nhịp nhanh hơn cho nồi chiên không dầu dung tích 6 lít nếu bạn cần khay chống dính và hẹn giờ.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>nồi chiên không dầu dung tích 6 lít</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: nồi chiên không dầu dung tích 6 lít: gọn hơn cho những lúc khay chống dính thật sự quan trọng.
+Subheadline: Dành cho gia đình muốn nấu nhanh gọn, nhất là khi bữa tối gia đình cần món nhanh, ít phải canh bếp và dễ dọn sau khi ăn. Điểm đáng xem là khay chống dính, hẹn giờ và dễ lau chùi; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên cân nhắc khẩu phần gia đình và cách vệ sinh khay.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với nồi chiên không dầu dung tích 6 lít.
+Subheadline: Nếu bạn từng ngại chuyện ngại dầu bắn, khay khó rửa hoặc dung tích không đủ cho cả nhà, hãy bắt đầu từ ba điểm: khay chống dính, hẹn giờ và dễ lau chùi. Ưu đãi hiện có: kèm sổ công thức điện tử.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn nồi chiên không dầu dung tích 6 lít vừa đủ thực tế cho gia đình muốn nấu nhanh gọn.
+Subheadline: Hợp với gia đình muốn nấu gọn hơn mà vẫn có nhiều lựa chọn món quen. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Kèm sổ công thức điện tử là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nồi chiên không dầu dung tích 6 lít</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
 Sản phẩm/dịch vụ: nồi chiên không dầu dung tích 6 lít.
 Từ khóa chính: khay chống dính; hẹn giờ; dễ lau chùi.
@@ -1722,21 +2474,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Gợi ý dễ dùng cho nồi chiên không dầu dung tích 6 lít cho gia đình muốn nấu nhanh gọn với khay chống dính.
-Subheadline: Tập trung vào hẹn giờ và dễ lau chùi, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: nồi chiên không dầu dung tích 6 lít là lựa chọn đáng cân nhắc cho gia đình muốn nấu nhanh gọn.
-Subheadline: Điểm mạnh nằm ở hẹn giờ, khay chống dính và kèm sổ công thức điện tử để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Thêm tiện lợi cho nồi chiên không dầu dung tích 6 lít nếu bạn cần khay chống dính và hẹn giờ.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: nồi chiên không dầu dung tích 6 lít: gọn hơn cho những lúc khay chống dính thật sự quan trọng.
+Subheadline: Dành cho gia đình muốn nấu nhanh gọn, nhất là khi bữa tối gia đình cần món nhanh, ít phải canh bếp và dễ dọn sau khi ăn. Điểm đáng xem là khay chống dính, hẹn giờ và dễ lau chùi; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên cân nhắc khẩu phần gia đình và cách vệ sinh khay.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với nồi chiên không dầu dung tích 6 lít.
+Subheadline: Nếu bạn từng ngại chuyện ngại dầu bắn, khay khó rửa hoặc dung tích không đủ cho cả nhà, hãy bắt đầu từ ba điểm: khay chống dính, hẹn giờ và dễ lau chùi. Ưu đãi hiện có: kèm sổ công thức điện tử.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn nồi chiên không dầu dung tích 6 lít vừa đủ thực tế cho gia đình muốn nấu nhanh gọn.
+Subheadline: Hợp với gia đình muốn nấu gọn hơn mà vẫn có nhiều lựa chọn món quen. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Kèm sổ công thức điện tử là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nồi chiên không dầu dung tích 6 lít</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Cảm xúc.
 Sản phẩm/dịch vụ: nồi chiên không dầu dung tích 6 lít.
 Từ khóa chính: khay chống dính; hẹn giờ; dễ lau chùi.
@@ -1760,36 +2527,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Mô tả ngắn: nồi chiên không dầu dung tích 6 lít dành cho gia đình muốn nấu nhanh gọn, nhấn vào trải nghiệm dùng rõ ràng và dễ hiểu.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. nồi chiên không dầu dung tích 6 lít dành cho gia đình muốn nấu nhanh gọn trong những lúc bữa tối gia đình cần món nhanh, ít phải canh bếp và dễ dọn sau khi ăn.
 Lợi ích chính:
-- Hỗ trợ nhu cầu thực tế nhờ khay chống dính và hẹn giờ.
-- Giúp bạn cân nhắc nhanh hơn với thông tin đúng brief và kèm sổ công thức điện tử.
+- Giúp bạn yên tâm hơn với nhu cầu khay chống dính mà không phải đọc quá nhiều thông tin rối.
+- Hẹn giờ là điểm cộng rõ ràng khi dùng hằng ngày.
+- Dễ lau chùi giúp sản phẩm dễ được đưa vào thói quen hiện có.
 Đặc điểm nổi bật:
-- khay chống dính.
-- dễ lau chùi.
-Lời kêu gọi hành động: Xem chi tiết để chọn mẫu phù hợp.
-Phiên bản 2:
-Mô tả ngắn: Nếu bạn là gia đình muốn nấu nhanh gọn, nồi chiên không dầu dung tích 6 lít là một lựa chọn gọn gàng, dễ dùng và sát nhu cầu.
+- khay chống dính, hẹn giờ và dễ lau chùi.
+- Thông tin đi kèm: kèm sổ công thức điện tử.
+Góc cần biết: Bạn nên cân nhắc khẩu phần gia đình và cách vệ sinh khay.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì ngại dầu bắn, khay khó rửa hoặc dung tích không đủ cho cả nhà, nồi chiên không dầu dung tích 6 lít là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: khay chống dính, hẹn giờ và dễ lau chùi.
 Lợi ích chính:
-- Mang lại cảm giác yên tâm khi xem thông tin rõ ràng.
-- Tập trung vào hẹn giờ và dễ lau chùi để phục vụ dùng hằng ngày.
-Đặc điểm nổi bật:
-- hẹn giờ.
-- kèm sổ công thức điện tử.
-Lời kêu gọi hành động: Nhắn tin để được tư vấn trước khi mua.
-Phiên bản 3:
-Mô tả ngắn: nồi chiên không dầu dung tích 6 lít giúp gia đình muốn nấu nhanh gọn có thêm một lựa chọn hợp lý cho nhu cầu thường ngày.
-Lợi ích chính:
-- dễ lau chùi làm cho việc dùng tiện hơn.
-- khay chống dính hỗ trợ đúng mối quan tâm chính.
+- Phù hợp với gia đình muốn nấu nhanh gọn muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi kèm sổ công thức điện tử giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
 Đặc điểm nổi bật:
 - khay chống dính.
 - hẹn giờ.
-Lời kêu gọi hành động: Lưu lại để so sánh khi cần.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+- dễ lau chùi.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: nồi chiên không dầu dung tích 6 lít hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với gia đình muốn nấu gọn hơn mà vẫn có nhiều lựa chọn món quen.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin khay chống dính, hẹn giờ và dễ lau chùi.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: khay chống dính, hẹn giờ và dễ lau chùi.
+- Ghi chú thêm để cân nhắc: kèm sổ công thức điện tử.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emotional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nồi chiên không dầu dung tích 6 lít</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: nồi chiên không dầu dung tích 6 lít.
 Từ khóa chính: khay chống dính; hẹn giờ; dễ lau chùi.
@@ -1813,7 +2599,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. nồi chiên không dầu dung tích 6 lít dành cho gia đình muốn nấu nhanh gọn trong những lúc bữa tối gia đình cần món nhanh, ít phải canh bếp và dễ dọn sau khi ăn.
+Lợi ích chính:
+- Giúp bạn yên tâm hơn với nhu cầu khay chống dính mà không phải đọc quá nhiều thông tin rối.
+- Hẹn giờ là điểm cộng rõ ràng khi dùng hằng ngày.
+- Dễ lau chùi giúp sản phẩm dễ được đưa vào thói quen hiện có.
+Đặc điểm nổi bật:
+- khay chống dính, hẹn giờ và dễ lau chùi.
+- Thông tin đi kèm: kèm sổ công thức điện tử.
+Góc cần biết: Bạn nên cân nhắc khẩu phần gia đình và cách vệ sinh khay.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì ngại dầu bắn, khay khó rửa hoặc dung tích không đủ cho cả nhà, nồi chiên không dầu dung tích 6 lít là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: khay chống dính, hẹn giờ và dễ lau chùi.
+Lợi ích chính:
+- Phù hợp với gia đình muốn nấu nhanh gọn muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi kèm sổ công thức điện tử giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
+Đặc điểm nổi bật:
+- khay chống dính.
+- hẹn giờ.
+- dễ lau chùi.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: nồi chiên không dầu dung tích 6 lít hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với gia đình muốn nấu gọn hơn mà vẫn có nhiều lựa chọn món quen.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin khay chống dính, hẹn giờ và dễ lau chùi.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: khay chống dính, hẹn giờ và dễ lau chùi.
+- Ghi chú thêm để cân nhắc: kèm sổ công thức điện tử.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nồi chiên không dầu dung tích 6 lít</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Thân thiện.
 Sản phẩm/dịch vụ: nồi chiên không dầu dung tích 6 lít.
 Từ khóa chính: khay chống dính; hẹn giờ; dễ lau chùi.
@@ -1837,24 +2671,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Một lựa chọn thân thiện cho gia đình muốn nấu nhanh gọn.
-Caption: nồi chiên không dầu dung tích 6 lít giúp việc hằng ngày nhẹ hơn nhờ khay chống dính, hẹn giờ và dễ lau chùi. Hiện có kèm sổ công thức điện tử, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #NoiChienKhong #GiaDinhMuon #KhayChongDinh
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của gia đình muốn nấu nhanh gọn.
-Caption: Với hẹn giờ và dễ lau chùi, nồi chiên không dầu dung tích 6 lít cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. kèm sổ công thức điện tử là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #NoiChienKhong #HenGio #MuaSamThongMinh
-Phiên bản 3:
-Hook: Gợi ý dễ dùng cho gia đình muốn nấu nhanh gọn một lựa chọn gọn gàng hơn.
-Caption: Khi xem nồi chiên không dầu dung tích 6 lít, hãy chú ý vào khay chống dính, hẹn giờ và dễ lau chùi. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #NoiChienKhong #DeLauChui #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Một món nhỏ, nhưng dùng đúng lúc thì thấy ngày nhẹ hơn một chút.
+Caption: nồi chiên không dầu dung tích 6 lít dành cho gia đình muốn nấu nhanh gọn trong những lúc bữa tối gia đình cần món nhanh, ít phải canh bếp và dễ dọn sau khi ăn. Mình sẽ nhìn vào khay chống dính, hẹn giờ và dễ lau chùi trước, rồi mới xét đến ưu đãi kèm sổ công thức điện tử. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên cân nhắc khẩu phần gia đình và cách vệ sinh khay.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #NoiChienKhongDau #BepGiaDinh #NauAnGon
+Phiên bản 2:
+Hook: Mua sắm dễ chịu hơn khi thông tin đủ rõ và không bị thúc ép.
+Caption: Nếu bạn từng gặp chuyện ngại dầu bắn, khay khó rửa hoặc dung tích không đủ cho cả nhà, nồi chiên không dầu dung tích 6 lít là một lựa chọn đáng để lưu lại. Sản phẩm có khay chống dính, hẹn giờ và dễ lau chùi, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Kèm sổ công thức điện tử là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #NoiChienKhongDau #BepGiaDinh #NauAnGon
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với nồi chiên không dầu dung tích 6 lít, hãy bắt đầu từ nhu cầu của gia đình muốn nấu nhanh gọn: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm khay chống dính, hẹn giờ và dễ lau chùi khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với gia đình muốn nấu gọn hơn mà vẫn có nhiều lựa chọn món quen.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #NoiChienKhongDau #BepGiaDinh #NauAnGon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nồi chiên không dầu dung tích 6 lít</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Khẩn cấp.
 Sản phẩm/dịch vụ: nồi chiên không dầu dung tích 6 lít.
 Từ khóa chính: khay chống dính; hẹn giờ; dễ lau chùi.
@@ -1878,24 +2727,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Cần xem ngay cho gia đình muốn nấu nhanh gọn.
-Caption: nồi chiên không dầu dung tích 6 lít giúp việc hằng ngày nhẹ hơn nhờ khay chống dính, hẹn giờ và dễ lau chùi. Hiện có kèm sổ công thức điện tử, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #NoiChienKhong #GiaDinhMuon #KhayChongDinh
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của gia đình muốn nấu nhanh gọn.
-Caption: Với hẹn giờ và dễ lau chùi, nồi chiên không dầu dung tích 6 lít cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. kèm sổ công thức điện tử là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #NoiChienKhong #HenGio #MuaSamThongMinh
-Phiên bản 3:
-Hook: Đừng chần chừ với gia đình muốn nấu nhanh gọn một lựa chọn gọn gàng hơn.
-Caption: Khi xem nồi chiên không dầu dung tích 6 lít, hãy chú ý vào khay chống dính, hẹn giờ và dễ lau chùi. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #NoiChienKhong #DeLauChui #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Đang cân nhắc thì nên xem kỹ hôm nay, nhưng không cần mua vội.
+Caption: nồi chiên không dầu dung tích 6 lít dành cho gia đình muốn nấu nhanh gọn trong những lúc bữa tối gia đình cần món nhanh, ít phải canh bếp và dễ dọn sau khi ăn. Mình sẽ nhìn vào khay chống dính, hẹn giờ và dễ lau chùi trước, rồi mới xét đến ưu đãi kèm sổ công thức điện tử. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên cân nhắc khẩu phần gia đình và cách vệ sinh khay.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #NoiChienKhongDau #BepGiaDinh #NauAnGon
+Phiên bản 2:
+Hook: Ưu đãi chỉ đáng giữ lại khi sản phẩm thật sự hợp với cách bạn dùng.
+Caption: Nếu bạn từng gặp chuyện ngại dầu bắn, khay khó rửa hoặc dung tích không đủ cho cả nhà, nồi chiên không dầu dung tích 6 lít là một lựa chọn đáng để lưu lại. Sản phẩm có khay chống dính, hẹn giờ và dễ lau chùi, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Kèm sổ công thức điện tử là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #NoiChienKhongDau #BepGiaDinh #NauAnGon
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với nồi chiên không dầu dung tích 6 lít, hãy bắt đầu từ nhu cầu của gia đình muốn nấu nhanh gọn: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm khay chống dính, hẹn giờ và dễ lau chùi khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với gia đình muốn nấu gọn hơn mà vẫn có nhiều lựa chọn món quen.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #NoiChienKhongDau #BepGiaDinh #NauAnGon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nồi chiên không dầu dung tích 6 lít</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Email Marketing với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: nồi chiên không dầu dung tích 6 lít.
 Từ khóa chính: khay chống dính; hẹn giờ; dễ lau chùi.
@@ -1920,27 +2784,45 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Subject: Gợi ý nồi chiên không dầu dung tích 6 lít cho gia đình muốn nấu nhanh gọn
-Preview text: Tóm tắt nhanh các điểm đáng cân nhắc trước khi chọn mua.
+    <t xml:space="preserve">Phiên bản 1:
+Subject: Gợi ý nồi chiên không dầu dung tích 6 lít cho nhu cầu dùng hằng ngày
+Preview text: Một vài điểm đáng xem trước khi bạn quyết định.
 Lời chào: Chào bạn,
-Nội dung chính: Nếu bạn đang tìm một lựa chọn phù hợp cho nhu cầu hằng ngày, nồi chiên không dầu dung tích 6 lít có các điểm nổi bật như khay chống dính, hẹn giờ và dễ lau chùi. Hiện có kèm sổ công thức điện tử, nên bạn có thể xem thêm thông tin trước khi quyết định.
-Lời kêu gọi hành động: Xem chi tiết sản phẩm hôm nay.
-Phiên bản 2:
-Subject: nồi chiên không dầu dung tích 6 lít có thể hợp với nhu cầu của bạn
-Preview text: Một vài lý do để gia đình muốn nấu nhanh gọn cân nhắc sản phẩm này.
+Nội dung chính: Nếu bạn là gia đình muốn nấu nhanh gọn, có lẽ điều bạn cần không phải một lời giới thiệu quá mạnh. Bạn cần biết nồi chiên không dầu dung tích 6 lít có hợp với bối cảnh bữa tối gia đình cần món nhanh, ít phải canh bếp và dễ dọn sau khi ăn hay không.
+Sản phẩm này đáng xem nhờ khay chống dính, hẹn giờ và dễ lau chùi. Trong đó, khay chống dính giúp xử lý nhu cầu chính; hẹn giờ và dễ lau chùi làm trải nghiệm dùng trọn vẹn hơn.
+Góc cần biết: Bạn nên cân nhắc khẩu phần gia đình và cách vệ sinh khay. Hiện có kèm sổ công thức điện tử, bạn có thể xem như một điểm cộng nếu sản phẩm đã đúng nhu cầu.
+Lời kêu gọi hành động: Mở chi tiết sản phẩm hoặc nhắn shop để được tư vấn kỹ hơn.
+Phiên bản 2:
+Subject: Trước khi mua nồi chiên không dầu dung tích 6 lít, bạn có thể xem nhanh điểm này
+Preview text: Chọn chắc hơn khi biết sản phẩm giải quyết đúng việc gì.
 Lời chào: Chào bạn,
-Nội dung chính: nồi chiên không dầu dung tích 6 lít tập trung vào hẹn giờ, khay chống dính và dễ lau chùi. Thông tin được viết theo đúng brief, không thêm chứng nhận hay số liệu ngoài phạm vi. kèm sổ công thức điện tử giúp bạn có thêm lý do so sánh.
-Lời kêu gọi hành động: Nhắn lại để được tư vấn lựa chọn phù hợp.
-Phiên bản 3:
-Subject: Xem nhanh nồi chiên không dầu dung tích 6 lít trước khi bạn chọn
-Preview text: Thông tin ngắn gọn, dễ so sánh và có ưu đãi đi kèm.
+Nội dung chính: Nhiều người phân vân vì ngại dầu bắn, khay khó rửa hoặc dung tích không đủ cho cả nhà. Vì vậy, với nồi chiên không dầu dung tích 6 lít, hãy nhìn vào nhu cầu thật trước: bạn cần khay chống dính, muốn hẹn giờ, hay quan tâm nhiều hơn đến dễ lau chùi?
+Nếu câu trả lời khớp với cách bạn dùng hằng ngày, đây là lựa chọn đáng cân nhắc. Nếu chưa chắc, bạn có thể hỏi shop trước khi đặt.
+Góc cần biết: Kèm sổ công thức điện tử đang đi kèm, nhưng quyết định cuối cùng vẫn nên dựa trên mức độ phù hợp.
+Lời kêu gọi hành động: Trả lời tin nhắn này với nhu cầu của bạn, shop sẽ gợi ý cụ thể hơn.
+Phiên bản 3:
+Subject: nồi chiên không dầu dung tích 6 lít có thể là món bạn đang tìm
+Preview text: Rõ lợi ích, rõ tình huống dùng, không cần quyết định vội.
 Lời chào: Chào bạn,
-Nội dung chính: Với gia đình muốn nấu nhanh gọn, một sản phẩm dễ hiểu thường giúp quyết định nhanh hơn. nồi chiên không dầu dung tích 6 lít có khay chống dính, hẹn giờ và dễ lau chùi; ngoài ra còn có kèm sổ công thức điện tử để bạn cân nhắc thêm.
-Lời kêu gọi hành động: Mở trang sản phẩm để xem thêm chi tiết.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Nội dung chính: Hợp với gia đình muốn nấu gọn hơn mà vẫn có nhiều lựa chọn món quen. nồi chiên không dầu dung tích 6 lít tập trung vào khay chống dính, hẹn giờ và dễ lau chùi, phù hợp với gia đình muốn nấu nhanh gọn khi muốn một lựa chọn thực tế hơn cho sinh hoạt hằng ngày.
+Bạn có thể cân nhắc sản phẩm này nếu đang cần giải quyết chuyện ngại dầu bắn, khay khó rửa hoặc dung tích không đủ cho cả nhà. Còn nếu muốn chắc hơn, hãy hỏi shop về tình huống dùng của bạn.
+Góc cần biết: Bạn nên cân nhắc khẩu phần gia đình và cách vệ sinh khay.
+Lời kêu gọi hành động: Xem chi tiết hoặc nhắn shop trước khi chốt đơn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nồi chiên không dầu dung tích 6 lít</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Lời Kêu Gọi Hành Động với tone Thân thiện.
 Sản phẩm/dịch vụ: nồi chiên không dầu dung tích 6 lít.
 Từ khóa chính: khay chống dính; hẹn giờ; dễ lau chùi.
@@ -1962,18 +2844,30 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Lời kêu gọi hành động chính: Mua nồi chiên không dầu dung tích 6 lít ngay hôm nay
-Microcopy: Phù hợp cho gia đình muốn nấu nhanh gọn, có kèm sổ công thức điện tử và thông tin rõ ràng để bạn chọn nhanh.
-Phiên bản 2:
-Lời kêu gọi hành động chính: Chọn nồi chiên không dầu dung tích 6 lít cho nhu cầu hiện tại
-Microcopy: Tập trung vào khay chống dính và hẹn giờ, giúp bạn quyết định dễ hơn.
-Phiên bản 3:
-Lời kêu gọi hành động chính: Nhắn shop để được tư vấn nồi chiên không dầu dung tích 6 lít
-Microcopy: Bạn có thể hỏi thêm về dễ lau chùi và kèm sổ công thức điện tử trước khi quyết định.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Lời kêu gọi hành động chính: Xem nồi chiên không dầu dung tích 6 lít có hợp với bạn không
+Microcopy: Dành cho gia đình muốn nấu nhanh gọn, nổi bật với khay chống dính, hẹn giờ và dễ lau chùi. Có kèm sổ công thức điện tử nếu bạn muốn cân nhắc thêm.
+Phiên bản 2:
+Lời kêu gọi hành động chính: Nhắn shop để chọn nồi chiên không dầu dung tích 6 lít đúng nhu cầu
+Microcopy: Kể nhanh bạn dùng trong bối cảnh nào, shop sẽ gợi ý theo tình huống thật như bữa tối gia đình cần món nhanh, ít phải canh bếp và dễ dọn sau khi ăn.
+Phiên bản 3:
+Lời kêu gọi hành động chính: Lưu nồi chiên không dầu dung tích 6 lít để so sánh trước khi mua
+Microcopy: Phù hợp hơn khi bạn muốn giải quyết chuyện ngại dầu bắn, khay khó rửa hoặc dung tích không đủ cho cả nhà mà vẫn cần một lựa chọn rõ ràng, dễ hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nồi chiên không dầu dung tích 6 lít</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Khẩn cấp.
 Sản phẩm/dịch vụ: balo laptop chống nước.
 Từ khóa chính: ngăn laptop 15 inch; vải chống nước; đệm vai êm.
@@ -1996,24 +2890,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Đừng chần chừ với balo laptop chống nước cho người đi làm di chuyển nhiều với ngăn laptop 15 inch.
-Subheadline: Tập trung vào vải chống nước và đệm vai êm, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: balo laptop chống nước là lựa chọn đáng cân nhắc cho người đi làm di chuyển nhiều.
-Subheadline: Điểm mạnh nằm ở vải chống nước, ngăn laptop 15 inch và miễn phí đổi màu trong 3 ngày để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Giữ nhịp nhanh hơn cho balo laptop chống nước nếu bạn cần ngăn laptop 15 inch và vải chống nước.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>balo laptop chống nước</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: balo laptop chống nước: gọn hơn cho những lúc ngăn laptop 15 inch thật sự quan trọng.
+Subheadline: Dành cho người đi làm di chuyển nhiều, nhất là khi đi làm, đi học hoặc di chuyển qua cơn mưa bất chợt vẫn muốn đồ đạc được sắp xếp gọn. Điểm đáng xem là ngăn laptop 15 inch, vải chống nước và đệm vai êm; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên kiểm tra kích thước laptop và số ngăn cần dùng hằng ngày.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với balo laptop chống nước.
+Subheadline: Nếu bạn từng ngại chuyện sợ laptop va đập nhẹ, giấy tờ ướt hoặc vai đau khi mang lâu, hãy bắt đầu từ ba điểm: ngăn laptop 15 inch, vải chống nước và đệm vai êm. Ưu đãi hiện có: miễn phí đổi màu trong 3 ngày.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn balo laptop chống nước vừa đủ thực tế cho người đi làm di chuyển nhiều.
+Subheadline: Hợp với người thường xuyên di chuyển và cần một chiếc balo nhìn chỉn chu. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Miễn phí đổi màu trong 3 ngày là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">balo laptop chống nước</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
 Sản phẩm/dịch vụ: balo laptop chống nước.
 Từ khóa chính: ngăn laptop 15 inch; vải chống nước; đệm vai êm.
@@ -2036,21 +2942,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Gợi ý dễ dùng cho balo laptop chống nước cho người đi làm di chuyển nhiều với ngăn laptop 15 inch.
-Subheadline: Tập trung vào vải chống nước và đệm vai êm, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: balo laptop chống nước là lựa chọn đáng cân nhắc cho người đi làm di chuyển nhiều.
-Subheadline: Điểm mạnh nằm ở vải chống nước, ngăn laptop 15 inch và miễn phí đổi màu trong 3 ngày để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Thêm tiện lợi cho balo laptop chống nước nếu bạn cần ngăn laptop 15 inch và vải chống nước.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: balo laptop chống nước: gọn hơn cho những lúc ngăn laptop 15 inch thật sự quan trọng.
+Subheadline: Dành cho người đi làm di chuyển nhiều, nhất là khi đi làm, đi học hoặc di chuyển qua cơn mưa bất chợt vẫn muốn đồ đạc được sắp xếp gọn. Điểm đáng xem là ngăn laptop 15 inch, vải chống nước và đệm vai êm; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên kiểm tra kích thước laptop và số ngăn cần dùng hằng ngày.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với balo laptop chống nước.
+Subheadline: Nếu bạn từng ngại chuyện sợ laptop va đập nhẹ, giấy tờ ướt hoặc vai đau khi mang lâu, hãy bắt đầu từ ba điểm: ngăn laptop 15 inch, vải chống nước và đệm vai êm. Ưu đãi hiện có: miễn phí đổi màu trong 3 ngày.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn balo laptop chống nước vừa đủ thực tế cho người đi làm di chuyển nhiều.
+Subheadline: Hợp với người thường xuyên di chuyển và cần một chiếc balo nhìn chỉn chu. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Miễn phí đổi màu trong 3 ngày là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">balo laptop chống nước</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Cảm xúc.
 Sản phẩm/dịch vụ: balo laptop chống nước.
 Từ khóa chính: ngăn laptop 15 inch; vải chống nước; đệm vai êm.
@@ -2074,36 +2995,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Mô tả ngắn: balo laptop chống nước dành cho người đi làm di chuyển nhiều, nhấn vào trải nghiệm dùng rõ ràng và dễ hiểu.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. balo laptop chống nước dành cho người đi làm di chuyển nhiều trong những lúc đi làm, đi học hoặc di chuyển qua cơn mưa bất chợt vẫn muốn đồ đạc được sắp xếp gọn.
 Lợi ích chính:
-- Hỗ trợ nhu cầu thực tế nhờ ngăn laptop 15 inch và vải chống nước.
-- Giúp bạn cân nhắc nhanh hơn với thông tin đúng brief và miễn phí đổi màu trong 3 ngày.
+- Giúp bạn yên tâm hơn với nhu cầu ngăn laptop 15 inch mà không phải đọc quá nhiều thông tin rối.
+- Vải chống nước là điểm cộng rõ ràng khi dùng hằng ngày.
+- Đệm vai êm giúp sản phẩm dễ được đưa vào thói quen hiện có.
 Đặc điểm nổi bật:
-- ngăn laptop 15 inch.
-- đệm vai êm.
-Lời kêu gọi hành động: Xem chi tiết để chọn mẫu phù hợp.
-Phiên bản 2:
-Mô tả ngắn: Nếu bạn là người đi làm di chuyển nhiều, balo laptop chống nước là một lựa chọn gọn gàng, dễ dùng và sát nhu cầu.
+- ngăn laptop 15 inch, vải chống nước và đệm vai êm.
+- Thông tin đi kèm: miễn phí đổi màu trong 3 ngày.
+Góc cần biết: Bạn nên kiểm tra kích thước laptop và số ngăn cần dùng hằng ngày.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì sợ laptop va đập nhẹ, giấy tờ ướt hoặc vai đau khi mang lâu, balo laptop chống nước là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: ngăn laptop 15 inch, vải chống nước và đệm vai êm.
 Lợi ích chính:
-- Mang lại cảm giác yên tâm khi xem thông tin rõ ràng.
-- Tập trung vào vải chống nước và đệm vai êm để phục vụ dùng hằng ngày.
-Đặc điểm nổi bật:
-- vải chống nước.
-- miễn phí đổi màu trong 3 ngày.
-Lời kêu gọi hành động: Nhắn tin để được tư vấn trước khi mua.
-Phiên bản 3:
-Mô tả ngắn: balo laptop chống nước giúp người đi làm di chuyển nhiều có thêm một lựa chọn hợp lý cho nhu cầu thường ngày.
-Lợi ích chính:
-- đệm vai êm làm cho việc dùng tiện hơn.
-- ngăn laptop 15 inch hỗ trợ đúng mối quan tâm chính.
+- Phù hợp với người đi làm di chuyển nhiều muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi miễn phí đổi màu trong 3 ngày giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
 Đặc điểm nổi bật:
 - ngăn laptop 15 inch.
 - vải chống nước.
-Lời kêu gọi hành động: Lưu lại để so sánh khi cần.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+- đệm vai êm.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: balo laptop chống nước hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người thường xuyên di chuyển và cần một chiếc balo nhìn chỉn chu.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin ngăn laptop 15 inch, vải chống nước và đệm vai êm.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: ngăn laptop 15 inch, vải chống nước và đệm vai êm.
+- Ghi chú thêm để cân nhắc: miễn phí đổi màu trong 3 ngày.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emotional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">balo laptop chống nước</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: balo laptop chống nước.
 Từ khóa chính: ngăn laptop 15 inch; vải chống nước; đệm vai êm.
@@ -2127,7 +3067,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. balo laptop chống nước dành cho người đi làm di chuyển nhiều trong những lúc đi làm, đi học hoặc di chuyển qua cơn mưa bất chợt vẫn muốn đồ đạc được sắp xếp gọn.
+Lợi ích chính:
+- Giúp bạn yên tâm hơn với nhu cầu ngăn laptop 15 inch mà không phải đọc quá nhiều thông tin rối.
+- Vải chống nước là điểm cộng rõ ràng khi dùng hằng ngày.
+- Đệm vai êm giúp sản phẩm dễ được đưa vào thói quen hiện có.
+Đặc điểm nổi bật:
+- ngăn laptop 15 inch, vải chống nước và đệm vai êm.
+- Thông tin đi kèm: miễn phí đổi màu trong 3 ngày.
+Góc cần biết: Bạn nên kiểm tra kích thước laptop và số ngăn cần dùng hằng ngày.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì sợ laptop va đập nhẹ, giấy tờ ướt hoặc vai đau khi mang lâu, balo laptop chống nước là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: ngăn laptop 15 inch, vải chống nước và đệm vai êm.
+Lợi ích chính:
+- Phù hợp với người đi làm di chuyển nhiều muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi miễn phí đổi màu trong 3 ngày giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
+Đặc điểm nổi bật:
+- ngăn laptop 15 inch.
+- vải chống nước.
+- đệm vai êm.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: balo laptop chống nước hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người thường xuyên di chuyển và cần một chiếc balo nhìn chỉn chu.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin ngăn laptop 15 inch, vải chống nước và đệm vai êm.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: ngăn laptop 15 inch, vải chống nước và đệm vai êm.
+- Ghi chú thêm để cân nhắc: miễn phí đổi màu trong 3 ngày.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">balo laptop chống nước</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Thân thiện.
 Sản phẩm/dịch vụ: balo laptop chống nước.
 Từ khóa chính: ngăn laptop 15 inch; vải chống nước; đệm vai êm.
@@ -2151,24 +3139,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Một lựa chọn thân thiện cho người đi làm di chuyển nhiều.
-Caption: balo laptop chống nước giúp việc hằng ngày nhẹ hơn nhờ ngăn laptop 15 inch, vải chống nước và đệm vai êm. Hiện có miễn phí đổi màu trong 3 ngày, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #BaloLaptopChong #NguoiDiLam #NganLaptop15
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của người đi làm di chuyển nhiều.
-Caption: Với vải chống nước và đệm vai êm, balo laptop chống nước cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. miễn phí đổi màu trong 3 ngày là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #BaloLaptopChong #VaiChongNuoc #MuaSamThongMinh
-Phiên bản 3:
-Hook: Gợi ý dễ dùng cho người đi làm di chuyển nhiều một lựa chọn gọn gàng hơn.
-Caption: Khi xem balo laptop chống nước, hãy chú ý vào ngăn laptop 15 inch, vải chống nước và đệm vai êm. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #BaloLaptopChong #DemVaiEm #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Một món nhỏ, nhưng dùng đúng lúc thì thấy ngày nhẹ hơn một chút.
+Caption: balo laptop chống nước dành cho người đi làm di chuyển nhiều trong những lúc đi làm, đi học hoặc di chuyển qua cơn mưa bất chợt vẫn muốn đồ đạc được sắp xếp gọn. Mình sẽ nhìn vào ngăn laptop 15 inch, vải chống nước và đệm vai êm trước, rồi mới xét đến ưu đãi miễn phí đổi màu trong 3 ngày. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên kiểm tra kích thước laptop và số ngăn cần dùng hằng ngày.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #BaloLaptop #DiLamMoiNgay #ChongNuoc
+Phiên bản 2:
+Hook: Mua sắm dễ chịu hơn khi thông tin đủ rõ và không bị thúc ép.
+Caption: Nếu bạn từng gặp chuyện sợ laptop va đập nhẹ, giấy tờ ướt hoặc vai đau khi mang lâu, balo laptop chống nước là một lựa chọn đáng để lưu lại. Sản phẩm có ngăn laptop 15 inch, vải chống nước và đệm vai êm, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Miễn phí đổi màu trong 3 ngày là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #BaloLaptop #DiLamMoiNgay #ChongNuoc
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với balo laptop chống nước, hãy bắt đầu từ nhu cầu của người đi làm di chuyển nhiều: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm ngăn laptop 15 inch, vải chống nước và đệm vai êm khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người thường xuyên di chuyển và cần một chiếc balo nhìn chỉn chu.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #BaloLaptop #DiLamMoiNgay #ChongNuoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">balo laptop chống nước</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Khẩn cấp.
 Sản phẩm/dịch vụ: balo laptop chống nước.
 Từ khóa chính: ngăn laptop 15 inch; vải chống nước; đệm vai êm.
@@ -2192,24 +3195,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Cần xem ngay cho người đi làm di chuyển nhiều.
-Caption: balo laptop chống nước giúp việc hằng ngày nhẹ hơn nhờ ngăn laptop 15 inch, vải chống nước và đệm vai êm. Hiện có miễn phí đổi màu trong 3 ngày, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #BaloLaptopChong #NguoiDiLam #NganLaptop15
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của người đi làm di chuyển nhiều.
-Caption: Với vải chống nước và đệm vai êm, balo laptop chống nước cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. miễn phí đổi màu trong 3 ngày là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #BaloLaptopChong #VaiChongNuoc #MuaSamThongMinh
-Phiên bản 3:
-Hook: Đừng chần chừ với người đi làm di chuyển nhiều một lựa chọn gọn gàng hơn.
-Caption: Khi xem balo laptop chống nước, hãy chú ý vào ngăn laptop 15 inch, vải chống nước và đệm vai êm. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #BaloLaptopChong #DemVaiEm #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Đang cân nhắc thì nên xem kỹ hôm nay, nhưng không cần mua vội.
+Caption: balo laptop chống nước dành cho người đi làm di chuyển nhiều trong những lúc đi làm, đi học hoặc di chuyển qua cơn mưa bất chợt vẫn muốn đồ đạc được sắp xếp gọn. Mình sẽ nhìn vào ngăn laptop 15 inch, vải chống nước và đệm vai êm trước, rồi mới xét đến ưu đãi miễn phí đổi màu trong 3 ngày. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên kiểm tra kích thước laptop và số ngăn cần dùng hằng ngày.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #BaloLaptop #DiLamMoiNgay #ChongNuoc
+Phiên bản 2:
+Hook: Ưu đãi chỉ đáng giữ lại khi sản phẩm thật sự hợp với cách bạn dùng.
+Caption: Nếu bạn từng gặp chuyện sợ laptop va đập nhẹ, giấy tờ ướt hoặc vai đau khi mang lâu, balo laptop chống nước là một lựa chọn đáng để lưu lại. Sản phẩm có ngăn laptop 15 inch, vải chống nước và đệm vai êm, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Miễn phí đổi màu trong 3 ngày là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #BaloLaptop #DiLamMoiNgay #ChongNuoc
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với balo laptop chống nước, hãy bắt đầu từ nhu cầu của người đi làm di chuyển nhiều: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm ngăn laptop 15 inch, vải chống nước và đệm vai êm khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người thường xuyên di chuyển và cần một chiếc balo nhìn chỉn chu.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #BaloLaptop #DiLamMoiNgay #ChongNuoc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">balo laptop chống nước</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Email Marketing với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: balo laptop chống nước.
 Từ khóa chính: ngăn laptop 15 inch; vải chống nước; đệm vai êm.
@@ -2234,27 +3252,45 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Subject: Gợi ý balo laptop chống nước cho người đi làm di chuyển nhiều
-Preview text: Tóm tắt nhanh các điểm đáng cân nhắc trước khi chọn mua.
+    <t xml:space="preserve">Phiên bản 1:
+Subject: Gợi ý balo laptop chống nước cho nhu cầu dùng hằng ngày
+Preview text: Một vài điểm đáng xem trước khi bạn quyết định.
 Lời chào: Chào bạn,
-Nội dung chính: Nếu bạn đang tìm một lựa chọn phù hợp cho nhu cầu hằng ngày, balo laptop chống nước có các điểm nổi bật như ngăn laptop 15 inch, vải chống nước và đệm vai êm. Hiện có miễn phí đổi màu trong 3 ngày, nên bạn có thể xem thêm thông tin trước khi quyết định.
-Lời kêu gọi hành động: Xem chi tiết sản phẩm hôm nay.
-Phiên bản 2:
-Subject: balo laptop chống nước có thể hợp với nhu cầu của bạn
-Preview text: Một vài lý do để người đi làm di chuyển nhiều cân nhắc sản phẩm này.
+Nội dung chính: Nếu bạn là người đi làm di chuyển nhiều, có lẽ điều bạn cần không phải một lời giới thiệu quá mạnh. Bạn cần biết balo laptop chống nước có hợp với bối cảnh đi làm, đi học hoặc di chuyển qua cơn mưa bất chợt vẫn muốn đồ đạc được sắp xếp gọn hay không.
+Sản phẩm này đáng xem nhờ ngăn laptop 15 inch, vải chống nước và đệm vai êm. Trong đó, ngăn laptop 15 inch giúp xử lý nhu cầu chính; vải chống nước và đệm vai êm làm trải nghiệm dùng trọn vẹn hơn.
+Góc cần biết: Bạn nên kiểm tra kích thước laptop và số ngăn cần dùng hằng ngày. Hiện có miễn phí đổi màu trong 3 ngày, bạn có thể xem như một điểm cộng nếu sản phẩm đã đúng nhu cầu.
+Lời kêu gọi hành động: Mở chi tiết sản phẩm hoặc nhắn shop để được tư vấn kỹ hơn.
+Phiên bản 2:
+Subject: Trước khi mua balo laptop chống nước, bạn có thể xem nhanh điểm này
+Preview text: Chọn chắc hơn khi biết sản phẩm giải quyết đúng việc gì.
 Lời chào: Chào bạn,
-Nội dung chính: balo laptop chống nước tập trung vào vải chống nước, ngăn laptop 15 inch và đệm vai êm. Thông tin được viết theo đúng brief, không thêm chứng nhận hay số liệu ngoài phạm vi. miễn phí đổi màu trong 3 ngày giúp bạn có thêm lý do so sánh.
-Lời kêu gọi hành động: Nhắn lại để được tư vấn lựa chọn phù hợp.
-Phiên bản 3:
-Subject: Xem nhanh balo laptop chống nước trước khi bạn chọn
-Preview text: Thông tin ngắn gọn, dễ so sánh và có ưu đãi đi kèm.
+Nội dung chính: Nhiều người phân vân vì sợ laptop va đập nhẹ, giấy tờ ướt hoặc vai đau khi mang lâu. Vì vậy, với balo laptop chống nước, hãy nhìn vào nhu cầu thật trước: bạn cần ngăn laptop 15 inch, muốn vải chống nước, hay quan tâm nhiều hơn đến đệm vai êm?
+Nếu câu trả lời khớp với cách bạn dùng hằng ngày, đây là lựa chọn đáng cân nhắc. Nếu chưa chắc, bạn có thể hỏi shop trước khi đặt.
+Góc cần biết: Miễn phí đổi màu trong 3 ngày đang đi kèm, nhưng quyết định cuối cùng vẫn nên dựa trên mức độ phù hợp.
+Lời kêu gọi hành động: Trả lời tin nhắn này với nhu cầu của bạn, shop sẽ gợi ý cụ thể hơn.
+Phiên bản 3:
+Subject: balo laptop chống nước có thể là món bạn đang tìm
+Preview text: Rõ lợi ích, rõ tình huống dùng, không cần quyết định vội.
 Lời chào: Chào bạn,
-Nội dung chính: Với người đi làm di chuyển nhiều, một sản phẩm dễ hiểu thường giúp quyết định nhanh hơn. balo laptop chống nước có ngăn laptop 15 inch, vải chống nước và đệm vai êm; ngoài ra còn có miễn phí đổi màu trong 3 ngày để bạn cân nhắc thêm.
-Lời kêu gọi hành động: Mở trang sản phẩm để xem thêm chi tiết.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Nội dung chính: Hợp với người thường xuyên di chuyển và cần một chiếc balo nhìn chỉn chu. balo laptop chống nước tập trung vào ngăn laptop 15 inch, vải chống nước và đệm vai êm, phù hợp với người đi làm di chuyển nhiều khi muốn một lựa chọn thực tế hơn cho sinh hoạt hằng ngày.
+Bạn có thể cân nhắc sản phẩm này nếu đang cần giải quyết chuyện sợ laptop va đập nhẹ, giấy tờ ướt hoặc vai đau khi mang lâu. Còn nếu muốn chắc hơn, hãy hỏi shop về tình huống dùng của bạn.
+Góc cần biết: Bạn nên kiểm tra kích thước laptop và số ngăn cần dùng hằng ngày.
+Lời kêu gọi hành động: Xem chi tiết hoặc nhắn shop trước khi chốt đơn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">balo laptop chống nước</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Lời Kêu Gọi Hành Động với tone Thân thiện.
 Sản phẩm/dịch vụ: balo laptop chống nước.
 Từ khóa chính: ngăn laptop 15 inch; vải chống nước; đệm vai êm.
@@ -2276,18 +3312,30 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Lời kêu gọi hành động chính: Mua balo laptop chống nước ngay hôm nay
-Microcopy: Phù hợp cho người đi làm di chuyển nhiều, có miễn phí đổi màu trong 3 ngày và thông tin rõ ràng để bạn chọn nhanh.
-Phiên bản 2:
-Lời kêu gọi hành động chính: Chọn balo laptop chống nước cho nhu cầu hiện tại
-Microcopy: Tập trung vào ngăn laptop 15 inch và vải chống nước, giúp bạn quyết định dễ hơn.
-Phiên bản 3:
-Lời kêu gọi hành động chính: Nhắn shop để được tư vấn balo laptop chống nước
-Microcopy: Bạn có thể hỏi thêm về đệm vai êm và miễn phí đổi màu trong 3 ngày trước khi quyết định.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Lời kêu gọi hành động chính: Xem balo laptop chống nước có hợp với bạn không
+Microcopy: Dành cho người đi làm di chuyển nhiều, nổi bật với ngăn laptop 15 inch, vải chống nước và đệm vai êm. Có miễn phí đổi màu trong 3 ngày nếu bạn muốn cân nhắc thêm.
+Phiên bản 2:
+Lời kêu gọi hành động chính: Nhắn shop để chọn balo laptop chống nước đúng nhu cầu
+Microcopy: Kể nhanh bạn dùng trong bối cảnh nào, shop sẽ gợi ý theo tình huống thật như đi làm, đi học hoặc di chuyển qua cơn mưa bất chợt vẫn muốn đồ đạc được sắp xếp gọn.
+Phiên bản 3:
+Lời kêu gọi hành động chính: Lưu balo laptop chống nước để so sánh trước khi mua
+Microcopy: Phù hợp hơn khi bạn muốn giải quyết chuyện sợ laptop va đập nhẹ, giấy tờ ướt hoặc vai đau khi mang lâu mà vẫn cần một lựa chọn rõ ràng, dễ hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">balo laptop chống nước</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Khẩn cấp.
 Sản phẩm/dịch vụ: tai nghe không dây chống ồn.
 Từ khóa chính: chống ồn chủ động; pin 30 giờ; micro rõ.
@@ -2310,24 +3358,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Đừng chần chừ với tai nghe không dây chống ồn cho người cần tập trung khi làm việc với chống ồn chủ động.
-Subheadline: Tập trung vào pin 30 giờ và micro rõ, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: tai nghe không dây chống ồn là lựa chọn đáng cân nhắc cho người cần tập trung khi làm việc.
-Subheadline: Điểm mạnh nằm ở pin 30 giờ, chống ồn chủ động và bảo hành chính hãng 12 tháng để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Giữ nhịp nhanh hơn cho tai nghe không dây chống ồn nếu bạn cần chống ồn chủ động và pin 30 giờ.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>tai nghe không dây chống ồn</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: tai nghe không dây chống ồn: gọn hơn cho những lúc chống ồn chủ động thật sự quan trọng.
+Subheadline: Dành cho người cần tập trung khi làm việc, nhất là khi quán cà phê, văn phòng mở hoặc chuyến xe đông người cần một khoảng tập trung riêng. Điểm đáng xem là chống ồn chủ động, pin 30 giờ và micro rõ; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên cân nhắc thời lượng pin, micro và cảm giác đeo lâu.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với tai nghe không dây chống ồn.
+Subheadline: Nếu bạn từng ngại chuyện ngại tiếng ồn chen vào cuộc gọi hoặc pin không đủ cho ngày dài, hãy bắt đầu từ ba điểm: chống ồn chủ động, pin 30 giờ và micro rõ. Ưu đãi hiện có: bảo hành chính hãng 12 tháng.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn tai nghe không dây chống ồn vừa đủ thực tế cho người cần tập trung khi làm việc.
+Subheadline: Hợp với người làm việc linh hoạt, cần nghe rõ và nói rõ hơn trong nhiều bối cảnh. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Bảo hành chính hãng 12 tháng là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tai nghe không dây chống ồn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
 Sản phẩm/dịch vụ: tai nghe không dây chống ồn.
 Từ khóa chính: chống ồn chủ động; pin 30 giờ; micro rõ.
@@ -2350,21 +3410,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Gợi ý dễ dùng cho tai nghe không dây chống ồn cho người cần tập trung khi làm việc với chống ồn chủ động.
-Subheadline: Tập trung vào pin 30 giờ và micro rõ, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: tai nghe không dây chống ồn là lựa chọn đáng cân nhắc cho người cần tập trung khi làm việc.
-Subheadline: Điểm mạnh nằm ở pin 30 giờ, chống ồn chủ động và bảo hành chính hãng 12 tháng để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Thêm tiện lợi cho tai nghe không dây chống ồn nếu bạn cần chống ồn chủ động và pin 30 giờ.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: tai nghe không dây chống ồn: gọn hơn cho những lúc chống ồn chủ động thật sự quan trọng.
+Subheadline: Dành cho người cần tập trung khi làm việc, nhất là khi quán cà phê, văn phòng mở hoặc chuyến xe đông người cần một khoảng tập trung riêng. Điểm đáng xem là chống ồn chủ động, pin 30 giờ và micro rõ; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên cân nhắc thời lượng pin, micro và cảm giác đeo lâu.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với tai nghe không dây chống ồn.
+Subheadline: Nếu bạn từng ngại chuyện ngại tiếng ồn chen vào cuộc gọi hoặc pin không đủ cho ngày dài, hãy bắt đầu từ ba điểm: chống ồn chủ động, pin 30 giờ và micro rõ. Ưu đãi hiện có: bảo hành chính hãng 12 tháng.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn tai nghe không dây chống ồn vừa đủ thực tế cho người cần tập trung khi làm việc.
+Subheadline: Hợp với người làm việc linh hoạt, cần nghe rõ và nói rõ hơn trong nhiều bối cảnh. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Bảo hành chính hãng 12 tháng là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tai nghe không dây chống ồn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Cảm xúc.
 Sản phẩm/dịch vụ: tai nghe không dây chống ồn.
 Từ khóa chính: chống ồn chủ động; pin 30 giờ; micro rõ.
@@ -2388,36 +3463,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Mô tả ngắn: tai nghe không dây chống ồn dành cho người cần tập trung khi làm việc, nhấn vào trải nghiệm dùng rõ ràng và dễ hiểu.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. tai nghe không dây chống ồn dành cho người cần tập trung khi làm việc trong những lúc quán cà phê, văn phòng mở hoặc chuyến xe đông người cần một khoảng tập trung riêng.
 Lợi ích chính:
-- Hỗ trợ nhu cầu thực tế nhờ chống ồn chủ động và pin 30 giờ.
-- Giúp bạn cân nhắc nhanh hơn với thông tin đúng brief và bảo hành chính hãng 12 tháng.
+- Giúp bạn yên tâm hơn với nhu cầu chống ồn chủ động mà không phải đọc quá nhiều thông tin rối.
+- Pin 30 giờ là điểm cộng rõ ràng khi dùng hằng ngày.
+- Micro rõ giúp sản phẩm dễ được đưa vào thói quen hiện có.
 Đặc điểm nổi bật:
-- chống ồn chủ động.
-- micro rõ.
-Lời kêu gọi hành động: Xem chi tiết để chọn mẫu phù hợp.
-Phiên bản 2:
-Mô tả ngắn: Nếu bạn là người cần tập trung khi làm việc, tai nghe không dây chống ồn là một lựa chọn gọn gàng, dễ dùng và sát nhu cầu.
+- chống ồn chủ động, pin 30 giờ và micro rõ.
+- Thông tin đi kèm: bảo hành chính hãng 12 tháng.
+Góc cần biết: Bạn nên cân nhắc thời lượng pin, micro và cảm giác đeo lâu.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì ngại tiếng ồn chen vào cuộc gọi hoặc pin không đủ cho ngày dài, tai nghe không dây chống ồn là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: chống ồn chủ động, pin 30 giờ và micro rõ.
 Lợi ích chính:
-- Mang lại cảm giác yên tâm khi xem thông tin rõ ràng.
-- Tập trung vào pin 30 giờ và micro rõ để phục vụ dùng hằng ngày.
-Đặc điểm nổi bật:
-- pin 30 giờ.
-- bảo hành chính hãng 12 tháng.
-Lời kêu gọi hành động: Nhắn tin để được tư vấn trước khi mua.
-Phiên bản 3:
-Mô tả ngắn: tai nghe không dây chống ồn giúp người cần tập trung khi làm việc có thêm một lựa chọn hợp lý cho nhu cầu thường ngày.
-Lợi ích chính:
-- micro rõ làm cho việc dùng tiện hơn.
-- chống ồn chủ động hỗ trợ đúng mối quan tâm chính.
+- Phù hợp với người cần tập trung khi làm việc muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi bảo hành chính hãng 12 tháng giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
 Đặc điểm nổi bật:
 - chống ồn chủ động.
 - pin 30 giờ.
-Lời kêu gọi hành động: Lưu lại để so sánh khi cần.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+- micro rõ.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: tai nghe không dây chống ồn hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người làm việc linh hoạt, cần nghe rõ và nói rõ hơn trong nhiều bối cảnh.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin chống ồn chủ động, pin 30 giờ và micro rõ.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: chống ồn chủ động, pin 30 giờ và micro rõ.
+- Ghi chú thêm để cân nhắc: bảo hành chính hãng 12 tháng.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emotional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tai nghe không dây chống ồn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: tai nghe không dây chống ồn.
 Từ khóa chính: chống ồn chủ động; pin 30 giờ; micro rõ.
@@ -2441,7 +3535,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. tai nghe không dây chống ồn dành cho người cần tập trung khi làm việc trong những lúc quán cà phê, văn phòng mở hoặc chuyến xe đông người cần một khoảng tập trung riêng.
+Lợi ích chính:
+- Giúp bạn yên tâm hơn với nhu cầu chống ồn chủ động mà không phải đọc quá nhiều thông tin rối.
+- Pin 30 giờ là điểm cộng rõ ràng khi dùng hằng ngày.
+- Micro rõ giúp sản phẩm dễ được đưa vào thói quen hiện có.
+Đặc điểm nổi bật:
+- chống ồn chủ động, pin 30 giờ và micro rõ.
+- Thông tin đi kèm: bảo hành chính hãng 12 tháng.
+Góc cần biết: Bạn nên cân nhắc thời lượng pin, micro và cảm giác đeo lâu.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì ngại tiếng ồn chen vào cuộc gọi hoặc pin không đủ cho ngày dài, tai nghe không dây chống ồn là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: chống ồn chủ động, pin 30 giờ và micro rõ.
+Lợi ích chính:
+- Phù hợp với người cần tập trung khi làm việc muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi bảo hành chính hãng 12 tháng giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
+Đặc điểm nổi bật:
+- chống ồn chủ động.
+- pin 30 giờ.
+- micro rõ.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: tai nghe không dây chống ồn hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người làm việc linh hoạt, cần nghe rõ và nói rõ hơn trong nhiều bối cảnh.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin chống ồn chủ động, pin 30 giờ và micro rõ.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: chống ồn chủ động, pin 30 giờ và micro rõ.
+- Ghi chú thêm để cân nhắc: bảo hành chính hãng 12 tháng.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tai nghe không dây chống ồn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Thân thiện.
 Sản phẩm/dịch vụ: tai nghe không dây chống ồn.
 Từ khóa chính: chống ồn chủ động; pin 30 giờ; micro rõ.
@@ -2465,24 +3607,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Một lựa chọn thân thiện cho người cần tập trung khi làm việc.
-Caption: tai nghe không dây chống ồn giúp việc hằng ngày nhẹ hơn nhờ chống ồn chủ động, pin 30 giờ và micro rõ. Hiện có bảo hành chính hãng 12 tháng, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #TaiNgheKhong #NguoiCanTap #ChongOnChu
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của người cần tập trung khi làm việc.
-Caption: Với pin 30 giờ và micro rõ, tai nghe không dây chống ồn cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. bảo hành chính hãng 12 tháng là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #TaiNgheKhong #Pin30Gio #MuaSamThongMinh
-Phiên bản 3:
-Hook: Gợi ý dễ dùng cho người cần tập trung khi làm việc một lựa chọn gọn gàng hơn.
-Caption: Khi xem tai nghe không dây chống ồn, hãy chú ý vào chống ồn chủ động, pin 30 giờ và micro rõ. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #TaiNgheKhong #MicroRo #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Một món nhỏ, nhưng dùng đúng lúc thì thấy ngày nhẹ hơn một chút.
+Caption: tai nghe không dây chống ồn dành cho người cần tập trung khi làm việc trong những lúc quán cà phê, văn phòng mở hoặc chuyến xe đông người cần một khoảng tập trung riêng. Mình sẽ nhìn vào chống ồn chủ động, pin 30 giờ và micro rõ trước, rồi mới xét đến ưu đãi bảo hành chính hãng 12 tháng. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên cân nhắc thời lượng pin, micro và cảm giác đeo lâu.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #TaiNgheKhongDay #TapTrungLamViec #ChongOn
+Phiên bản 2:
+Hook: Mua sắm dễ chịu hơn khi thông tin đủ rõ và không bị thúc ép.
+Caption: Nếu bạn từng gặp chuyện ngại tiếng ồn chen vào cuộc gọi hoặc pin không đủ cho ngày dài, tai nghe không dây chống ồn là một lựa chọn đáng để lưu lại. Sản phẩm có chống ồn chủ động, pin 30 giờ và micro rõ, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Bảo hành chính hãng 12 tháng là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #TaiNgheKhongDay #TapTrungLamViec #ChongOn
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với tai nghe không dây chống ồn, hãy bắt đầu từ nhu cầu của người cần tập trung khi làm việc: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm chống ồn chủ động, pin 30 giờ và micro rõ khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người làm việc linh hoạt, cần nghe rõ và nói rõ hơn trong nhiều bối cảnh.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #TaiNgheKhongDay #TapTrungLamViec #ChongOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tai nghe không dây chống ồn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Khẩn cấp.
 Sản phẩm/dịch vụ: tai nghe không dây chống ồn.
 Từ khóa chính: chống ồn chủ động; pin 30 giờ; micro rõ.
@@ -2506,24 +3663,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Cần xem ngay cho người cần tập trung khi làm việc.
-Caption: tai nghe không dây chống ồn giúp việc hằng ngày nhẹ hơn nhờ chống ồn chủ động, pin 30 giờ và micro rõ. Hiện có bảo hành chính hãng 12 tháng, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #TaiNgheKhong #NguoiCanTap #ChongOnChu
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của người cần tập trung khi làm việc.
-Caption: Với pin 30 giờ và micro rõ, tai nghe không dây chống ồn cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. bảo hành chính hãng 12 tháng là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #TaiNgheKhong #Pin30Gio #MuaSamThongMinh
-Phiên bản 3:
-Hook: Đừng chần chừ với người cần tập trung khi làm việc một lựa chọn gọn gàng hơn.
-Caption: Khi xem tai nghe không dây chống ồn, hãy chú ý vào chống ồn chủ động, pin 30 giờ và micro rõ. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #TaiNgheKhong #MicroRo #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Đang cân nhắc thì nên xem kỹ hôm nay, nhưng không cần mua vội.
+Caption: tai nghe không dây chống ồn dành cho người cần tập trung khi làm việc trong những lúc quán cà phê, văn phòng mở hoặc chuyến xe đông người cần một khoảng tập trung riêng. Mình sẽ nhìn vào chống ồn chủ động, pin 30 giờ và micro rõ trước, rồi mới xét đến ưu đãi bảo hành chính hãng 12 tháng. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên cân nhắc thời lượng pin, micro và cảm giác đeo lâu.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #TaiNgheKhongDay #TapTrungLamViec #ChongOn
+Phiên bản 2:
+Hook: Ưu đãi chỉ đáng giữ lại khi sản phẩm thật sự hợp với cách bạn dùng.
+Caption: Nếu bạn từng gặp chuyện ngại tiếng ồn chen vào cuộc gọi hoặc pin không đủ cho ngày dài, tai nghe không dây chống ồn là một lựa chọn đáng để lưu lại. Sản phẩm có chống ồn chủ động, pin 30 giờ và micro rõ, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Bảo hành chính hãng 12 tháng là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #TaiNgheKhongDay #TapTrungLamViec #ChongOn
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với tai nghe không dây chống ồn, hãy bắt đầu từ nhu cầu của người cần tập trung khi làm việc: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm chống ồn chủ động, pin 30 giờ và micro rõ khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người làm việc linh hoạt, cần nghe rõ và nói rõ hơn trong nhiều bối cảnh.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #TaiNgheKhongDay #TapTrungLamViec #ChongOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tai nghe không dây chống ồn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Email Marketing với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: tai nghe không dây chống ồn.
 Từ khóa chính: chống ồn chủ động; pin 30 giờ; micro rõ.
@@ -2548,27 +3720,45 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Subject: Gợi ý tai nghe không dây chống ồn cho người cần tập trung khi làm việc
-Preview text: Tóm tắt nhanh các điểm đáng cân nhắc trước khi chọn mua.
+    <t xml:space="preserve">Phiên bản 1:
+Subject: Gợi ý tai nghe không dây chống ồn cho nhu cầu dùng hằng ngày
+Preview text: Một vài điểm đáng xem trước khi bạn quyết định.
 Lời chào: Chào bạn,
-Nội dung chính: Nếu bạn đang tìm một lựa chọn phù hợp cho nhu cầu hằng ngày, tai nghe không dây chống ồn có các điểm nổi bật như chống ồn chủ động, pin 30 giờ và micro rõ. Hiện có bảo hành chính hãng 12 tháng, nên bạn có thể xem thêm thông tin trước khi quyết định.
-Lời kêu gọi hành động: Xem chi tiết sản phẩm hôm nay.
-Phiên bản 2:
-Subject: tai nghe không dây chống ồn có thể hợp với nhu cầu của bạn
-Preview text: Một vài lý do để người cần tập trung khi làm việc cân nhắc sản phẩm này.
+Nội dung chính: Nếu bạn là người cần tập trung khi làm việc, có lẽ điều bạn cần không phải một lời giới thiệu quá mạnh. Bạn cần biết tai nghe không dây chống ồn có hợp với bối cảnh quán cà phê, văn phòng mở hoặc chuyến xe đông người cần một khoảng tập trung riêng hay không.
+Sản phẩm này đáng xem nhờ chống ồn chủ động, pin 30 giờ và micro rõ. Trong đó, chống ồn chủ động giúp xử lý nhu cầu chính; pin 30 giờ và micro rõ làm trải nghiệm dùng trọn vẹn hơn.
+Góc cần biết: Bạn nên cân nhắc thời lượng pin, micro và cảm giác đeo lâu. Hiện có bảo hành chính hãng 12 tháng, bạn có thể xem như một điểm cộng nếu sản phẩm đã đúng nhu cầu.
+Lời kêu gọi hành động: Mở chi tiết sản phẩm hoặc nhắn shop để được tư vấn kỹ hơn.
+Phiên bản 2:
+Subject: Trước khi mua tai nghe không dây chống ồn, bạn có thể xem nhanh điểm này
+Preview text: Chọn chắc hơn khi biết sản phẩm giải quyết đúng việc gì.
 Lời chào: Chào bạn,
-Nội dung chính: tai nghe không dây chống ồn tập trung vào pin 30 giờ, chống ồn chủ động và micro rõ. Thông tin được viết theo đúng brief, không thêm chứng nhận hay số liệu ngoài phạm vi. bảo hành chính hãng 12 tháng giúp bạn có thêm lý do so sánh.
-Lời kêu gọi hành động: Nhắn lại để được tư vấn lựa chọn phù hợp.
-Phiên bản 3:
-Subject: Xem nhanh tai nghe không dây chống ồn trước khi bạn chọn
-Preview text: Thông tin ngắn gọn, dễ so sánh và có ưu đãi đi kèm.
+Nội dung chính: Nhiều người phân vân vì ngại tiếng ồn chen vào cuộc gọi hoặc pin không đủ cho ngày dài. Vì vậy, với tai nghe không dây chống ồn, hãy nhìn vào nhu cầu thật trước: bạn cần chống ồn chủ động, muốn pin 30 giờ, hay quan tâm nhiều hơn đến micro rõ?
+Nếu câu trả lời khớp với cách bạn dùng hằng ngày, đây là lựa chọn đáng cân nhắc. Nếu chưa chắc, bạn có thể hỏi shop trước khi đặt.
+Góc cần biết: Bảo hành chính hãng 12 tháng đang đi kèm, nhưng quyết định cuối cùng vẫn nên dựa trên mức độ phù hợp.
+Lời kêu gọi hành động: Trả lời tin nhắn này với nhu cầu của bạn, shop sẽ gợi ý cụ thể hơn.
+Phiên bản 3:
+Subject: tai nghe không dây chống ồn có thể là món bạn đang tìm
+Preview text: Rõ lợi ích, rõ tình huống dùng, không cần quyết định vội.
 Lời chào: Chào bạn,
-Nội dung chính: Với người cần tập trung khi làm việc, một sản phẩm dễ hiểu thường giúp quyết định nhanh hơn. tai nghe không dây chống ồn có chống ồn chủ động, pin 30 giờ và micro rõ; ngoài ra còn có bảo hành chính hãng 12 tháng để bạn cân nhắc thêm.
-Lời kêu gọi hành động: Mở trang sản phẩm để xem thêm chi tiết.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Nội dung chính: Hợp với người làm việc linh hoạt, cần nghe rõ và nói rõ hơn trong nhiều bối cảnh. tai nghe không dây chống ồn tập trung vào chống ồn chủ động, pin 30 giờ và micro rõ, phù hợp với người cần tập trung khi làm việc khi muốn một lựa chọn thực tế hơn cho sinh hoạt hằng ngày.
+Bạn có thể cân nhắc sản phẩm này nếu đang cần giải quyết chuyện ngại tiếng ồn chen vào cuộc gọi hoặc pin không đủ cho ngày dài. Còn nếu muốn chắc hơn, hãy hỏi shop về tình huống dùng của bạn.
+Góc cần biết: Bạn nên cân nhắc thời lượng pin, micro và cảm giác đeo lâu.
+Lời kêu gọi hành động: Xem chi tiết hoặc nhắn shop trước khi chốt đơn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tai nghe không dây chống ồn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Lời Kêu Gọi Hành Động với tone Thân thiện.
 Sản phẩm/dịch vụ: tai nghe không dây chống ồn.
 Từ khóa chính: chống ồn chủ động; pin 30 giờ; micro rõ.
@@ -2590,18 +3780,30 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Lời kêu gọi hành động chính: Mua tai nghe không dây chống ồn ngay hôm nay
-Microcopy: Phù hợp cho người cần tập trung khi làm việc, có bảo hành chính hãng 12 tháng và thông tin rõ ràng để bạn chọn nhanh.
-Phiên bản 2:
-Lời kêu gọi hành động chính: Chọn tai nghe không dây chống ồn cho nhu cầu hiện tại
-Microcopy: Tập trung vào chống ồn chủ động và pin 30 giờ, giúp bạn quyết định dễ hơn.
-Phiên bản 3:
-Lời kêu gọi hành động chính: Nhắn shop để được tư vấn tai nghe không dây chống ồn
-Microcopy: Bạn có thể hỏi thêm về micro rõ và bảo hành chính hãng 12 tháng trước khi quyết định.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Lời kêu gọi hành động chính: Xem tai nghe không dây chống ồn có hợp với bạn không
+Microcopy: Dành cho người cần tập trung khi làm việc, nổi bật với chống ồn chủ động, pin 30 giờ và micro rõ. Có bảo hành chính hãng 12 tháng nếu bạn muốn cân nhắc thêm.
+Phiên bản 2:
+Lời kêu gọi hành động chính: Nhắn shop để chọn tai nghe không dây chống ồn đúng nhu cầu
+Microcopy: Kể nhanh bạn dùng trong bối cảnh nào, shop sẽ gợi ý theo tình huống thật như quán cà phê, văn phòng mở hoặc chuyến xe đông người cần một khoảng tập trung riêng.
+Phiên bản 3:
+Lời kêu gọi hành động chính: Lưu tai nghe không dây chống ồn để so sánh trước khi mua
+Microcopy: Phù hợp hơn khi bạn muốn giải quyết chuyện ngại tiếng ồn chen vào cuộc gọi hoặc pin không đủ cho ngày dài mà vẫn cần một lựa chọn rõ ràng, dễ hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tai nghe không dây chống ồn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Khẩn cấp.
 Sản phẩm/dịch vụ: khóa cửa thông minh.
 Từ khóa chính: mở bằng vân tay; mã số tạm thời; cảnh báo pin yếu.
@@ -2624,24 +3826,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Đừng chần chừ với khóa cửa thông minh cho chủ căn hộ muốn kiểm soát ra vào với mở bằng vân tay.
-Subheadline: Tập trung vào mã số tạm thời và cảnh báo pin yếu, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: khóa cửa thông minh là lựa chọn đáng cân nhắc cho chủ căn hộ muốn kiểm soát ra vào.
-Subheadline: Điểm mạnh nằm ở mã số tạm thời, mở bằng vân tay và lắp đặt ưu đãi trong nội thành để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Giữ nhịp nhanh hơn cho khóa cửa thông minh nếu bạn cần mở bằng vân tay và mã số tạm thời.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>khóa cửa thông minh</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: khóa cửa thông minh: gọn hơn cho những lúc mở bằng vân tay thật sự quan trọng.
+Subheadline: Dành cho chủ căn hộ muốn kiểm soát ra vào, nhất là khi ra vào căn hộ nhiều lần trong ngày, có lúc cần gửi mã tạm cho người thân hoặc khách. Điểm đáng xem là mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên hỏi kỹ loại cửa, phương án lắp đặt và cách xử lý khi pin yếu.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với khóa cửa thông minh.
+Subheadline: Nếu bạn từng ngại chuyện sợ quên chìa, pin yếu hoặc khó kiểm soát người ra vào, hãy bắt đầu từ ba điểm: mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu. Ưu đãi hiện có: lắp đặt ưu đãi trong nội thành.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn khóa cửa thông minh vừa đủ thực tế cho chủ căn hộ muốn kiểm soát ra vào.
+Subheadline: Hợp với chủ căn hộ muốn tiện hơn nhưng vẫn cần hiểu rõ cách vận hành. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Lắp đặt ưu đãi trong nội thành là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">khóa cửa thông minh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
 Sản phẩm/dịch vụ: khóa cửa thông minh.
 Từ khóa chính: mở bằng vân tay; mã số tạm thời; cảnh báo pin yếu.
@@ -2664,21 +3878,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Gợi ý dễ dùng cho khóa cửa thông minh cho chủ căn hộ muốn kiểm soát ra vào với mở bằng vân tay.
-Subheadline: Tập trung vào mã số tạm thời và cảnh báo pin yếu, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: khóa cửa thông minh là lựa chọn đáng cân nhắc cho chủ căn hộ muốn kiểm soát ra vào.
-Subheadline: Điểm mạnh nằm ở mã số tạm thời, mở bằng vân tay và lắp đặt ưu đãi trong nội thành để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Thêm tiện lợi cho khóa cửa thông minh nếu bạn cần mở bằng vân tay và mã số tạm thời.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: khóa cửa thông minh: gọn hơn cho những lúc mở bằng vân tay thật sự quan trọng.
+Subheadline: Dành cho chủ căn hộ muốn kiểm soát ra vào, nhất là khi ra vào căn hộ nhiều lần trong ngày, có lúc cần gửi mã tạm cho người thân hoặc khách. Điểm đáng xem là mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên hỏi kỹ loại cửa, phương án lắp đặt và cách xử lý khi pin yếu.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với khóa cửa thông minh.
+Subheadline: Nếu bạn từng ngại chuyện sợ quên chìa, pin yếu hoặc khó kiểm soát người ra vào, hãy bắt đầu từ ba điểm: mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu. Ưu đãi hiện có: lắp đặt ưu đãi trong nội thành.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn khóa cửa thông minh vừa đủ thực tế cho chủ căn hộ muốn kiểm soát ra vào.
+Subheadline: Hợp với chủ căn hộ muốn tiện hơn nhưng vẫn cần hiểu rõ cách vận hành. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Lắp đặt ưu đãi trong nội thành là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">khóa cửa thông minh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Cảm xúc.
 Sản phẩm/dịch vụ: khóa cửa thông minh.
 Từ khóa chính: mở bằng vân tay; mã số tạm thời; cảnh báo pin yếu.
@@ -2702,36 +3931,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Mô tả ngắn: khóa cửa thông minh dành cho chủ căn hộ muốn kiểm soát ra vào, nhấn vào trải nghiệm dùng rõ ràng và dễ hiểu.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. khóa cửa thông minh dành cho chủ căn hộ muốn kiểm soát ra vào trong những lúc ra vào căn hộ nhiều lần trong ngày, có lúc cần gửi mã tạm cho người thân hoặc khách.
 Lợi ích chính:
-- Hỗ trợ nhu cầu thực tế nhờ mở bằng vân tay và mã số tạm thời.
-- Giúp bạn cân nhắc nhanh hơn với thông tin đúng brief và lắp đặt ưu đãi trong nội thành.
+- Giúp bạn yên tâm hơn với nhu cầu mở bằng vân tay mà không phải đọc quá nhiều thông tin rối.
+- Mã số tạm thời là điểm cộng rõ ràng khi dùng hằng ngày.
+- Cảnh báo pin yếu giúp sản phẩm dễ được đưa vào thói quen hiện có.
 Đặc điểm nổi bật:
-- mở bằng vân tay.
-- cảnh báo pin yếu.
-Lời kêu gọi hành động: Xem chi tiết để chọn mẫu phù hợp.
-Phiên bản 2:
-Mô tả ngắn: Nếu bạn là chủ căn hộ muốn kiểm soát ra vào, khóa cửa thông minh là một lựa chọn gọn gàng, dễ dùng và sát nhu cầu.
+- mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu.
+- Thông tin đi kèm: lắp đặt ưu đãi trong nội thành.
+Góc cần biết: Bạn nên hỏi kỹ loại cửa, phương án lắp đặt và cách xử lý khi pin yếu.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì sợ quên chìa, pin yếu hoặc khó kiểm soát người ra vào, khóa cửa thông minh là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu.
 Lợi ích chính:
-- Mang lại cảm giác yên tâm khi xem thông tin rõ ràng.
-- Tập trung vào mã số tạm thời và cảnh báo pin yếu để phục vụ dùng hằng ngày.
-Đặc điểm nổi bật:
-- mã số tạm thời.
-- lắp đặt ưu đãi trong nội thành.
-Lời kêu gọi hành động: Nhắn tin để được tư vấn trước khi mua.
-Phiên bản 3:
-Mô tả ngắn: khóa cửa thông minh giúp chủ căn hộ muốn kiểm soát ra vào có thêm một lựa chọn hợp lý cho nhu cầu thường ngày.
-Lợi ích chính:
-- cảnh báo pin yếu làm cho việc dùng tiện hơn.
-- mở bằng vân tay hỗ trợ đúng mối quan tâm chính.
+- Phù hợp với chủ căn hộ muốn kiểm soát ra vào muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi lắp đặt ưu đãi trong nội thành giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
 Đặc điểm nổi bật:
 - mở bằng vân tay.
 - mã số tạm thời.
-Lời kêu gọi hành động: Lưu lại để so sánh khi cần.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+- cảnh báo pin yếu.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: khóa cửa thông minh hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với chủ căn hộ muốn tiện hơn nhưng vẫn cần hiểu rõ cách vận hành.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu.
+- Ghi chú thêm để cân nhắc: lắp đặt ưu đãi trong nội thành.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emotional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">khóa cửa thông minh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: khóa cửa thông minh.
 Từ khóa chính: mở bằng vân tay; mã số tạm thời; cảnh báo pin yếu.
@@ -2755,7 +4003,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. khóa cửa thông minh dành cho chủ căn hộ muốn kiểm soát ra vào trong những lúc ra vào căn hộ nhiều lần trong ngày, có lúc cần gửi mã tạm cho người thân hoặc khách.
+Lợi ích chính:
+- Giúp bạn yên tâm hơn với nhu cầu mở bằng vân tay mà không phải đọc quá nhiều thông tin rối.
+- Mã số tạm thời là điểm cộng rõ ràng khi dùng hằng ngày.
+- Cảnh báo pin yếu giúp sản phẩm dễ được đưa vào thói quen hiện có.
+Đặc điểm nổi bật:
+- mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu.
+- Thông tin đi kèm: lắp đặt ưu đãi trong nội thành.
+Góc cần biết: Bạn nên hỏi kỹ loại cửa, phương án lắp đặt và cách xử lý khi pin yếu.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì sợ quên chìa, pin yếu hoặc khó kiểm soát người ra vào, khóa cửa thông minh là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu.
+Lợi ích chính:
+- Phù hợp với chủ căn hộ muốn kiểm soát ra vào muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi lắp đặt ưu đãi trong nội thành giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
+Đặc điểm nổi bật:
+- mở bằng vân tay.
+- mã số tạm thời.
+- cảnh báo pin yếu.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: khóa cửa thông minh hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với chủ căn hộ muốn tiện hơn nhưng vẫn cần hiểu rõ cách vận hành.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu.
+- Ghi chú thêm để cân nhắc: lắp đặt ưu đãi trong nội thành.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">khóa cửa thông minh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Thân thiện.
 Sản phẩm/dịch vụ: khóa cửa thông minh.
 Từ khóa chính: mở bằng vân tay; mã số tạm thời; cảnh báo pin yếu.
@@ -2779,24 +4075,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Một lựa chọn thân thiện cho chủ căn hộ muốn kiểm soát ra vào.
-Caption: khóa cửa thông minh giúp việc hằng ngày nhẹ hơn nhờ mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu. Hiện có lắp đặt ưu đãi trong nội thành, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #KhoaCuaThong #ChuCanHo #MoBangVan
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của chủ căn hộ muốn kiểm soát ra vào.
-Caption: Với mã số tạm thời và cảnh báo pin yếu, khóa cửa thông minh cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. lắp đặt ưu đãi trong nội thành là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #KhoaCuaThong #MaSoTam #MuaSamThongMinh
-Phiên bản 3:
-Hook: Gợi ý dễ dùng cho chủ căn hộ muốn kiểm soát ra vào một lựa chọn gọn gàng hơn.
-Caption: Khi xem khóa cửa thông minh, hãy chú ý vào mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #KhoaCuaThong #CanhBaoPin #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Một món nhỏ, nhưng dùng đúng lúc thì thấy ngày nhẹ hơn một chút.
+Caption: khóa cửa thông minh dành cho chủ căn hộ muốn kiểm soát ra vào trong những lúc ra vào căn hộ nhiều lần trong ngày, có lúc cần gửi mã tạm cho người thân hoặc khách. Mình sẽ nhìn vào mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu trước, rồi mới xét đến ưu đãi lắp đặt ưu đãi trong nội thành. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên hỏi kỹ loại cửa, phương án lắp đặt và cách xử lý khi pin yếu.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #KhoaCuaThongMinh #CanHoHienDai #AnTamRaVao
+Phiên bản 2:
+Hook: Mua sắm dễ chịu hơn khi thông tin đủ rõ và không bị thúc ép.
+Caption: Nếu bạn từng gặp chuyện sợ quên chìa, pin yếu hoặc khó kiểm soát người ra vào, khóa cửa thông minh là một lựa chọn đáng để lưu lại. Sản phẩm có mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Lắp đặt ưu đãi trong nội thành là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #KhoaCuaThongMinh #CanHoHienDai #AnTamRaVao
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với khóa cửa thông minh, hãy bắt đầu từ nhu cầu của chủ căn hộ muốn kiểm soát ra vào: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với chủ căn hộ muốn tiện hơn nhưng vẫn cần hiểu rõ cách vận hành.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #KhoaCuaThongMinh #CanHoHienDai #AnTamRaVao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">khóa cửa thông minh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Khẩn cấp.
 Sản phẩm/dịch vụ: khóa cửa thông minh.
 Từ khóa chính: mở bằng vân tay; mã số tạm thời; cảnh báo pin yếu.
@@ -2820,24 +4131,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Cần xem ngay cho chủ căn hộ muốn kiểm soát ra vào.
-Caption: khóa cửa thông minh giúp việc hằng ngày nhẹ hơn nhờ mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu. Hiện có lắp đặt ưu đãi trong nội thành, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #KhoaCuaThong #ChuCanHo #MoBangVan
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của chủ căn hộ muốn kiểm soát ra vào.
-Caption: Với mã số tạm thời và cảnh báo pin yếu, khóa cửa thông minh cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. lắp đặt ưu đãi trong nội thành là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #KhoaCuaThong #MaSoTam #MuaSamThongMinh
-Phiên bản 3:
-Hook: Đừng chần chừ với chủ căn hộ muốn kiểm soát ra vào một lựa chọn gọn gàng hơn.
-Caption: Khi xem khóa cửa thông minh, hãy chú ý vào mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #KhoaCuaThong #CanhBaoPin #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Đang cân nhắc thì nên xem kỹ hôm nay, nhưng không cần mua vội.
+Caption: khóa cửa thông minh dành cho chủ căn hộ muốn kiểm soát ra vào trong những lúc ra vào căn hộ nhiều lần trong ngày, có lúc cần gửi mã tạm cho người thân hoặc khách. Mình sẽ nhìn vào mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu trước, rồi mới xét đến ưu đãi lắp đặt ưu đãi trong nội thành. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên hỏi kỹ loại cửa, phương án lắp đặt và cách xử lý khi pin yếu.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #KhoaCuaThongMinh #CanHoHienDai #AnTamRaVao
+Phiên bản 2:
+Hook: Ưu đãi chỉ đáng giữ lại khi sản phẩm thật sự hợp với cách bạn dùng.
+Caption: Nếu bạn từng gặp chuyện sợ quên chìa, pin yếu hoặc khó kiểm soát người ra vào, khóa cửa thông minh là một lựa chọn đáng để lưu lại. Sản phẩm có mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Lắp đặt ưu đãi trong nội thành là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #KhoaCuaThongMinh #CanHoHienDai #AnTamRaVao
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với khóa cửa thông minh, hãy bắt đầu từ nhu cầu của chủ căn hộ muốn kiểm soát ra vào: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với chủ căn hộ muốn tiện hơn nhưng vẫn cần hiểu rõ cách vận hành.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #KhoaCuaThongMinh #CanHoHienDai #AnTamRaVao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">khóa cửa thông minh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Email Marketing với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: khóa cửa thông minh.
 Từ khóa chính: mở bằng vân tay; mã số tạm thời; cảnh báo pin yếu.
@@ -2862,27 +4188,45 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Subject: Gợi ý khóa cửa thông minh cho chủ căn hộ muốn kiểm soát ra vào
-Preview text: Tóm tắt nhanh các điểm đáng cân nhắc trước khi chọn mua.
+    <t xml:space="preserve">Phiên bản 1:
+Subject: Gợi ý khóa cửa thông minh cho nhu cầu dùng hằng ngày
+Preview text: Một vài điểm đáng xem trước khi bạn quyết định.
 Lời chào: Chào bạn,
-Nội dung chính: Nếu bạn đang tìm một lựa chọn phù hợp cho nhu cầu hằng ngày, khóa cửa thông minh có các điểm nổi bật như mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu. Hiện có lắp đặt ưu đãi trong nội thành, nên bạn có thể xem thêm thông tin trước khi quyết định.
-Lời kêu gọi hành động: Xem chi tiết sản phẩm hôm nay.
-Phiên bản 2:
-Subject: khóa cửa thông minh có thể hợp với nhu cầu của bạn
-Preview text: Một vài lý do để chủ căn hộ muốn kiểm soát ra vào cân nhắc sản phẩm này.
+Nội dung chính: Nếu bạn là chủ căn hộ muốn kiểm soát ra vào, có lẽ điều bạn cần không phải một lời giới thiệu quá mạnh. Bạn cần biết khóa cửa thông minh có hợp với bối cảnh ra vào căn hộ nhiều lần trong ngày, có lúc cần gửi mã tạm cho người thân hoặc khách hay không.
+Sản phẩm này đáng xem nhờ mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu. Trong đó, mở bằng vân tay giúp xử lý nhu cầu chính; mã số tạm thời và cảnh báo pin yếu làm trải nghiệm dùng trọn vẹn hơn.
+Góc cần biết: Bạn nên hỏi kỹ loại cửa, phương án lắp đặt và cách xử lý khi pin yếu. Hiện có lắp đặt ưu đãi trong nội thành, bạn có thể xem như một điểm cộng nếu sản phẩm đã đúng nhu cầu.
+Lời kêu gọi hành động: Mở chi tiết sản phẩm hoặc nhắn shop để được tư vấn kỹ hơn.
+Phiên bản 2:
+Subject: Trước khi mua khóa cửa thông minh, bạn có thể xem nhanh điểm này
+Preview text: Chọn chắc hơn khi biết sản phẩm giải quyết đúng việc gì.
 Lời chào: Chào bạn,
-Nội dung chính: khóa cửa thông minh tập trung vào mã số tạm thời, mở bằng vân tay và cảnh báo pin yếu. Thông tin được viết theo đúng brief, không thêm chứng nhận hay số liệu ngoài phạm vi. lắp đặt ưu đãi trong nội thành giúp bạn có thêm lý do so sánh.
-Lời kêu gọi hành động: Nhắn lại để được tư vấn lựa chọn phù hợp.
-Phiên bản 3:
-Subject: Xem nhanh khóa cửa thông minh trước khi bạn chọn
-Preview text: Thông tin ngắn gọn, dễ so sánh và có ưu đãi đi kèm.
+Nội dung chính: Nhiều người phân vân vì sợ quên chìa, pin yếu hoặc khó kiểm soát người ra vào. Vì vậy, với khóa cửa thông minh, hãy nhìn vào nhu cầu thật trước: bạn cần mở bằng vân tay, muốn mã số tạm thời, hay quan tâm nhiều hơn đến cảnh báo pin yếu?
+Nếu câu trả lời khớp với cách bạn dùng hằng ngày, đây là lựa chọn đáng cân nhắc. Nếu chưa chắc, bạn có thể hỏi shop trước khi đặt.
+Góc cần biết: Lắp đặt ưu đãi trong nội thành đang đi kèm, nhưng quyết định cuối cùng vẫn nên dựa trên mức độ phù hợp.
+Lời kêu gọi hành động: Trả lời tin nhắn này với nhu cầu của bạn, shop sẽ gợi ý cụ thể hơn.
+Phiên bản 3:
+Subject: khóa cửa thông minh có thể là món bạn đang tìm
+Preview text: Rõ lợi ích, rõ tình huống dùng, không cần quyết định vội.
 Lời chào: Chào bạn,
-Nội dung chính: Với chủ căn hộ muốn kiểm soát ra vào, một sản phẩm dễ hiểu thường giúp quyết định nhanh hơn. khóa cửa thông minh có mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu; ngoài ra còn có lắp đặt ưu đãi trong nội thành để bạn cân nhắc thêm.
-Lời kêu gọi hành động: Mở trang sản phẩm để xem thêm chi tiết.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Nội dung chính: Hợp với chủ căn hộ muốn tiện hơn nhưng vẫn cần hiểu rõ cách vận hành. khóa cửa thông minh tập trung vào mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu, phù hợp với chủ căn hộ muốn kiểm soát ra vào khi muốn một lựa chọn thực tế hơn cho sinh hoạt hằng ngày.
+Bạn có thể cân nhắc sản phẩm này nếu đang cần giải quyết chuyện sợ quên chìa, pin yếu hoặc khó kiểm soát người ra vào. Còn nếu muốn chắc hơn, hãy hỏi shop về tình huống dùng của bạn.
+Góc cần biết: Bạn nên hỏi kỹ loại cửa, phương án lắp đặt và cách xử lý khi pin yếu.
+Lời kêu gọi hành động: Xem chi tiết hoặc nhắn shop trước khi chốt đơn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">khóa cửa thông minh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Lời Kêu Gọi Hành Động với tone Thân thiện.
 Sản phẩm/dịch vụ: khóa cửa thông minh.
 Từ khóa chính: mở bằng vân tay; mã số tạm thời; cảnh báo pin yếu.
@@ -2904,18 +4248,30 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Lời kêu gọi hành động chính: Mua khóa cửa thông minh ngay hôm nay
-Microcopy: Phù hợp cho chủ căn hộ muốn kiểm soát ra vào, có lắp đặt ưu đãi trong nội thành và thông tin rõ ràng để bạn chọn nhanh.
-Phiên bản 2:
-Lời kêu gọi hành động chính: Chọn khóa cửa thông minh cho nhu cầu hiện tại
-Microcopy: Tập trung vào mở bằng vân tay và mã số tạm thời, giúp bạn quyết định dễ hơn.
-Phiên bản 3:
-Lời kêu gọi hành động chính: Nhắn shop để được tư vấn khóa cửa thông minh
-Microcopy: Bạn có thể hỏi thêm về cảnh báo pin yếu và lắp đặt ưu đãi trong nội thành trước khi quyết định.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Lời kêu gọi hành động chính: Xem khóa cửa thông minh có hợp với bạn không
+Microcopy: Dành cho chủ căn hộ muốn kiểm soát ra vào, nổi bật với mở bằng vân tay, mã số tạm thời và cảnh báo pin yếu. Có lắp đặt ưu đãi trong nội thành nếu bạn muốn cân nhắc thêm.
+Phiên bản 2:
+Lời kêu gọi hành động chính: Nhắn shop để chọn khóa cửa thông minh đúng nhu cầu
+Microcopy: Kể nhanh bạn dùng trong bối cảnh nào, shop sẽ gợi ý theo tình huống thật như ra vào căn hộ nhiều lần trong ngày, có lúc cần gửi mã tạm cho người thân hoặc khách.
+Phiên bản 3:
+Lời kêu gọi hành động chính: Lưu khóa cửa thông minh để so sánh trước khi mua
+Microcopy: Phù hợp hơn khi bạn muốn giải quyết chuyện sợ quên chìa, pin yếu hoặc khó kiểm soát người ra vào mà vẫn cần một lựa chọn rõ ràng, dễ hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">khóa cửa thông minh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Khẩn cấp.
 Sản phẩm/dịch vụ: thảm yoga chống trượt.
 Từ khóa chính: bề mặt bám tốt; dày 6 mm; dễ cuộn gọn.
@@ -2938,24 +4294,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Đừng chần chừ với thảm yoga chống trượt cho người tập tại nhà với bề mặt bám tốt.
-Subheadline: Tập trung vào dày 6 mm và dễ cuộn gọn, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: thảm yoga chống trượt là lựa chọn đáng cân nhắc cho người tập tại nhà.
-Subheadline: Điểm mạnh nằm ở dày 6 mm, bề mặt bám tốt và tặng dây đeo thảm để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Giữ nhịp nhanh hơn cho thảm yoga chống trượt nếu bạn cần bề mặt bám tốt và dày 6 mm.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>thảm yoga chống trượt</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: thảm yoga chống trượt: gọn hơn cho những lúc bề mặt bám tốt thật sự quan trọng.
+Subheadline: Dành cho người tập tại nhà, nhất là khi buổi tập tại nhà cần một mặt thảm ổn định để giữ nhịp thở và tư thế. Điểm đáng xem là bề mặt bám tốt, dày 6 mm và dễ cuộn gọn; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên chọn độ dày, bề mặt bám và cách vệ sinh sau buổi tập.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với thảm yoga chống trượt.
+Subheadline: Nếu bạn từng ngại chuyện sàn trơn hoặc thảm quá mỏng làm buổi tập mất tập trung, hãy bắt đầu từ ba điểm: bề mặt bám tốt, dày 6 mm và dễ cuộn gọn. Ưu đãi hiện có: tặng dây đeo thảm.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn thảm yoga chống trượt vừa đủ thực tế cho người tập tại nhà.
+Subheadline: Hợp với người muốn duy trì thói quen vận động nhẹ nhàng tại nhà. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Tặng dây đeo thảm là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thảm yoga chống trượt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
 Sản phẩm/dịch vụ: thảm yoga chống trượt.
 Từ khóa chính: bề mặt bám tốt; dày 6 mm; dễ cuộn gọn.
@@ -2978,21 +4346,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Gợi ý dễ dùng cho thảm yoga chống trượt cho người tập tại nhà với bề mặt bám tốt.
-Subheadline: Tập trung vào dày 6 mm và dễ cuộn gọn, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: thảm yoga chống trượt là lựa chọn đáng cân nhắc cho người tập tại nhà.
-Subheadline: Điểm mạnh nằm ở dày 6 mm, bề mặt bám tốt và tặng dây đeo thảm để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Thêm tiện lợi cho thảm yoga chống trượt nếu bạn cần bề mặt bám tốt và dày 6 mm.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: thảm yoga chống trượt: gọn hơn cho những lúc bề mặt bám tốt thật sự quan trọng.
+Subheadline: Dành cho người tập tại nhà, nhất là khi buổi tập tại nhà cần một mặt thảm ổn định để giữ nhịp thở và tư thế. Điểm đáng xem là bề mặt bám tốt, dày 6 mm và dễ cuộn gọn; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên chọn độ dày, bề mặt bám và cách vệ sinh sau buổi tập.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với thảm yoga chống trượt.
+Subheadline: Nếu bạn từng ngại chuyện sàn trơn hoặc thảm quá mỏng làm buổi tập mất tập trung, hãy bắt đầu từ ba điểm: bề mặt bám tốt, dày 6 mm và dễ cuộn gọn. Ưu đãi hiện có: tặng dây đeo thảm.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn thảm yoga chống trượt vừa đủ thực tế cho người tập tại nhà.
+Subheadline: Hợp với người muốn duy trì thói quen vận động nhẹ nhàng tại nhà. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Tặng dây đeo thảm là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thảm yoga chống trượt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Cảm xúc.
 Sản phẩm/dịch vụ: thảm yoga chống trượt.
 Từ khóa chính: bề mặt bám tốt; dày 6 mm; dễ cuộn gọn.
@@ -3016,36 +4399,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Mô tả ngắn: thảm yoga chống trượt dành cho người tập tại nhà, nhấn vào trải nghiệm dùng rõ ràng và dễ hiểu.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. thảm yoga chống trượt dành cho người tập tại nhà trong những lúc buổi tập tại nhà cần một mặt thảm ổn định để giữ nhịp thở và tư thế.
 Lợi ích chính:
-- Hỗ trợ nhu cầu thực tế nhờ bề mặt bám tốt và dày 6 mm.
-- Giúp bạn cân nhắc nhanh hơn với thông tin đúng brief và tặng dây đeo thảm.
+- Giúp bạn yên tâm hơn với nhu cầu bề mặt bám tốt mà không phải đọc quá nhiều thông tin rối.
+- Dày 6 mm là điểm cộng rõ ràng khi dùng hằng ngày.
+- Dễ cuộn gọn giúp sản phẩm dễ được đưa vào thói quen hiện có.
 Đặc điểm nổi bật:
-- bề mặt bám tốt.
-- dễ cuộn gọn.
-Lời kêu gọi hành động: Xem chi tiết để chọn mẫu phù hợp.
-Phiên bản 2:
-Mô tả ngắn: Nếu bạn là người tập tại nhà, thảm yoga chống trượt là một lựa chọn gọn gàng, dễ dùng và sát nhu cầu.
+- bề mặt bám tốt, dày 6 mm và dễ cuộn gọn.
+- Thông tin đi kèm: tặng dây đeo thảm.
+Góc cần biết: Bạn nên chọn độ dày, bề mặt bám và cách vệ sinh sau buổi tập.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì sàn trơn hoặc thảm quá mỏng làm buổi tập mất tập trung, thảm yoga chống trượt là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: bề mặt bám tốt, dày 6 mm và dễ cuộn gọn.
 Lợi ích chính:
-- Mang lại cảm giác yên tâm khi xem thông tin rõ ràng.
-- Tập trung vào dày 6 mm và dễ cuộn gọn để phục vụ dùng hằng ngày.
-Đặc điểm nổi bật:
-- dày 6 mm.
-- tặng dây đeo thảm.
-Lời kêu gọi hành động: Nhắn tin để được tư vấn trước khi mua.
-Phiên bản 3:
-Mô tả ngắn: thảm yoga chống trượt giúp người tập tại nhà có thêm một lựa chọn hợp lý cho nhu cầu thường ngày.
-Lợi ích chính:
-- dễ cuộn gọn làm cho việc dùng tiện hơn.
-- bề mặt bám tốt hỗ trợ đúng mối quan tâm chính.
+- Phù hợp với người tập tại nhà muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi tặng dây đeo thảm giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
 Đặc điểm nổi bật:
 - bề mặt bám tốt.
 - dày 6 mm.
-Lời kêu gọi hành động: Lưu lại để so sánh khi cần.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+- dễ cuộn gọn.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: thảm yoga chống trượt hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người muốn duy trì thói quen vận động nhẹ nhàng tại nhà.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin bề mặt bám tốt, dày 6 mm và dễ cuộn gọn.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: bề mặt bám tốt, dày 6 mm và dễ cuộn gọn.
+- Ghi chú thêm để cân nhắc: tặng dây đeo thảm.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emotional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thảm yoga chống trượt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: thảm yoga chống trượt.
 Từ khóa chính: bề mặt bám tốt; dày 6 mm; dễ cuộn gọn.
@@ -3069,7 +4471,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. thảm yoga chống trượt dành cho người tập tại nhà trong những lúc buổi tập tại nhà cần một mặt thảm ổn định để giữ nhịp thở và tư thế.
+Lợi ích chính:
+- Giúp bạn yên tâm hơn với nhu cầu bề mặt bám tốt mà không phải đọc quá nhiều thông tin rối.
+- Dày 6 mm là điểm cộng rõ ràng khi dùng hằng ngày.
+- Dễ cuộn gọn giúp sản phẩm dễ được đưa vào thói quen hiện có.
+Đặc điểm nổi bật:
+- bề mặt bám tốt, dày 6 mm và dễ cuộn gọn.
+- Thông tin đi kèm: tặng dây đeo thảm.
+Góc cần biết: Bạn nên chọn độ dày, bề mặt bám và cách vệ sinh sau buổi tập.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì sàn trơn hoặc thảm quá mỏng làm buổi tập mất tập trung, thảm yoga chống trượt là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: bề mặt bám tốt, dày 6 mm và dễ cuộn gọn.
+Lợi ích chính:
+- Phù hợp với người tập tại nhà muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi tặng dây đeo thảm giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
+Đặc điểm nổi bật:
+- bề mặt bám tốt.
+- dày 6 mm.
+- dễ cuộn gọn.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: thảm yoga chống trượt hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người muốn duy trì thói quen vận động nhẹ nhàng tại nhà.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin bề mặt bám tốt, dày 6 mm và dễ cuộn gọn.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: bề mặt bám tốt, dày 6 mm và dễ cuộn gọn.
+- Ghi chú thêm để cân nhắc: tặng dây đeo thảm.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thảm yoga chống trượt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Thân thiện.
 Sản phẩm/dịch vụ: thảm yoga chống trượt.
 Từ khóa chính: bề mặt bám tốt; dày 6 mm; dễ cuộn gọn.
@@ -3093,24 +4543,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Một lựa chọn thân thiện cho người tập tại nhà.
-Caption: thảm yoga chống trượt giúp việc hằng ngày nhẹ hơn nhờ bề mặt bám tốt, dày 6 mm và dễ cuộn gọn. Hiện có tặng dây đeo thảm, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #ThamYogaChong #NguoiTapTai #BeMatBam
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của người tập tại nhà.
-Caption: Với dày 6 mm và dễ cuộn gọn, thảm yoga chống trượt cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. tặng dây đeo thảm là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #ThamYogaChong #Day6Mm #MuaSamThongMinh
-Phiên bản 3:
-Hook: Gợi ý dễ dùng cho người tập tại nhà một lựa chọn gọn gàng hơn.
-Caption: Khi xem thảm yoga chống trượt, hãy chú ý vào bề mặt bám tốt, dày 6 mm và dễ cuộn gọn. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #ThamYogaChong #DeCuonGon #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Một món nhỏ, nhưng dùng đúng lúc thì thấy ngày nhẹ hơn một chút.
+Caption: thảm yoga chống trượt dành cho người tập tại nhà trong những lúc buổi tập tại nhà cần một mặt thảm ổn định để giữ nhịp thở và tư thế. Mình sẽ nhìn vào bề mặt bám tốt, dày 6 mm và dễ cuộn gọn trước, rồi mới xét đến ưu đãi tặng dây đeo thảm. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên chọn độ dày, bề mặt bám và cách vệ sinh sau buổi tập.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #ThamYoga #TapTaiNha #SongKhoeMoiNgay
+Phiên bản 2:
+Hook: Mua sắm dễ chịu hơn khi thông tin đủ rõ và không bị thúc ép.
+Caption: Nếu bạn từng gặp chuyện sàn trơn hoặc thảm quá mỏng làm buổi tập mất tập trung, thảm yoga chống trượt là một lựa chọn đáng để lưu lại. Sản phẩm có bề mặt bám tốt, dày 6 mm và dễ cuộn gọn, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Tặng dây đeo thảm là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #ThamYoga #TapTaiNha #SongKhoeMoiNgay
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với thảm yoga chống trượt, hãy bắt đầu từ nhu cầu của người tập tại nhà: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm bề mặt bám tốt, dày 6 mm và dễ cuộn gọn khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người muốn duy trì thói quen vận động nhẹ nhàng tại nhà.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #ThamYoga #TapTaiNha #SongKhoeMoiNgay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thảm yoga chống trượt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Khẩn cấp.
 Sản phẩm/dịch vụ: thảm yoga chống trượt.
 Từ khóa chính: bề mặt bám tốt; dày 6 mm; dễ cuộn gọn.
@@ -3134,24 +4599,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Cần xem ngay cho người tập tại nhà.
-Caption: thảm yoga chống trượt giúp việc hằng ngày nhẹ hơn nhờ bề mặt bám tốt, dày 6 mm và dễ cuộn gọn. Hiện có tặng dây đeo thảm, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #ThamYogaChong #NguoiTapTai #BeMatBam
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của người tập tại nhà.
-Caption: Với dày 6 mm và dễ cuộn gọn, thảm yoga chống trượt cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. tặng dây đeo thảm là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #ThamYogaChong #Day6Mm #MuaSamThongMinh
-Phiên bản 3:
-Hook: Đừng chần chừ với người tập tại nhà một lựa chọn gọn gàng hơn.
-Caption: Khi xem thảm yoga chống trượt, hãy chú ý vào bề mặt bám tốt, dày 6 mm và dễ cuộn gọn. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #ThamYogaChong #DeCuonGon #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Đang cân nhắc thì nên xem kỹ hôm nay, nhưng không cần mua vội.
+Caption: thảm yoga chống trượt dành cho người tập tại nhà trong những lúc buổi tập tại nhà cần một mặt thảm ổn định để giữ nhịp thở và tư thế. Mình sẽ nhìn vào bề mặt bám tốt, dày 6 mm và dễ cuộn gọn trước, rồi mới xét đến ưu đãi tặng dây đeo thảm. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên chọn độ dày, bề mặt bám và cách vệ sinh sau buổi tập.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #ThamYoga #TapTaiNha #SongKhoeMoiNgay
+Phiên bản 2:
+Hook: Ưu đãi chỉ đáng giữ lại khi sản phẩm thật sự hợp với cách bạn dùng.
+Caption: Nếu bạn từng gặp chuyện sàn trơn hoặc thảm quá mỏng làm buổi tập mất tập trung, thảm yoga chống trượt là một lựa chọn đáng để lưu lại. Sản phẩm có bề mặt bám tốt, dày 6 mm và dễ cuộn gọn, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Tặng dây đeo thảm là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #ThamYoga #TapTaiNha #SongKhoeMoiNgay
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với thảm yoga chống trượt, hãy bắt đầu từ nhu cầu của người tập tại nhà: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm bề mặt bám tốt, dày 6 mm và dễ cuộn gọn khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người muốn duy trì thói quen vận động nhẹ nhàng tại nhà.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #ThamYoga #TapTaiNha #SongKhoeMoiNgay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thảm yoga chống trượt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Email Marketing với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: thảm yoga chống trượt.
 Từ khóa chính: bề mặt bám tốt; dày 6 mm; dễ cuộn gọn.
@@ -3176,27 +4656,45 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Subject: Gợi ý thảm yoga chống trượt cho người tập tại nhà
-Preview text: Tóm tắt nhanh các điểm đáng cân nhắc trước khi chọn mua.
+    <t xml:space="preserve">Phiên bản 1:
+Subject: Gợi ý thảm yoga chống trượt cho nhu cầu dùng hằng ngày
+Preview text: Một vài điểm đáng xem trước khi bạn quyết định.
 Lời chào: Chào bạn,
-Nội dung chính: Nếu bạn đang tìm một lựa chọn phù hợp cho nhu cầu hằng ngày, thảm yoga chống trượt có các điểm nổi bật như bề mặt bám tốt, dày 6 mm và dễ cuộn gọn. Hiện có tặng dây đeo thảm, nên bạn có thể xem thêm thông tin trước khi quyết định.
-Lời kêu gọi hành động: Xem chi tiết sản phẩm hôm nay.
-Phiên bản 2:
-Subject: thảm yoga chống trượt có thể hợp với nhu cầu của bạn
-Preview text: Một vài lý do để người tập tại nhà cân nhắc sản phẩm này.
+Nội dung chính: Nếu bạn là người tập tại nhà, có lẽ điều bạn cần không phải một lời giới thiệu quá mạnh. Bạn cần biết thảm yoga chống trượt có hợp với bối cảnh buổi tập tại nhà cần một mặt thảm ổn định để giữ nhịp thở và tư thế hay không.
+Sản phẩm này đáng xem nhờ bề mặt bám tốt, dày 6 mm và dễ cuộn gọn. Trong đó, bề mặt bám tốt giúp xử lý nhu cầu chính; dày 6 mm và dễ cuộn gọn làm trải nghiệm dùng trọn vẹn hơn.
+Góc cần biết: Bạn nên chọn độ dày, bề mặt bám và cách vệ sinh sau buổi tập. Hiện có tặng dây đeo thảm, bạn có thể xem như một điểm cộng nếu sản phẩm đã đúng nhu cầu.
+Lời kêu gọi hành động: Mở chi tiết sản phẩm hoặc nhắn shop để được tư vấn kỹ hơn.
+Phiên bản 2:
+Subject: Trước khi mua thảm yoga chống trượt, bạn có thể xem nhanh điểm này
+Preview text: Chọn chắc hơn khi biết sản phẩm giải quyết đúng việc gì.
 Lời chào: Chào bạn,
-Nội dung chính: thảm yoga chống trượt tập trung vào dày 6 mm, bề mặt bám tốt và dễ cuộn gọn. Thông tin được viết theo đúng brief, không thêm chứng nhận hay số liệu ngoài phạm vi. tặng dây đeo thảm giúp bạn có thêm lý do so sánh.
-Lời kêu gọi hành động: Nhắn lại để được tư vấn lựa chọn phù hợp.
-Phiên bản 3:
-Subject: Xem nhanh thảm yoga chống trượt trước khi bạn chọn
-Preview text: Thông tin ngắn gọn, dễ so sánh và có ưu đãi đi kèm.
+Nội dung chính: Nhiều người phân vân vì sàn trơn hoặc thảm quá mỏng làm buổi tập mất tập trung. Vì vậy, với thảm yoga chống trượt, hãy nhìn vào nhu cầu thật trước: bạn cần bề mặt bám tốt, muốn dày 6 mm, hay quan tâm nhiều hơn đến dễ cuộn gọn?
+Nếu câu trả lời khớp với cách bạn dùng hằng ngày, đây là lựa chọn đáng cân nhắc. Nếu chưa chắc, bạn có thể hỏi shop trước khi đặt.
+Góc cần biết: Tặng dây đeo thảm đang đi kèm, nhưng quyết định cuối cùng vẫn nên dựa trên mức độ phù hợp.
+Lời kêu gọi hành động: Trả lời tin nhắn này với nhu cầu của bạn, shop sẽ gợi ý cụ thể hơn.
+Phiên bản 3:
+Subject: thảm yoga chống trượt có thể là món bạn đang tìm
+Preview text: Rõ lợi ích, rõ tình huống dùng, không cần quyết định vội.
 Lời chào: Chào bạn,
-Nội dung chính: Với người tập tại nhà, một sản phẩm dễ hiểu thường giúp quyết định nhanh hơn. thảm yoga chống trượt có bề mặt bám tốt, dày 6 mm và dễ cuộn gọn; ngoài ra còn có tặng dây đeo thảm để bạn cân nhắc thêm.
-Lời kêu gọi hành động: Mở trang sản phẩm để xem thêm chi tiết.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Nội dung chính: Hợp với người muốn duy trì thói quen vận động nhẹ nhàng tại nhà. thảm yoga chống trượt tập trung vào bề mặt bám tốt, dày 6 mm và dễ cuộn gọn, phù hợp với người tập tại nhà khi muốn một lựa chọn thực tế hơn cho sinh hoạt hằng ngày.
+Bạn có thể cân nhắc sản phẩm này nếu đang cần giải quyết chuyện sàn trơn hoặc thảm quá mỏng làm buổi tập mất tập trung. Còn nếu muốn chắc hơn, hãy hỏi shop về tình huống dùng của bạn.
+Góc cần biết: Bạn nên chọn độ dày, bề mặt bám và cách vệ sinh sau buổi tập.
+Lời kêu gọi hành động: Xem chi tiết hoặc nhắn shop trước khi chốt đơn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thảm yoga chống trượt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Lời Kêu Gọi Hành Động với tone Thân thiện.
 Sản phẩm/dịch vụ: thảm yoga chống trượt.
 Từ khóa chính: bề mặt bám tốt; dày 6 mm; dễ cuộn gọn.
@@ -3218,18 +4716,30 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Lời kêu gọi hành động chính: Mua thảm yoga chống trượt ngay hôm nay
-Microcopy: Phù hợp cho người tập tại nhà, có tặng dây đeo thảm và thông tin rõ ràng để bạn chọn nhanh.
-Phiên bản 2:
-Lời kêu gọi hành động chính: Chọn thảm yoga chống trượt cho nhu cầu hiện tại
-Microcopy: Tập trung vào bề mặt bám tốt và dày 6 mm, giúp bạn quyết định dễ hơn.
-Phiên bản 3:
-Lời kêu gọi hành động chính: Nhắn shop để được tư vấn thảm yoga chống trượt
-Microcopy: Bạn có thể hỏi thêm về dễ cuộn gọn và tặng dây đeo thảm trước khi quyết định.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Lời kêu gọi hành động chính: Xem thảm yoga chống trượt có hợp với bạn không
+Microcopy: Dành cho người tập tại nhà, nổi bật với bề mặt bám tốt, dày 6 mm và dễ cuộn gọn. Có tặng dây đeo thảm nếu bạn muốn cân nhắc thêm.
+Phiên bản 2:
+Lời kêu gọi hành động chính: Nhắn shop để chọn thảm yoga chống trượt đúng nhu cầu
+Microcopy: Kể nhanh bạn dùng trong bối cảnh nào, shop sẽ gợi ý theo tình huống thật như buổi tập tại nhà cần một mặt thảm ổn định để giữ nhịp thở và tư thế.
+Phiên bản 3:
+Lời kêu gọi hành động chính: Lưu thảm yoga chống trượt để so sánh trước khi mua
+Microcopy: Phù hợp hơn khi bạn muốn giải quyết chuyện sàn trơn hoặc thảm quá mỏng làm buổi tập mất tập trung mà vẫn cần một lựa chọn rõ ràng, dễ hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thảm yoga chống trượt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Khẩn cấp.
 Sản phẩm/dịch vụ: máy lọc không khí phòng ngủ.
 Từ khóa chính: màng lọc HEPA; chế độ ngủ yên tĩnh; cảm biến bụi.
@@ -3252,24 +4762,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Đừng chần chừ với máy lọc không khí phòng ngủ cho gia đình có trẻ nhỏ với màng lọc HEPA.
-Subheadline: Tập trung vào chế độ ngủ yên tĩnh và cảm biến bụi, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: máy lọc không khí phòng ngủ là lựa chọn đáng cân nhắc cho gia đình có trẻ nhỏ.
-Subheadline: Điểm mạnh nằm ở chế độ ngủ yên tĩnh, màng lọc HEPA và tư vấn diện tích phòng miễn phí để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Giữ nhịp nhanh hơn cho máy lọc không khí phòng ngủ nếu bạn cần màng lọc HEPA và chế độ ngủ yên tĩnh.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>máy lọc không khí phòng ngủ</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: máy lọc không khí phòng ngủ: gọn hơn cho những lúc màng lọc HEPA thật sự quan trọng.
+Subheadline: Dành cho gia đình có trẻ nhỏ, nhất là khi phòng ngủ cần không gian yên tĩnh hơn, nhất là khi gia đình có trẻ nhỏ. Điểm đáng xem là màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên hỏi diện tích phòng, chế độ ngủ và lịch bảo trì màng lọc.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với máy lọc không khí phòng ngủ.
+Subheadline: Nếu bạn từng ngại chuyện ngại tiếng máy, chọn sai diện tích phòng hoặc không biết khi nào cần thay lọc, hãy bắt đầu từ ba điểm: màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi. Ưu đãi hiện có: tư vấn diện tích phòng miễn phí.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn máy lọc không khí phòng ngủ vừa đủ thực tế cho gia đình có trẻ nhỏ.
+Subheadline: Hợp với gia đình muốn chăm chút chất lượng không gian ngủ một cách vừa phải. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Tư vấn diện tích phòng miễn phí là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">máy lọc không khí phòng ngủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
 Sản phẩm/dịch vụ: máy lọc không khí phòng ngủ.
 Từ khóa chính: màng lọc HEPA; chế độ ngủ yên tĩnh; cảm biến bụi.
@@ -3292,21 +4814,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Gợi ý dễ dùng cho máy lọc không khí phòng ngủ cho gia đình có trẻ nhỏ với màng lọc HEPA.
-Subheadline: Tập trung vào chế độ ngủ yên tĩnh và cảm biến bụi, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: máy lọc không khí phòng ngủ là lựa chọn đáng cân nhắc cho gia đình có trẻ nhỏ.
-Subheadline: Điểm mạnh nằm ở chế độ ngủ yên tĩnh, màng lọc HEPA và tư vấn diện tích phòng miễn phí để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Thêm tiện lợi cho máy lọc không khí phòng ngủ nếu bạn cần màng lọc HEPA và chế độ ngủ yên tĩnh.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: máy lọc không khí phòng ngủ: gọn hơn cho những lúc màng lọc HEPA thật sự quan trọng.
+Subheadline: Dành cho gia đình có trẻ nhỏ, nhất là khi phòng ngủ cần không gian yên tĩnh hơn, nhất là khi gia đình có trẻ nhỏ. Điểm đáng xem là màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên hỏi diện tích phòng, chế độ ngủ và lịch bảo trì màng lọc.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với máy lọc không khí phòng ngủ.
+Subheadline: Nếu bạn từng ngại chuyện ngại tiếng máy, chọn sai diện tích phòng hoặc không biết khi nào cần thay lọc, hãy bắt đầu từ ba điểm: màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi. Ưu đãi hiện có: tư vấn diện tích phòng miễn phí.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn máy lọc không khí phòng ngủ vừa đủ thực tế cho gia đình có trẻ nhỏ.
+Subheadline: Hợp với gia đình muốn chăm chút chất lượng không gian ngủ một cách vừa phải. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Tư vấn diện tích phòng miễn phí là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">máy lọc không khí phòng ngủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Cảm xúc.
 Sản phẩm/dịch vụ: máy lọc không khí phòng ngủ.
 Từ khóa chính: màng lọc HEPA; chế độ ngủ yên tĩnh; cảm biến bụi.
@@ -3330,36 +4867,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Mô tả ngắn: máy lọc không khí phòng ngủ dành cho gia đình có trẻ nhỏ, nhấn vào trải nghiệm dùng rõ ràng và dễ hiểu.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. máy lọc không khí phòng ngủ dành cho gia đình có trẻ nhỏ trong những lúc phòng ngủ cần không gian yên tĩnh hơn, nhất là khi gia đình có trẻ nhỏ.
 Lợi ích chính:
-- Hỗ trợ nhu cầu thực tế nhờ màng lọc HEPA và chế độ ngủ yên tĩnh.
-- Giúp bạn cân nhắc nhanh hơn với thông tin đúng brief và tư vấn diện tích phòng miễn phí.
+- Giúp bạn yên tâm hơn với nhu cầu màng lọc HEPA mà không phải đọc quá nhiều thông tin rối.
+- Chế độ ngủ yên tĩnh là điểm cộng rõ ràng khi dùng hằng ngày.
+- Cảm biến bụi giúp sản phẩm dễ được đưa vào thói quen hiện có.
 Đặc điểm nổi bật:
-- màng lọc HEPA.
-- cảm biến bụi.
-Lời kêu gọi hành động: Xem chi tiết để chọn mẫu phù hợp.
-Phiên bản 2:
-Mô tả ngắn: Nếu bạn là gia đình có trẻ nhỏ, máy lọc không khí phòng ngủ là một lựa chọn gọn gàng, dễ dùng và sát nhu cầu.
+- màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi.
+- Thông tin đi kèm: tư vấn diện tích phòng miễn phí.
+Góc cần biết: Bạn nên hỏi diện tích phòng, chế độ ngủ và lịch bảo trì màng lọc.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì ngại tiếng máy, chọn sai diện tích phòng hoặc không biết khi nào cần thay lọc, máy lọc không khí phòng ngủ là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi.
 Lợi ích chính:
-- Mang lại cảm giác yên tâm khi xem thông tin rõ ràng.
-- Tập trung vào chế độ ngủ yên tĩnh và cảm biến bụi để phục vụ dùng hằng ngày.
-Đặc điểm nổi bật:
-- chế độ ngủ yên tĩnh.
-- tư vấn diện tích phòng miễn phí.
-Lời kêu gọi hành động: Nhắn tin để được tư vấn trước khi mua.
-Phiên bản 3:
-Mô tả ngắn: máy lọc không khí phòng ngủ giúp gia đình có trẻ nhỏ có thêm một lựa chọn hợp lý cho nhu cầu thường ngày.
-Lợi ích chính:
-- cảm biến bụi làm cho việc dùng tiện hơn.
-- màng lọc HEPA hỗ trợ đúng mối quan tâm chính.
+- Phù hợp với gia đình có trẻ nhỏ muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi tư vấn diện tích phòng miễn phí giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
 Đặc điểm nổi bật:
 - màng lọc HEPA.
 - chế độ ngủ yên tĩnh.
-Lời kêu gọi hành động: Lưu lại để so sánh khi cần.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+- cảm biến bụi.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: máy lọc không khí phòng ngủ hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với gia đình muốn chăm chút chất lượng không gian ngủ một cách vừa phải.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi.
+- Ghi chú thêm để cân nhắc: tư vấn diện tích phòng miễn phí.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emotional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">máy lọc không khí phòng ngủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: máy lọc không khí phòng ngủ.
 Từ khóa chính: màng lọc HEPA; chế độ ngủ yên tĩnh; cảm biến bụi.
@@ -3383,7 +4939,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. máy lọc không khí phòng ngủ dành cho gia đình có trẻ nhỏ trong những lúc phòng ngủ cần không gian yên tĩnh hơn, nhất là khi gia đình có trẻ nhỏ.
+Lợi ích chính:
+- Giúp bạn yên tâm hơn với nhu cầu màng lọc HEPA mà không phải đọc quá nhiều thông tin rối.
+- Chế độ ngủ yên tĩnh là điểm cộng rõ ràng khi dùng hằng ngày.
+- Cảm biến bụi giúp sản phẩm dễ được đưa vào thói quen hiện có.
+Đặc điểm nổi bật:
+- màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi.
+- Thông tin đi kèm: tư vấn diện tích phòng miễn phí.
+Góc cần biết: Bạn nên hỏi diện tích phòng, chế độ ngủ và lịch bảo trì màng lọc.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì ngại tiếng máy, chọn sai diện tích phòng hoặc không biết khi nào cần thay lọc, máy lọc không khí phòng ngủ là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi.
+Lợi ích chính:
+- Phù hợp với gia đình có trẻ nhỏ muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi tư vấn diện tích phòng miễn phí giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
+Đặc điểm nổi bật:
+- màng lọc HEPA.
+- chế độ ngủ yên tĩnh.
+- cảm biến bụi.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: máy lọc không khí phòng ngủ hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với gia đình muốn chăm chút chất lượng không gian ngủ một cách vừa phải.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi.
+- Ghi chú thêm để cân nhắc: tư vấn diện tích phòng miễn phí.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">máy lọc không khí phòng ngủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Thân thiện.
 Sản phẩm/dịch vụ: máy lọc không khí phòng ngủ.
 Từ khóa chính: màng lọc HEPA; chế độ ngủ yên tĩnh; cảm biến bụi.
@@ -3407,24 +5011,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Một lựa chọn thân thiện cho gia đình có trẻ nhỏ.
-Caption: máy lọc không khí phòng ngủ giúp việc hằng ngày nhẹ hơn nhờ màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi. Hiện có tư vấn diện tích phòng miễn phí, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #MayLocKhong #GiaDinhCo #MangLocHEPA
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của gia đình có trẻ nhỏ.
-Caption: Với chế độ ngủ yên tĩnh và cảm biến bụi, máy lọc không khí phòng ngủ cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. tư vấn diện tích phòng miễn phí là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #MayLocKhong #CheDoNgu #MuaSamThongMinh
-Phiên bản 3:
-Hook: Gợi ý dễ dùng cho gia đình có trẻ nhỏ một lựa chọn gọn gàng hơn.
-Caption: Khi xem máy lọc không khí phòng ngủ, hãy chú ý vào màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #MayLocKhong #CamBienBui #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Một món nhỏ, nhưng dùng đúng lúc thì thấy ngày nhẹ hơn một chút.
+Caption: máy lọc không khí phòng ngủ dành cho gia đình có trẻ nhỏ trong những lúc phòng ngủ cần không gian yên tĩnh hơn, nhất là khi gia đình có trẻ nhỏ. Mình sẽ nhìn vào màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi trước, rồi mới xét đến ưu đãi tư vấn diện tích phòng miễn phí. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên hỏi diện tích phòng, chế độ ngủ và lịch bảo trì màng lọc.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #MayLocKhongKhi #PhongNguYenTinh #GiaDinhCoTreNho
+Phiên bản 2:
+Hook: Mua sắm dễ chịu hơn khi thông tin đủ rõ và không bị thúc ép.
+Caption: Nếu bạn từng gặp chuyện ngại tiếng máy, chọn sai diện tích phòng hoặc không biết khi nào cần thay lọc, máy lọc không khí phòng ngủ là một lựa chọn đáng để lưu lại. Sản phẩm có màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Tư vấn diện tích phòng miễn phí là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #MayLocKhongKhi #PhongNguYenTinh #GiaDinhCoTreNho
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với máy lọc không khí phòng ngủ, hãy bắt đầu từ nhu cầu của gia đình có trẻ nhỏ: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với gia đình muốn chăm chút chất lượng không gian ngủ một cách vừa phải.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #MayLocKhongKhi #PhongNguYenTinh #GiaDinhCoTreNho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">máy lọc không khí phòng ngủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Khẩn cấp.
 Sản phẩm/dịch vụ: máy lọc không khí phòng ngủ.
 Từ khóa chính: màng lọc HEPA; chế độ ngủ yên tĩnh; cảm biến bụi.
@@ -3448,24 +5067,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Cần xem ngay cho gia đình có trẻ nhỏ.
-Caption: máy lọc không khí phòng ngủ giúp việc hằng ngày nhẹ hơn nhờ màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi. Hiện có tư vấn diện tích phòng miễn phí, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #MayLocKhong #GiaDinhCo #MangLocHEPA
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của gia đình có trẻ nhỏ.
-Caption: Với chế độ ngủ yên tĩnh và cảm biến bụi, máy lọc không khí phòng ngủ cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. tư vấn diện tích phòng miễn phí là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #MayLocKhong #CheDoNgu #MuaSamThongMinh
-Phiên bản 3:
-Hook: Đừng chần chừ với gia đình có trẻ nhỏ một lựa chọn gọn gàng hơn.
-Caption: Khi xem máy lọc không khí phòng ngủ, hãy chú ý vào màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #MayLocKhong #CamBienBui #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Đang cân nhắc thì nên xem kỹ hôm nay, nhưng không cần mua vội.
+Caption: máy lọc không khí phòng ngủ dành cho gia đình có trẻ nhỏ trong những lúc phòng ngủ cần không gian yên tĩnh hơn, nhất là khi gia đình có trẻ nhỏ. Mình sẽ nhìn vào màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi trước, rồi mới xét đến ưu đãi tư vấn diện tích phòng miễn phí. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên hỏi diện tích phòng, chế độ ngủ và lịch bảo trì màng lọc.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #MayLocKhongKhi #PhongNguYenTinh #GiaDinhCoTreNho
+Phiên bản 2:
+Hook: Ưu đãi chỉ đáng giữ lại khi sản phẩm thật sự hợp với cách bạn dùng.
+Caption: Nếu bạn từng gặp chuyện ngại tiếng máy, chọn sai diện tích phòng hoặc không biết khi nào cần thay lọc, máy lọc không khí phòng ngủ là một lựa chọn đáng để lưu lại. Sản phẩm có màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Tư vấn diện tích phòng miễn phí là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #MayLocKhongKhi #PhongNguYenTinh #GiaDinhCoTreNho
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với máy lọc không khí phòng ngủ, hãy bắt đầu từ nhu cầu của gia đình có trẻ nhỏ: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với gia đình muốn chăm chút chất lượng không gian ngủ một cách vừa phải.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #MayLocKhongKhi #PhongNguYenTinh #GiaDinhCoTreNho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">máy lọc không khí phòng ngủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Email Marketing với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: máy lọc không khí phòng ngủ.
 Từ khóa chính: màng lọc HEPA; chế độ ngủ yên tĩnh; cảm biến bụi.
@@ -3490,27 +5124,45 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Subject: Gợi ý máy lọc không khí phòng ngủ cho gia đình có trẻ nhỏ
-Preview text: Tóm tắt nhanh các điểm đáng cân nhắc trước khi chọn mua.
+    <t xml:space="preserve">Phiên bản 1:
+Subject: Gợi ý máy lọc không khí phòng ngủ cho nhu cầu dùng hằng ngày
+Preview text: Một vài điểm đáng xem trước khi bạn quyết định.
 Lời chào: Chào bạn,
-Nội dung chính: Nếu bạn đang tìm một lựa chọn phù hợp cho nhu cầu hằng ngày, máy lọc không khí phòng ngủ có các điểm nổi bật như màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi. Hiện có tư vấn diện tích phòng miễn phí, nên bạn có thể xem thêm thông tin trước khi quyết định.
-Lời kêu gọi hành động: Xem chi tiết sản phẩm hôm nay.
-Phiên bản 2:
-Subject: máy lọc không khí phòng ngủ có thể hợp với nhu cầu của bạn
-Preview text: Một vài lý do để gia đình có trẻ nhỏ cân nhắc sản phẩm này.
+Nội dung chính: Nếu bạn là gia đình có trẻ nhỏ, có lẽ điều bạn cần không phải một lời giới thiệu quá mạnh. Bạn cần biết máy lọc không khí phòng ngủ có hợp với bối cảnh phòng ngủ cần không gian yên tĩnh hơn, nhất là khi gia đình có trẻ nhỏ hay không.
+Sản phẩm này đáng xem nhờ màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi. Trong đó, màng lọc HEPA giúp xử lý nhu cầu chính; chế độ ngủ yên tĩnh và cảm biến bụi làm trải nghiệm dùng trọn vẹn hơn.
+Góc cần biết: Bạn nên hỏi diện tích phòng, chế độ ngủ và lịch bảo trì màng lọc. Hiện có tư vấn diện tích phòng miễn phí, bạn có thể xem như một điểm cộng nếu sản phẩm đã đúng nhu cầu.
+Lời kêu gọi hành động: Mở chi tiết sản phẩm hoặc nhắn shop để được tư vấn kỹ hơn.
+Phiên bản 2:
+Subject: Trước khi mua máy lọc không khí phòng ngủ, bạn có thể xem nhanh điểm này
+Preview text: Chọn chắc hơn khi biết sản phẩm giải quyết đúng việc gì.
 Lời chào: Chào bạn,
-Nội dung chính: máy lọc không khí phòng ngủ tập trung vào chế độ ngủ yên tĩnh, màng lọc HEPA và cảm biến bụi. Thông tin được viết theo đúng brief, không thêm chứng nhận hay số liệu ngoài phạm vi. tư vấn diện tích phòng miễn phí giúp bạn có thêm lý do so sánh.
-Lời kêu gọi hành động: Nhắn lại để được tư vấn lựa chọn phù hợp.
-Phiên bản 3:
-Subject: Xem nhanh máy lọc không khí phòng ngủ trước khi bạn chọn
-Preview text: Thông tin ngắn gọn, dễ so sánh và có ưu đãi đi kèm.
+Nội dung chính: Nhiều người phân vân vì ngại tiếng máy, chọn sai diện tích phòng hoặc không biết khi nào cần thay lọc. Vì vậy, với máy lọc không khí phòng ngủ, hãy nhìn vào nhu cầu thật trước: bạn cần màng lọc HEPA, muốn chế độ ngủ yên tĩnh, hay quan tâm nhiều hơn đến cảm biến bụi?
+Nếu câu trả lời khớp với cách bạn dùng hằng ngày, đây là lựa chọn đáng cân nhắc. Nếu chưa chắc, bạn có thể hỏi shop trước khi đặt.
+Góc cần biết: Tư vấn diện tích phòng miễn phí đang đi kèm, nhưng quyết định cuối cùng vẫn nên dựa trên mức độ phù hợp.
+Lời kêu gọi hành động: Trả lời tin nhắn này với nhu cầu của bạn, shop sẽ gợi ý cụ thể hơn.
+Phiên bản 3:
+Subject: máy lọc không khí phòng ngủ có thể là món bạn đang tìm
+Preview text: Rõ lợi ích, rõ tình huống dùng, không cần quyết định vội.
 Lời chào: Chào bạn,
-Nội dung chính: Với gia đình có trẻ nhỏ, một sản phẩm dễ hiểu thường giúp quyết định nhanh hơn. máy lọc không khí phòng ngủ có màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi; ngoài ra còn có tư vấn diện tích phòng miễn phí để bạn cân nhắc thêm.
-Lời kêu gọi hành động: Mở trang sản phẩm để xem thêm chi tiết.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Nội dung chính: Hợp với gia đình muốn chăm chút chất lượng không gian ngủ một cách vừa phải. máy lọc không khí phòng ngủ tập trung vào màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi, phù hợp với gia đình có trẻ nhỏ khi muốn một lựa chọn thực tế hơn cho sinh hoạt hằng ngày.
+Bạn có thể cân nhắc sản phẩm này nếu đang cần giải quyết chuyện ngại tiếng máy, chọn sai diện tích phòng hoặc không biết khi nào cần thay lọc. Còn nếu muốn chắc hơn, hãy hỏi shop về tình huống dùng của bạn.
+Góc cần biết: Bạn nên hỏi diện tích phòng, chế độ ngủ và lịch bảo trì màng lọc.
+Lời kêu gọi hành động: Xem chi tiết hoặc nhắn shop trước khi chốt đơn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">máy lọc không khí phòng ngủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Lời Kêu Gọi Hành Động với tone Thân thiện.
 Sản phẩm/dịch vụ: máy lọc không khí phòng ngủ.
 Từ khóa chính: màng lọc HEPA; chế độ ngủ yên tĩnh; cảm biến bụi.
@@ -3532,18 +5184,30 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Lời kêu gọi hành động chính: Mua máy lọc không khí phòng ngủ ngay hôm nay
-Microcopy: Phù hợp cho gia đình có trẻ nhỏ, có tư vấn diện tích phòng miễn phí và thông tin rõ ràng để bạn chọn nhanh.
-Phiên bản 2:
-Lời kêu gọi hành động chính: Chọn máy lọc không khí phòng ngủ cho nhu cầu hiện tại
-Microcopy: Tập trung vào màng lọc HEPA và chế độ ngủ yên tĩnh, giúp bạn quyết định dễ hơn.
-Phiên bản 3:
-Lời kêu gọi hành động chính: Nhắn shop để được tư vấn máy lọc không khí phòng ngủ
-Microcopy: Bạn có thể hỏi thêm về cảm biến bụi và tư vấn diện tích phòng miễn phí trước khi quyết định.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Lời kêu gọi hành động chính: Xem máy lọc không khí phòng ngủ có hợp với bạn không
+Microcopy: Dành cho gia đình có trẻ nhỏ, nổi bật với màng lọc HEPA, chế độ ngủ yên tĩnh và cảm biến bụi. Có tư vấn diện tích phòng miễn phí nếu bạn muốn cân nhắc thêm.
+Phiên bản 2:
+Lời kêu gọi hành động chính: Nhắn shop để chọn máy lọc không khí phòng ngủ đúng nhu cầu
+Microcopy: Kể nhanh bạn dùng trong bối cảnh nào, shop sẽ gợi ý theo tình huống thật như phòng ngủ cần không gian yên tĩnh hơn, nhất là khi gia đình có trẻ nhỏ.
+Phiên bản 3:
+Lời kêu gọi hành động chính: Lưu máy lọc không khí phòng ngủ để so sánh trước khi mua
+Microcopy: Phù hợp hơn khi bạn muốn giải quyết chuyện ngại tiếng máy, chọn sai diện tích phòng hoặc không biết khi nào cần thay lọc mà vẫn cần một lựa chọn rõ ràng, dễ hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">máy lọc không khí phòng ngủ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Khẩn cấp.
 Sản phẩm/dịch vụ: ví da mini nhiều ngăn.
 Từ khóa chính: da mềm; nhiều ngăn thẻ; kích thước nhỏ.
@@ -3566,24 +5230,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Đừng chần chừ với ví da mini nhiều ngăn cho người thích phụ kiện gọn gàng với da mềm.
-Subheadline: Tập trung vào nhiều ngăn thẻ và kích thước nhỏ, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: ví da mini nhiều ngăn là lựa chọn đáng cân nhắc cho người thích phụ kiện gọn gàng.
-Subheadline: Điểm mạnh nằm ở nhiều ngăn thẻ, da mềm và khắc tên theo yêu cầu để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Giữ nhịp nhanh hơn cho ví da mini nhiều ngăn nếu bạn cần da mềm và nhiều ngăn thẻ.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>ví da mini nhiều ngăn</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: ví da mini nhiều ngăn: gọn hơn cho những lúc da mềm thật sự quan trọng.
+Subheadline: Dành cho người thích phụ kiện gọn gàng, nhất là khi ra ngoài gọn nhẹ, chỉ cần thẻ, ít tiền mặt và vài món nhỏ dễ lấy. Điểm đáng xem là da mềm, nhiều ngăn thẻ và kích thước nhỏ; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên cân nhắc số thẻ hay mang và nhu cầu khắc tên.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với ví da mini nhiều ngăn.
+Subheadline: Nếu bạn từng ngại chuyện ngại ví dày cộm, khó tìm thẻ hoặc phụ kiện nhìn không đủ chỉn chu, hãy bắt đầu từ ba điểm: da mềm, nhiều ngăn thẻ và kích thước nhỏ. Ưu đãi hiện có: khắc tên theo yêu cầu.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn ví da mini nhiều ngăn vừa đủ thực tế cho người thích phụ kiện gọn gàng.
+Subheadline: Hợp với người thích phụ kiện nhỏ nhưng vẫn muốn mọi thứ có chỗ riêng. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Khắc tên theo yêu cầu là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ví da mini nhiều ngăn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Tiêu Đề Quảng Cáo với tone Thân thiện.
 Sản phẩm/dịch vụ: ví da mini nhiều ngăn.
 Từ khóa chính: da mềm; nhiều ngăn thẻ; kích thước nhỏ.
@@ -3606,21 +5282,36 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Headline: Gợi ý dễ dùng cho ví da mini nhiều ngăn cho người thích phụ kiện gọn gàng với da mềm.
-Subheadline: Tập trung vào nhiều ngăn thẻ và kích thước nhỏ, phù hợp khi bạn cần một lựa chọn rõ ràng và nhanh.
-Lời kêu gọi hành động: Xem ngay để chọn đúng mẫu.
-Phiên bản 2:
-Headline: ví da mini nhiều ngăn là lựa chọn đáng cân nhắc cho người thích phụ kiện gọn gàng.
-Subheadline: Điểm mạnh nằm ở nhiều ngăn thẻ, da mềm và khắc tên theo yêu cầu để bạn so sánh dễ hơn.
-Lời kêu gọi hành động: Nhắn shop để được tư vấn nhanh.
-Phiên bản 3:
-Headline: Thêm tiện lợi cho ví da mini nhiều ngăn nếu bạn cần da mềm và nhiều ngăn thẻ.
-Subheadline: Cách trình bày gọn, bám sát nhu cầu thật và không nói quá công dụng.
-Lời kêu gọi hành động: Mở chi tiết sản phẩm ngay hôm nay.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Headline: ví da mini nhiều ngăn: gọn hơn cho những lúc da mềm thật sự quan trọng.
+Subheadline: Dành cho người thích phụ kiện gọn gàng, nhất là khi ra ngoài gọn nhẹ, chỉ cần thẻ, ít tiền mặt và vài món nhỏ dễ lấy. Điểm đáng xem là da mềm, nhiều ngăn thẻ và kích thước nhỏ; đủ rõ để bạn cân nhắc mà không cần một lời hứa quá tay.
+Góc cần biết: Bạn nên cân nhắc số thẻ hay mang và nhu cầu khắc tên.
+Lời kêu gọi hành động: Nhắn shop hỏi mẫu phù hợp trước khi chốt.
+Phiên bản 2:
+Headline: Bớt một nỗi lo nhỏ mỗi ngày với ví da mini nhiều ngăn.
+Subheadline: Nếu bạn từng ngại chuyện ngại ví dày cộm, khó tìm thẻ hoặc phụ kiện nhìn không đủ chỉn chu, hãy bắt đầu từ ba điểm: da mềm, nhiều ngăn thẻ và kích thước nhỏ. Ưu đãi hiện có: khắc tên theo yêu cầu.
+Góc cần biết: Chọn theo thói quen dùng thật sẽ dễ hài lòng hơn chọn vì một câu quảng cáo hay.
+Lời kêu gọi hành động: Xem chi tiết sản phẩm rồi lưu lại để so sánh.
+Phiên bản 3:
+Headline: Một lựa chọn ví da mini nhiều ngăn vừa đủ thực tế cho người thích phụ kiện gọn gàng.
+Subheadline: Hợp với người thích phụ kiện nhỏ nhưng vẫn muốn mọi thứ có chỗ riêng. Sản phẩm phù hợp khi bạn muốn thông tin rõ, lợi ích cụ thể và một lời nhắc mua hàng nhẹ nhàng.
+Góc cần biết: Khắc tên theo yêu cầu là điểm cộng thêm, không phải lý do duy nhất để quyết định.
+Lời kêu gọi hành động: Hỏi shop nếu bạn muốn kiểm tra kỹ trước khi mua.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">headline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ví da mini nhiều ngăn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Cảm xúc.
 Sản phẩm/dịch vụ: ví da mini nhiều ngăn.
 Từ khóa chính: da mềm; nhiều ngăn thẻ; kích thước nhỏ.
@@ -3644,36 +5335,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Mô tả ngắn: ví da mini nhiều ngăn dành cho người thích phụ kiện gọn gàng, nhấn vào trải nghiệm dùng rõ ràng và dễ hiểu.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. ví da mini nhiều ngăn dành cho người thích phụ kiện gọn gàng trong những lúc ra ngoài gọn nhẹ, chỉ cần thẻ, ít tiền mặt và vài món nhỏ dễ lấy.
 Lợi ích chính:
-- Hỗ trợ nhu cầu thực tế nhờ da mềm và nhiều ngăn thẻ.
-- Giúp bạn cân nhắc nhanh hơn với thông tin đúng brief và khắc tên theo yêu cầu.
+- Giúp bạn yên tâm hơn với nhu cầu da mềm mà không phải đọc quá nhiều thông tin rối.
+- Nhiều ngăn thẻ là điểm cộng rõ ràng khi dùng hằng ngày.
+- Kích thước nhỏ giúp sản phẩm dễ được đưa vào thói quen hiện có.
 Đặc điểm nổi bật:
-- da mềm.
-- kích thước nhỏ.
-Lời kêu gọi hành động: Xem chi tiết để chọn mẫu phù hợp.
-Phiên bản 2:
-Mô tả ngắn: Nếu bạn là người thích phụ kiện gọn gàng, ví da mini nhiều ngăn là một lựa chọn gọn gàng, dễ dùng và sát nhu cầu.
+- da mềm, nhiều ngăn thẻ và kích thước nhỏ.
+- Thông tin đi kèm: khắc tên theo yêu cầu.
+Góc cần biết: Bạn nên cân nhắc số thẻ hay mang và nhu cầu khắc tên.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì ngại ví dày cộm, khó tìm thẻ hoặc phụ kiện nhìn không đủ chỉn chu, ví da mini nhiều ngăn là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: da mềm, nhiều ngăn thẻ và kích thước nhỏ.
 Lợi ích chính:
-- Mang lại cảm giác yên tâm khi xem thông tin rõ ràng.
-- Tập trung vào nhiều ngăn thẻ và kích thước nhỏ để phục vụ dùng hằng ngày.
-Đặc điểm nổi bật:
-- nhiều ngăn thẻ.
-- khắc tên theo yêu cầu.
-Lời kêu gọi hành động: Nhắn tin để được tư vấn trước khi mua.
-Phiên bản 3:
-Mô tả ngắn: ví da mini nhiều ngăn giúp người thích phụ kiện gọn gàng có thêm một lựa chọn hợp lý cho nhu cầu thường ngày.
-Lợi ích chính:
-- kích thước nhỏ làm cho việc dùng tiện hơn.
-- da mềm hỗ trợ đúng mối quan tâm chính.
+- Phù hợp với người thích phụ kiện gọn gàng muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi khắc tên theo yêu cầu giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
 Đặc điểm nổi bật:
 - da mềm.
 - nhiều ngăn thẻ.
-Lời kêu gọi hành động: Lưu lại để so sánh khi cần.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+- kích thước nhỏ.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: ví da mini nhiều ngăn hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người thích phụ kiện nhỏ nhưng vẫn muốn mọi thứ có chỗ riêng.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin da mềm, nhiều ngăn thẻ và kích thước nhỏ.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: da mềm, nhiều ngăn thẻ và kích thước nhỏ.
+- Ghi chú thêm để cân nhắc: khắc tên theo yêu cầu.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">emotional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ví da mini nhiều ngăn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Mô Tả Sản Phẩm với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: ví da mini nhiều ngăn.
 Từ khóa chính: da mềm; nhiều ngăn thẻ; kích thước nhỏ.
@@ -3697,7 +5407,55 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Mô tả ngắn: Có những món không cần làm cuộc sống thay đổi hẳn, chỉ cần làm một việc nhỏ trở nên nhẹ hơn. ví da mini nhiều ngăn dành cho người thích phụ kiện gọn gàng trong những lúc ra ngoài gọn nhẹ, chỉ cần thẻ, ít tiền mặt và vài món nhỏ dễ lấy.
+Lợi ích chính:
+- Giúp bạn yên tâm hơn với nhu cầu da mềm mà không phải đọc quá nhiều thông tin rối.
+- Nhiều ngăn thẻ là điểm cộng rõ ràng khi dùng hằng ngày.
+- Kích thước nhỏ giúp sản phẩm dễ được đưa vào thói quen hiện có.
+Đặc điểm nổi bật:
+- da mềm, nhiều ngăn thẻ và kích thước nhỏ.
+- Thông tin đi kèm: khắc tên theo yêu cầu.
+Góc cần biết: Bạn nên cân nhắc số thẻ hay mang và nhu cầu khắc tên.
+Lời kêu gọi hành động: Nhắn shop mô tả nhu cầu của bạn để được gợi ý mẫu phù hợp.
+Phiên bản 2:
+Mô tả ngắn: Nếu bạn từng phân vân vì ngại ví dày cộm, khó tìm thẻ hoặc phụ kiện nhìn không đủ chỉn chu, ví da mini nhiều ngăn là một lựa chọn đáng xem. Cách sản phẩm thuyết phục không nằm ở lời nói lớn, mà ở những chi tiết đủ dùng: da mềm, nhiều ngăn thẻ và kích thước nhỏ.
+Lợi ích chính:
+- Phù hợp với người thích phụ kiện gọn gàng muốn mua chắc tay hơn.
+- Dễ so sánh vì các điểm chính được nói thẳng vào nhu cầu dùng thật.
+- Ưu đãi khắc tên theo yêu cầu giúp bạn có thêm lý do cân nhắc nếu sản phẩm đã đúng nhu cầu.
+Đặc điểm nổi bật:
+- da mềm.
+- nhiều ngăn thẻ.
+- kích thước nhỏ.
+Góc cần biết: Nên chọn khi sản phẩm giải quyết đúng việc bạn đang cần, không chỉ vì đang có ưu đãi.
+Lời kêu gọi hành động: Xem chi tiết và hỏi shop trước nếu còn điểm chưa chắc.
+Phiên bản 3:
+Mô tả ngắn: ví da mini nhiều ngăn hợp với người thích một lựa chọn rõ ràng, không phô trương và dễ đưa vào sinh hoạt mỗi ngày.
+Lợi ích chính:
+- Hợp với người thích phụ kiện nhỏ nhưng vẫn muốn mọi thứ có chỗ riêng.
+- Giảm cảm giác phải đoán mò khi mua online nhờ các thông tin da mềm, nhiều ngăn thẻ và kích thước nhỏ.
+- Tạo cảm giác được tư vấn thay vì bị thúc ép.
+Đặc điểm nổi bật:
+- Điểm chính dễ kiểm tra: da mềm, nhiều ngăn thẻ và kích thước nhỏ.
+- Ghi chú thêm để cân nhắc: khắc tên theo yêu cầu.
+Góc cần biết: Mua đúng nhu cầu sẽ dễ dùng lâu hơn mua vì thấy vội.
+Lời kêu gọi hành động: Lưu lại để so sánh hoặc nhắn shop hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ví da mini nhiều ngăn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Thân thiện.
 Sản phẩm/dịch vụ: ví da mini nhiều ngăn.
 Từ khóa chính: da mềm; nhiều ngăn thẻ; kích thước nhỏ.
@@ -3721,24 +5479,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Một lựa chọn thân thiện cho người thích phụ kiện gọn gàng.
-Caption: ví da mini nhiều ngăn giúp việc hằng ngày nhẹ hơn nhờ da mềm, nhiều ngăn thẻ và kích thước nhỏ. Hiện có khắc tên theo yêu cầu, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #ViDaMini #NguoiThichPhu #DaMem
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của người thích phụ kiện gọn gàng.
-Caption: Với nhiều ngăn thẻ và kích thước nhỏ, ví da mini nhiều ngăn cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. khắc tên theo yêu cầu là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #ViDaMini #NhieuNganThe #MuaSamThongMinh
-Phiên bản 3:
-Hook: Gợi ý dễ dùng cho người thích phụ kiện gọn gàng một lựa chọn gọn gàng hơn.
-Caption: Khi xem ví da mini nhiều ngăn, hãy chú ý vào da mềm, nhiều ngăn thẻ và kích thước nhỏ. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #ViDaMini #KichThuocNho #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Một món nhỏ, nhưng dùng đúng lúc thì thấy ngày nhẹ hơn một chút.
+Caption: ví da mini nhiều ngăn dành cho người thích phụ kiện gọn gàng trong những lúc ra ngoài gọn nhẹ, chỉ cần thẻ, ít tiền mặt và vài món nhỏ dễ lấy. Mình sẽ nhìn vào da mềm, nhiều ngăn thẻ và kích thước nhỏ trước, rồi mới xét đến ưu đãi khắc tên theo yêu cầu. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên cân nhắc số thẻ hay mang và nhu cầu khắc tên.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #ViDaMini #PhuKienGonGang #KhacTenTheoYeuCau
+Phiên bản 2:
+Hook: Mua sắm dễ chịu hơn khi thông tin đủ rõ và không bị thúc ép.
+Caption: Nếu bạn từng gặp chuyện ngại ví dày cộm, khó tìm thẻ hoặc phụ kiện nhìn không đủ chỉn chu, ví da mini nhiều ngăn là một lựa chọn đáng để lưu lại. Sản phẩm có da mềm, nhiều ngăn thẻ và kích thước nhỏ, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Khắc tên theo yêu cầu là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #ViDaMini #PhuKienGonGang #KhacTenTheoYeuCau
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với ví da mini nhiều ngăn, hãy bắt đầu từ nhu cầu của người thích phụ kiện gọn gàng: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm da mềm, nhiều ngăn thẻ và kích thước nhỏ khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người thích phụ kiện nhỏ nhưng vẫn muốn mọi thứ có chỗ riêng.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #ViDaMini #PhuKienGonGang #KhacTenTheoYeuCau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ví da mini nhiều ngăn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Social Media Post với tone Khẩn cấp.
 Sản phẩm/dịch vụ: ví da mini nhiều ngăn.
 Từ khóa chính: da mềm; nhiều ngăn thẻ; kích thước nhỏ.
@@ -3762,24 +5535,39 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Hook: Cần xem ngay cho người thích phụ kiện gọn gàng.
-Caption: ví da mini nhiều ngăn giúp việc hằng ngày nhẹ hơn nhờ da mềm, nhiều ngăn thẻ và kích thước nhỏ. Hiện có khắc tên theo yêu cầu, phù hợp nếu bạn đang tìm một lựa chọn rõ ràng, dễ cân nhắc.
-Lời kêu gọi hành động: Lưu lại hoặc nhắn shop để hỏi thêm.
-Hashtags: #ViDaMini #NguoiThichPhu #DaMem
-Phiên bản 2:
-Hook: Đừng để nhu cầu nhỏ làm chậm nhịp của người thích phụ kiện gọn gàng.
-Caption: Với nhiều ngăn thẻ và kích thước nhỏ, ví da mini nhiều ngăn cho cảm giác thực tế, dễ hiểu và không nói quá công dụng. khắc tên theo yêu cầu là điểm cộng thêm nếu bạn đang so sánh lựa chọn.
-Lời kêu gọi hành động: Bình luận nhu cầu của bạn để được gợi ý.
-Hashtags: #ViDaMini #NhieuNganThe #MuaSamThongMinh
-Phiên bản 3:
-Hook: Đừng chần chừ với người thích phụ kiện gọn gàng một lựa chọn gọn gàng hơn.
-Caption: Khi xem ví da mini nhiều ngăn, hãy chú ý vào da mềm, nhiều ngăn thẻ và kích thước nhỏ. Đây là phần thông tin đủ để bạn cân nhắc trước khi quyết định.
-Lời kêu gọi hành động: Nhắn tin để kiểm tra mẫu phù hợp.
-Hashtags: #ViDaMini #KichThuocNho #ThuongMaiDienTu</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+    <t xml:space="preserve">Phiên bản 1:
+Hook: Đang cân nhắc thì nên xem kỹ hôm nay, nhưng không cần mua vội.
+Caption: ví da mini nhiều ngăn dành cho người thích phụ kiện gọn gàng trong những lúc ra ngoài gọn nhẹ, chỉ cần thẻ, ít tiền mặt và vài món nhỏ dễ lấy. Mình sẽ nhìn vào da mềm, nhiều ngăn thẻ và kích thước nhỏ trước, rồi mới xét đến ưu đãi khắc tên theo yêu cầu. Vậy mới biết đây là món hợp thật hay chỉ là món nghe có vẻ hay.
+Góc cần biết: Bạn nên cân nhắc số thẻ hay mang và nhu cầu khắc tên.
+Lời kêu gọi hành động: Nhắn shop nếu bạn muốn được gợi ý theo nhu cầu riêng.
+Hashtags: #ViDaMini #PhuKienGonGang #KhacTenTheoYeuCau
+Phiên bản 2:
+Hook: Ưu đãi chỉ đáng giữ lại khi sản phẩm thật sự hợp với cách bạn dùng.
+Caption: Nếu bạn từng gặp chuyện ngại ví dày cộm, khó tìm thẻ hoặc phụ kiện nhìn không đủ chỉn chu, ví da mini nhiều ngăn là một lựa chọn đáng để lưu lại. Sản phẩm có da mềm, nhiều ngăn thẻ và kích thước nhỏ, vừa đủ để bạn so sánh nhanh mà không cần đọc quá nhiều lời quảng cáo.
+Góc cần biết: Khắc tên theo yêu cầu là điểm cộng thêm khi sản phẩm đã phù hợp.
+Lời kêu gọi hành động: Lưu bài này lại để xem lại trước khi chọn.
+Hashtags: #ViDaMini #PhuKienGonGang #KhacTenTheoYeuCau
+Phiên bản 3:
+Hook: Có những quyết định mua hàng nên chậm lại một nhịp để chọn đúng hơn.
+Caption: Với ví da mini nhiều ngăn, hãy bắt đầu từ nhu cầu của người thích phụ kiện gọn gàng: cần gì, dùng lúc nào, có vướng điểm nào không. Nếu các điểm da mềm, nhiều ngăn thẻ và kích thước nhỏ khớp với thói quen của bạn, sản phẩm này đáng được cân nhắc.
+Góc cần biết: Hợp với người thích phụ kiện nhỏ nhưng vẫn muốn mọi thứ có chỗ riêng.
+Lời kêu gọi hành động: Bình luận nhu cầu hoặc nhắn shop để được tư vấn cụ thể hơn.
+Hashtags: #ViDaMini #PhuKienGonGang #KhacTenTheoYeuCau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">urgent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">social</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ví da mini nhiều ngăn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Email Marketing với tone Chuyên nghiệp.
 Sản phẩm/dịch vụ: ví da mini nhiều ngăn.
 Từ khóa chính: da mềm; nhiều ngăn thẻ; kích thước nhỏ.
@@ -3804,27 +5592,45 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Subject: Gợi ý ví da mini nhiều ngăn cho người thích phụ kiện gọn gàng
-Preview text: Tóm tắt nhanh các điểm đáng cân nhắc trước khi chọn mua.
+    <t xml:space="preserve">Phiên bản 1:
+Subject: Gợi ý ví da mini nhiều ngăn cho nhu cầu dùng hằng ngày
+Preview text: Một vài điểm đáng xem trước khi bạn quyết định.
 Lời chào: Chào bạn,
-Nội dung chính: Nếu bạn đang tìm một lựa chọn phù hợp cho nhu cầu hằng ngày, ví da mini nhiều ngăn có các điểm nổi bật như da mềm, nhiều ngăn thẻ và kích thước nhỏ. Hiện có khắc tên theo yêu cầu, nên bạn có thể xem thêm thông tin trước khi quyết định.
-Lời kêu gọi hành động: Xem chi tiết sản phẩm hôm nay.
-Phiên bản 2:
-Subject: ví da mini nhiều ngăn có thể hợp với nhu cầu của bạn
-Preview text: Một vài lý do để người thích phụ kiện gọn gàng cân nhắc sản phẩm này.
+Nội dung chính: Nếu bạn là người thích phụ kiện gọn gàng, có lẽ điều bạn cần không phải một lời giới thiệu quá mạnh. Bạn cần biết ví da mini nhiều ngăn có hợp với bối cảnh ra ngoài gọn nhẹ, chỉ cần thẻ, ít tiền mặt và vài món nhỏ dễ lấy hay không.
+Sản phẩm này đáng xem nhờ da mềm, nhiều ngăn thẻ và kích thước nhỏ. Trong đó, da mềm giúp xử lý nhu cầu chính; nhiều ngăn thẻ và kích thước nhỏ làm trải nghiệm dùng trọn vẹn hơn.
+Góc cần biết: Bạn nên cân nhắc số thẻ hay mang và nhu cầu khắc tên. Hiện có khắc tên theo yêu cầu, bạn có thể xem như một điểm cộng nếu sản phẩm đã đúng nhu cầu.
+Lời kêu gọi hành động: Mở chi tiết sản phẩm hoặc nhắn shop để được tư vấn kỹ hơn.
+Phiên bản 2:
+Subject: Trước khi mua ví da mini nhiều ngăn, bạn có thể xem nhanh điểm này
+Preview text: Chọn chắc hơn khi biết sản phẩm giải quyết đúng việc gì.
 Lời chào: Chào bạn,
-Nội dung chính: ví da mini nhiều ngăn tập trung vào nhiều ngăn thẻ, da mềm và kích thước nhỏ. Thông tin được viết theo đúng brief, không thêm chứng nhận hay số liệu ngoài phạm vi. khắc tên theo yêu cầu giúp bạn có thêm lý do so sánh.
-Lời kêu gọi hành động: Nhắn lại để được tư vấn lựa chọn phù hợp.
-Phiên bản 3:
-Subject: Xem nhanh ví da mini nhiều ngăn trước khi bạn chọn
-Preview text: Thông tin ngắn gọn, dễ so sánh và có ưu đãi đi kèm.
+Nội dung chính: Nhiều người phân vân vì ngại ví dày cộm, khó tìm thẻ hoặc phụ kiện nhìn không đủ chỉn chu. Vì vậy, với ví da mini nhiều ngăn, hãy nhìn vào nhu cầu thật trước: bạn cần da mềm, muốn nhiều ngăn thẻ, hay quan tâm nhiều hơn đến kích thước nhỏ?
+Nếu câu trả lời khớp với cách bạn dùng hằng ngày, đây là lựa chọn đáng cân nhắc. Nếu chưa chắc, bạn có thể hỏi shop trước khi đặt.
+Góc cần biết: Khắc tên theo yêu cầu đang đi kèm, nhưng quyết định cuối cùng vẫn nên dựa trên mức độ phù hợp.
+Lời kêu gọi hành động: Trả lời tin nhắn này với nhu cầu của bạn, shop sẽ gợi ý cụ thể hơn.
+Phiên bản 3:
+Subject: ví da mini nhiều ngăn có thể là món bạn đang tìm
+Preview text: Rõ lợi ích, rõ tình huống dùng, không cần quyết định vội.
 Lời chào: Chào bạn,
-Nội dung chính: Với người thích phụ kiện gọn gàng, một sản phẩm dễ hiểu thường giúp quyết định nhanh hơn. ví da mini nhiều ngăn có da mềm, nhiều ngăn thẻ và kích thước nhỏ; ngoài ra còn có khắc tên theo yêu cầu để bạn cân nhắc thêm.
-Lời kêu gọi hành động: Mở trang sản phẩm để xem thêm chi tiết.</t>
-  </si>
-  <si>
-    <t>Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
+Nội dung chính: Hợp với người thích phụ kiện nhỏ nhưng vẫn muốn mọi thứ có chỗ riêng. ví da mini nhiều ngăn tập trung vào da mềm, nhiều ngăn thẻ và kích thước nhỏ, phù hợp với người thích phụ kiện gọn gàng khi muốn một lựa chọn thực tế hơn cho sinh hoạt hằng ngày.
+Bạn có thể cân nhắc sản phẩm này nếu đang cần giải quyết chuyện ngại ví dày cộm, khó tìm thẻ hoặc phụ kiện nhìn không đủ chỉn chu. Còn nếu muốn chắc hơn, hãy hỏi shop về tình huống dùng của bạn.
+Góc cần biết: Bạn nên cân nhắc số thẻ hay mang và nhu cầu khắc tên.
+Lời kêu gọi hành động: Xem chi tiết hoặc nhắn shop trước khi chốt đơn.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">professional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ví da mini nhiều ngăn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bạn là chuyên gia copywriting cho ngành Thương Mại Điện Tử.
 Hãy viết Lời Kêu Gọi Hành Động với tone Thân thiện.
 Sản phẩm/dịch vụ: ví da mini nhiều ngăn.
 Từ khóa chính: da mềm; nhiều ngăn thẻ; kích thước nhỏ.
@@ -3846,15 +5652,27 @@
 Temperature tham khảo: 0.7.</t>
   </si>
   <si>
-    <t>Phiên bản 1:
-Lời kêu gọi hành động chính: Mua ví da mini nhiều ngăn ngay hôm nay
-Microcopy: Phù hợp cho người thích phụ kiện gọn gàng, có khắc tên theo yêu cầu và thông tin rõ ràng để bạn chọn nhanh.
-Phiên bản 2:
-Lời kêu gọi hành động chính: Chọn ví da mini nhiều ngăn cho nhu cầu hiện tại
-Microcopy: Tập trung vào da mềm và nhiều ngăn thẻ, giúp bạn quyết định dễ hơn.
-Phiên bản 3:
-Lời kêu gọi hành động chính: Nhắn shop để được tư vấn ví da mini nhiều ngăn
-Microcopy: Bạn có thể hỏi thêm về kích thước nhỏ và khắc tên theo yêu cầu trước khi quyết định.</t>
+    <t xml:space="preserve">Phiên bản 1:
+Lời kêu gọi hành động chính: Xem ví da mini nhiều ngăn có hợp với bạn không
+Microcopy: Dành cho người thích phụ kiện gọn gàng, nổi bật với da mềm, nhiều ngăn thẻ và kích thước nhỏ. Có khắc tên theo yêu cầu nếu bạn muốn cân nhắc thêm.
+Phiên bản 2:
+Lời kêu gọi hành động chính: Nhắn shop để chọn ví da mini nhiều ngăn đúng nhu cầu
+Microcopy: Kể nhanh bạn dùng trong bối cảnh nào, shop sẽ gợi ý theo tình huống thật như ra ngoài gọn nhẹ, chỉ cần thẻ, ít tiền mặt và vài món nhỏ dễ lấy.
+Phiên bản 3:
+Lời kêu gọi hành động chính: Lưu ví da mini nhiều ngăn để so sánh trước khi mua
+Microcopy: Phù hợp hơn khi bạn muốn giải quyết chuyện ngại ví dày cộm, khó tìm thẻ hoặc phụ kiện nhìn không đủ chỉn chu mà vẫn cần một lựa chọn rõ ràng, dễ hỏi thêm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecommerce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">friendly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ví da mini nhiều ngăn</t>
   </si>
 </sst>
 </file>
@@ -4259,9 +6077,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B81724B5-3AFA-4C3F-A26F-99DBA64F7C78}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{B81724B5-3AFA-4C3F-A26F-99DBA64F7C78}">
   <dimension ref="A1:F97"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" ns3:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="62.77734375" customWidth="1"/>
     <col min="2" max="2" width="82.77734375" customWidth="1"/>
@@ -4270,7 +6088,7 @@
     <col min="6" max="6" width="28.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4290,7 +6108,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -4310,7 +6128,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -4318,1896 +6136,1896 @@
         <v>13</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>72</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>20</v>
+        <v>75</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>18</v>
+        <v>76</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>41</v>
+        <v>79</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>42</v>
+        <v>84</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>9</v>
+        <v>87</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>14</v>
+        <v>99</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>8</v>
+        <v>104</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>9</v>
+        <v>105</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>10</v>
+        <v>106</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>108</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>52</v>
+        <v>109</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>14</v>
+        <v>111</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>54</v>
+        <v>115</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>17</v>
+        <v>117</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>18</v>
+        <v>118</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>8</v>
+        <v>122</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>56</v>
+        <v>126</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>8</v>
+        <v>128</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>14</v>
+        <v>129</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>23</v>
+        <v>130</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>59</v>
+        <v>133</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>9</v>
+        <v>135</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>23</v>
+        <v>136</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>61</v>
+        <v>139</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>8</v>
+        <v>140</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>28</v>
+        <v>142</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>8</v>
+        <v>146</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>14</v>
+        <v>147</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>31</v>
+        <v>148</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>65</v>
+        <v>151</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>8</v>
+        <v>152</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>9</v>
+        <v>153</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>67</v>
+        <v>156</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>68</v>
+        <v>157</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>8</v>
+        <v>158</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>14</v>
+        <v>159</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>10</v>
+        <v>160</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>69</v>
+        <v>162</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>70</v>
+        <v>163</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>8</v>
+        <v>164</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>17</v>
+        <v>165</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>18</v>
+        <v>166</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>71</v>
+        <v>168</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>70</v>
+        <v>169</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>8</v>
+        <v>170</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>20</v>
+        <v>171</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>18</v>
+        <v>172</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>72</v>
+        <v>174</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>73</v>
+        <v>175</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>8</v>
+        <v>176</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>14</v>
+        <v>177</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>23</v>
+        <v>178</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>74</v>
+        <v>180</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>75</v>
+        <v>181</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>8</v>
+        <v>182</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>9</v>
+        <v>183</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>23</v>
+        <v>184</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>76</v>
+        <v>186</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>77</v>
+        <v>187</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>8</v>
+        <v>188</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>20</v>
+        <v>189</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>28</v>
+        <v>190</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>78</v>
+        <v>192</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>79</v>
+        <v>193</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>8</v>
+        <v>194</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>14</v>
+        <v>195</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>31</v>
+        <v>196</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>80</v>
+        <v>198</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>81</v>
+        <v>199</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>9</v>
+        <v>201</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>10</v>
+        <v>202</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>84</v>
+        <v>205</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>8</v>
+        <v>206</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>14</v>
+        <v>207</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>10</v>
+        <v>208</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>85</v>
+        <v>210</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>86</v>
+        <v>211</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>8</v>
+        <v>212</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>17</v>
+        <v>213</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>18</v>
+        <v>214</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>87</v>
+        <v>216</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>86</v>
+        <v>217</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>8</v>
+        <v>218</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>18</v>
+        <v>220</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>88</v>
+        <v>222</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>89</v>
+        <v>223</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>8</v>
+        <v>224</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>14</v>
+        <v>225</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>23</v>
+        <v>226</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>90</v>
+        <v>228</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>91</v>
+        <v>229</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>8</v>
+        <v>230</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>9</v>
+        <v>231</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>23</v>
+        <v>232</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>92</v>
+        <v>234</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>93</v>
+        <v>235</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>8</v>
+        <v>236</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>20</v>
+        <v>237</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>28</v>
+        <v>238</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>94</v>
+        <v>240</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>95</v>
+        <v>241</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>8</v>
+        <v>242</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>14</v>
+        <v>243</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>31</v>
+        <v>244</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>246</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>97</v>
+        <v>247</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>8</v>
+        <v>248</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>9</v>
+        <v>249</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>10</v>
+        <v>250</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>99</v>
+        <v>252</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>100</v>
+        <v>253</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>8</v>
+        <v>254</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>14</v>
+        <v>255</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>10</v>
+        <v>256</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>101</v>
+        <v>258</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>102</v>
+        <v>259</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>8</v>
+        <v>260</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>17</v>
+        <v>261</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>18</v>
+        <v>262</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>103</v>
+        <v>264</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>102</v>
+        <v>265</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>8</v>
+        <v>266</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>20</v>
+        <v>267</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>18</v>
+        <v>268</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>104</v>
+        <v>270</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>105</v>
+        <v>271</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>8</v>
+        <v>272</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>14</v>
+        <v>273</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>23</v>
+        <v>274</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>106</v>
+        <v>276</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>107</v>
+        <v>277</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>8</v>
+        <v>278</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>9</v>
+        <v>279</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>23</v>
+        <v>280</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>108</v>
+        <v>282</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>109</v>
+        <v>283</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>8</v>
+        <v>284</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>20</v>
+        <v>285</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>28</v>
+        <v>286</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>110</v>
+        <v>288</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>111</v>
+        <v>289</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>8</v>
+        <v>290</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>14</v>
+        <v>291</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>31</v>
+        <v>292</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>112</v>
+        <v>294</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>113</v>
+        <v>295</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>8</v>
+        <v>296</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>9</v>
+        <v>297</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>10</v>
+        <v>298</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>115</v>
+        <v>300</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>116</v>
+        <v>301</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>8</v>
+        <v>302</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>14</v>
+        <v>303</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>10</v>
+        <v>304</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>117</v>
+        <v>306</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>118</v>
+        <v>307</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>8</v>
+        <v>308</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>17</v>
+        <v>309</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>18</v>
+        <v>310</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>119</v>
+        <v>312</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>118</v>
+        <v>313</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>8</v>
+        <v>314</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>20</v>
+        <v>315</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>18</v>
+        <v>316</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>120</v>
+        <v>318</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>121</v>
+        <v>319</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>8</v>
+        <v>320</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>14</v>
+        <v>321</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>23</v>
+        <v>322</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>122</v>
+        <v>324</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>123</v>
+        <v>325</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>8</v>
+        <v>326</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>9</v>
+        <v>327</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>23</v>
+        <v>328</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>125</v>
+        <v>331</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>8</v>
+        <v>332</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>20</v>
+        <v>333</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>28</v>
+        <v>334</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>126</v>
+        <v>336</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>127</v>
+        <v>337</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>8</v>
+        <v>338</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>14</v>
+        <v>339</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>31</v>
+        <v>340</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>128</v>
+        <v>342</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>129</v>
+        <v>343</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>8</v>
+        <v>344</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>9</v>
+        <v>345</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>10</v>
+        <v>346</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>131</v>
+        <v>348</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>132</v>
+        <v>349</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>8</v>
+        <v>350</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>14</v>
+        <v>351</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>10</v>
+        <v>352</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>133</v>
+        <v>354</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>134</v>
+        <v>355</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>8</v>
+        <v>356</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>17</v>
+        <v>357</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>18</v>
+        <v>358</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>135</v>
+        <v>360</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>134</v>
+        <v>361</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>8</v>
+        <v>362</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>20</v>
+        <v>363</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>18</v>
+        <v>364</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>136</v>
+        <v>366</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>137</v>
+        <v>367</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>8</v>
+        <v>368</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>14</v>
+        <v>369</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>23</v>
+        <v>370</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>138</v>
+        <v>372</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>139</v>
+        <v>373</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>8</v>
+        <v>374</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>9</v>
+        <v>375</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>23</v>
+        <v>376</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>140</v>
+        <v>378</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>141</v>
+        <v>379</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>8</v>
+        <v>380</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>20</v>
+        <v>381</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>28</v>
+        <v>382</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>142</v>
+        <v>384</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>143</v>
+        <v>385</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>8</v>
+        <v>386</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>14</v>
+        <v>387</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>31</v>
+        <v>388</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>144</v>
+        <v>390</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>145</v>
+        <v>391</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>8</v>
+        <v>392</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>9</v>
+        <v>393</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>10</v>
+        <v>394</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>147</v>
+        <v>396</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>148</v>
+        <v>397</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>8</v>
+        <v>398</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>14</v>
+        <v>399</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>10</v>
+        <v>400</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>149</v>
+        <v>402</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>150</v>
+        <v>403</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>8</v>
+        <v>404</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>17</v>
+        <v>405</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>18</v>
+        <v>406</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>151</v>
+        <v>408</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>150</v>
+        <v>409</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>8</v>
+        <v>410</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>20</v>
+        <v>411</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>18</v>
+        <v>412</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>152</v>
+        <v>414</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>153</v>
+        <v>415</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>8</v>
+        <v>416</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>14</v>
+        <v>417</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>23</v>
+        <v>418</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A71" s="1" t="s">
-        <v>154</v>
+        <v>420</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>155</v>
+        <v>421</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>8</v>
+        <v>422</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>9</v>
+        <v>423</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>23</v>
+        <v>424</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>156</v>
+        <v>426</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>157</v>
+        <v>427</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>8</v>
+        <v>428</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>20</v>
+        <v>429</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>28</v>
+        <v>430</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>158</v>
+        <v>432</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>159</v>
+        <v>433</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>8</v>
+        <v>434</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>14</v>
+        <v>435</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>31</v>
+        <v>436</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>160</v>
+        <v>438</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>161</v>
+        <v>439</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>8</v>
+        <v>440</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>9</v>
+        <v>441</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>10</v>
+        <v>442</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>163</v>
+        <v>444</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>164</v>
+        <v>445</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>8</v>
+        <v>446</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>14</v>
+        <v>447</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>10</v>
+        <v>448</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>165</v>
+        <v>450</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>166</v>
+        <v>451</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>8</v>
+        <v>452</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>17</v>
+        <v>453</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>18</v>
+        <v>454</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>167</v>
+        <v>456</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>166</v>
+        <v>457</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>8</v>
+        <v>458</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>20</v>
+        <v>459</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>18</v>
+        <v>460</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>168</v>
+        <v>462</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>169</v>
+        <v>463</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>8</v>
+        <v>464</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>14</v>
+        <v>465</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>23</v>
+        <v>466</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>170</v>
+        <v>468</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>171</v>
+        <v>469</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>8</v>
+        <v>470</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>9</v>
+        <v>471</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>23</v>
+        <v>472</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>172</v>
+        <v>474</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>173</v>
+        <v>475</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>8</v>
+        <v>476</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>20</v>
+        <v>477</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>28</v>
+        <v>478</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A81" s="1" t="s">
-        <v>174</v>
+        <v>480</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>175</v>
+        <v>481</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>8</v>
+        <v>482</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>14</v>
+        <v>483</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>31</v>
+        <v>484</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A82" s="1" t="s">
-        <v>176</v>
+        <v>486</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>177</v>
+        <v>487</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>8</v>
+        <v>488</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>9</v>
+        <v>489</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>10</v>
+        <v>490</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A83" s="1" t="s">
-        <v>179</v>
+        <v>492</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>180</v>
+        <v>493</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>8</v>
+        <v>494</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>14</v>
+        <v>495</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>10</v>
+        <v>496</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A84" s="1" t="s">
-        <v>181</v>
+        <v>498</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>182</v>
+        <v>499</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>8</v>
+        <v>500</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>17</v>
+        <v>501</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>18</v>
+        <v>502</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A85" s="1" t="s">
-        <v>183</v>
+        <v>504</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>182</v>
+        <v>505</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>8</v>
+        <v>506</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>20</v>
+        <v>507</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>18</v>
+        <v>508</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A86" s="1" t="s">
-        <v>184</v>
+        <v>510</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>185</v>
+        <v>511</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>8</v>
+        <v>512</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>14</v>
+        <v>513</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>23</v>
+        <v>514</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A87" s="1" t="s">
-        <v>186</v>
+        <v>516</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>187</v>
+        <v>517</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>8</v>
+        <v>518</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>9</v>
+        <v>519</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>23</v>
+        <v>520</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A88" s="1" t="s">
-        <v>188</v>
+        <v>522</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>189</v>
+        <v>523</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>8</v>
+        <v>524</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>20</v>
+        <v>525</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>28</v>
+        <v>526</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A89" s="1" t="s">
-        <v>190</v>
+        <v>528</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>191</v>
+        <v>529</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>8</v>
+        <v>530</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>14</v>
+        <v>531</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>31</v>
+        <v>532</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A90" s="1" t="s">
-        <v>192</v>
+        <v>534</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>193</v>
+        <v>535</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>8</v>
+        <v>536</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>9</v>
+        <v>537</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>10</v>
+        <v>538</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A91" s="1" t="s">
-        <v>195</v>
+        <v>540</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>196</v>
+        <v>541</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>8</v>
+        <v>542</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>14</v>
+        <v>543</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>10</v>
+        <v>544</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A92" s="1" t="s">
-        <v>197</v>
+        <v>546</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>198</v>
+        <v>547</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>8</v>
+        <v>548</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>17</v>
+        <v>549</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>18</v>
+        <v>550</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A93" s="1" t="s">
-        <v>199</v>
+        <v>552</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>198</v>
+        <v>553</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>8</v>
+        <v>554</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>20</v>
+        <v>555</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>18</v>
+        <v>556</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A94" s="1" t="s">
-        <v>200</v>
+        <v>558</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>201</v>
+        <v>559</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>8</v>
+        <v>560</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>14</v>
+        <v>561</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>23</v>
+        <v>562</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A95" s="1" t="s">
-        <v>202</v>
+        <v>564</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>203</v>
+        <v>565</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>8</v>
+        <v>566</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>9</v>
+        <v>567</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>23</v>
+        <v>568</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A96" s="1" t="s">
-        <v>204</v>
+        <v>570</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>205</v>
+        <v>571</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>8</v>
+        <v>572</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>20</v>
+        <v>573</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>28</v>
+        <v>574</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
       <c r="A97" s="1" t="s">
-        <v>206</v>
+        <v>576</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>207</v>
+        <v>577</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>8</v>
+        <v>578</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>14</v>
+        <v>579</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>31</v>
+        <v>580</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>194</v>
+        <v>581</v>
       </c>
     </row>
   </sheetData>

--- a/fine_tuning_excel_pack_brand_voice_UTF8_FIXED/01_train_examples_brand_voice_UTF8_FIXED.xlsx
+++ b/fine_tuning_excel_pack_brand_voice_UTF8_FIXED/01_train_examples_brand_voice_UTF8_FIXED.xlsx
@@ -6077,9 +6077,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" ns1:Ignorable="x14ac xr xr2 xr3" ns2:uid="{B81724B5-3AFA-4C3F-A26F-99DBA64F7C78}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac xr" xr:uid="{B81724B5-3AFA-4C3F-A26F-99DBA64F7C78}">
   <dimension ref="A1:F97"/>
-  <sheetFormatPr defaultRowHeight="14.4" ns3:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="62.77734375" customWidth="1"/>
     <col min="2" max="2" width="82.77734375" customWidth="1"/>
@@ -6088,7 +6088,7 @@
     <col min="6" max="6" width="28.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="3" customFormat="1" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="1" spans="1:6" s="3" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -6108,7 +6108,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="2" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -6128,7 +6128,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="3" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -6148,7 +6148,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="4" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -6168,7 +6168,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="5" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>24</v>
       </c>
@@ -6188,7 +6188,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
@@ -6208,7 +6208,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="7" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>36</v>
       </c>
@@ -6228,7 +6228,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="8" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>42</v>
       </c>
@@ -6248,7 +6248,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="9" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>48</v>
       </c>
@@ -6268,7 +6268,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="10" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>54</v>
       </c>
@@ -6288,7 +6288,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="11" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>60</v>
       </c>
@@ -6308,7 +6308,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="12" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>66</v>
       </c>
@@ -6328,7 +6328,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="13" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>72</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="14" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>78</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>84</v>
       </c>
@@ -6388,7 +6388,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="16" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>90</v>
       </c>
@@ -6408,7 +6408,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>96</v>
       </c>
@@ -6428,7 +6428,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>102</v>
       </c>
@@ -6448,7 +6448,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>108</v>
       </c>
@@ -6468,7 +6468,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>114</v>
       </c>
@@ -6488,7 +6488,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>120</v>
       </c>
@@ -6508,7 +6508,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>126</v>
       </c>
@@ -6528,7 +6528,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="23" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>132</v>
       </c>
@@ -6548,7 +6548,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="24" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>138</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="25" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>144</v>
       </c>
@@ -6588,7 +6588,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="26" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>150</v>
       </c>
@@ -6608,7 +6608,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="27" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>156</v>
       </c>
@@ -6628,7 +6628,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="28" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>162</v>
       </c>
@@ -6648,7 +6648,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="29" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>168</v>
       </c>
@@ -6668,7 +6668,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="30" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>174</v>
       </c>
@@ -6688,7 +6688,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="31" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>180</v>
       </c>
@@ -6708,7 +6708,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="32" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>186</v>
       </c>
@@ -6728,7 +6728,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="33" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>192</v>
       </c>
@@ -6748,7 +6748,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="34" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>198</v>
       </c>
@@ -6768,7 +6768,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="35" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>204</v>
       </c>
@@ -6788,7 +6788,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="36" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>210</v>
       </c>
@@ -6808,7 +6808,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="37" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>216</v>
       </c>
@@ -6828,7 +6828,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="38" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>222</v>
       </c>
@@ -6848,7 +6848,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="39" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>228</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="40" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>234</v>
       </c>
@@ -6888,7 +6888,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="41" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>240</v>
       </c>
@@ -6908,7 +6908,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="42" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>246</v>
       </c>
@@ -6928,7 +6928,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="43" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>252</v>
       </c>
@@ -6948,7 +6948,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="44" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>258</v>
       </c>
@@ -6968,7 +6968,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="45" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>264</v>
       </c>
@@ -6988,7 +6988,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="46" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>270</v>
       </c>
@@ -7008,7 +7008,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>276</v>
       </c>
@@ -7028,7 +7028,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="48" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>282</v>
       </c>
@@ -7048,7 +7048,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="49" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>288</v>
       </c>
@@ -7068,7 +7068,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="50" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>294</v>
       </c>
@@ -7088,7 +7088,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>300</v>
       </c>
@@ -7108,7 +7108,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>306</v>
       </c>
@@ -7128,7 +7128,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="53" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>312</v>
       </c>
@@ -7148,7 +7148,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="54" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>318</v>
       </c>
@@ -7168,7 +7168,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>324</v>
       </c>
@@ -7188,7 +7188,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="56" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>330</v>
       </c>
@@ -7208,7 +7208,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="57" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>336</v>
       </c>
@@ -7228,7 +7228,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>342</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="59" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>348</v>
       </c>
@@ -7268,7 +7268,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="60" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>354</v>
       </c>
@@ -7288,7 +7288,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="61" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>360</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="62" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>366</v>
       </c>
@@ -7328,7 +7328,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>372</v>
       </c>
@@ -7348,7 +7348,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>378</v>
       </c>
@@ -7368,7 +7368,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="65" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>384</v>
       </c>
@@ -7388,7 +7388,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="66" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>390</v>
       </c>
@@ -7408,7 +7408,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="67" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>396</v>
       </c>
@@ -7428,7 +7428,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="68" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>402</v>
       </c>
@@ -7448,7 +7448,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="69" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>408</v>
       </c>
@@ -7468,7 +7468,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="70" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>414</v>
       </c>
@@ -7488,7 +7488,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="71" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>420</v>
       </c>
@@ -7508,7 +7508,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="72" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>426</v>
       </c>
@@ -7528,7 +7528,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="73" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>432</v>
       </c>
@@ -7548,7 +7548,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="74" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>438</v>
       </c>
@@ -7568,7 +7568,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="75" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>444</v>
       </c>
@@ -7588,7 +7588,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="76" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>450</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="77" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="77" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>456</v>
       </c>
@@ -7628,7 +7628,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="78" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>462</v>
       </c>
@@ -7648,7 +7648,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="79" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>468</v>
       </c>
@@ -7668,7 +7668,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="80" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="80" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>474</v>
       </c>
@@ -7688,7 +7688,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="81" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="81" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>480</v>
       </c>
@@ -7708,7 +7708,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="82" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="82" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>486</v>
       </c>
@@ -7728,7 +7728,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="83" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="83" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>492</v>
       </c>
@@ -7748,7 +7748,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="84" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>498</v>
       </c>
@@ -7768,7 +7768,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="85" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="85" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>504</v>
       </c>
@@ -7788,7 +7788,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="86" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="86" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>510</v>
       </c>
@@ -7808,7 +7808,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="87" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="87" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>516</v>
       </c>
@@ -7828,7 +7828,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="88" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="88" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>522</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="89" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>528</v>
       </c>
@@ -7868,7 +7868,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="90" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>534</v>
       </c>
@@ -7888,7 +7888,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="91" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="91" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>540</v>
       </c>
@@ -7908,7 +7908,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="92" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="92" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>546</v>
       </c>
@@ -7928,7 +7928,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="93" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="93" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>552</v>
       </c>
@@ -7948,7 +7948,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="94" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="94" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>558</v>
       </c>
@@ -7968,7 +7968,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="95" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>564</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="96" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="96" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>570</v>
       </c>
@@ -8008,7 +8008,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="97" spans="1:6" ht="54" customHeight="1" ns3:dyDescent="0.3">
+    <row r="97" spans="1:6" ht="54" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>576</v>
       </c>
